--- a/Sidetrade_Valuation_2026_v2.xlsx
+++ b/Sidetrade_Valuation_2026_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abbah\Downloads\Portefolio\Portefolio\Sidetrade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90046EA8-93B2-4ADE-91CA-FC1F0520E702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEABC4CA-E2F6-48EC-A88B-F64CDC90A3C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21840" tabRatio="500" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="922" uniqueCount="732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="732">
   <si>
     <t>LBO AFFORDABILITY MODEL — BASE CASE  |  Max Entry EV for IRR targets</t>
   </si>
@@ -1085,7 +1085,7 @@
     <t>TRADING COMPS — SaaS B2B / Finance Automation / O2C peers  |  Forward multiples FY2026E</t>
   </si>
   <si>
-    <t>EUR-translated at ~1.10 USD/EUR. Multiples approx. H1-2025. Update if market moves materially.</t>
+    <t>ATTENTION - Multiples approx. H1-2025, PERIMES: rafraichir prix/guidances 2026 des 4 peers avant toute diffusion (sources: communiques guidance 2026, cf. note audit 12.5). Metriques non homogenes entre peers (EBITDA adj. / non-GAAP OI). EUR/USD ~1.10. Derniere revue: 15-Jul-2026.</t>
   </si>
   <si>
     <t>Company</t>
@@ -1172,7 +1172,10 @@
     <t>O2C SaaS — Bridgepoint/GA acq. 2024</t>
   </si>
   <si>
-    <t>* Last traded pre-announcement. Deal: 6.9× FY25E Sales, 34.6× EBITDA</t>
+    <t>"n.m."</t>
+  </si>
+  <si>
+    <t>* Last traded pre-announcement. Deal 2024: ~7,7x CA 2024A / ~6,9x FY25E Sales (doc offre). EBITDA n.d.</t>
   </si>
   <si>
     <t>AGGREGATES (excl. Esker * reference row — row 9)</t>
@@ -1223,7 +1226,7 @@
     <t>Selected trading comp range  (€m EV)</t>
   </si>
   <si>
-    <t>Consistent with Valo.docx synthesis. Midpoint aligns with DCF Base.</t>
+    <t>Derive: moyenne des EV implicites Sales/EBITDA aux multiples retenus (l.21/23). Plus de midpoint saisi en dur (audit 4.4) - la fourchette bouge si les multiples ou le DCF bougent.</t>
   </si>
   <si>
     <t>* Esker (row 9): taken private. Included as directional reference only; use Transaction_comps for control multiples.</t>
@@ -1232,7 +1235,7 @@
     <t>TRANSACTION COMPS — Precedent M&amp;A in Office-of-CFO / O2C / Fintech SaaS  (control transactions)</t>
   </si>
   <si>
-    <t>All deals include control premium (30-50% vs. trading). Not directly comparable to stand-alone DCF/trading EV.</t>
+    <t>All deals include control premium (30-50% vs. trading). Faits verifies et corriges le 15-Jul-2026 (audit 4.5): Billtrust-&gt;EQT, Bottomline-&gt;Thoma Bravo, Esker EV/CA restates.</t>
   </si>
   <si>
     <t>Target</t>
@@ -1268,7 +1271,7 @@
     <t>O2C / AR automation (France)</t>
   </si>
   <si>
-    <t>Best read-across: same vertical, Euronext Growth, enterprise O2C</t>
+    <t>Offre 262 EUR/action (sept. 2024): equity ~1 619 M, EV ~1 576 M; ~7,7x CA 2024A (205,3 M). Doc offre: moyenne transactions ~6,8x NTM Sales. EBITDA LTM non retraite -&gt; exclu des agregats.</t>
   </si>
   <si>
     <t>Coupa</t>
@@ -1286,13 +1289,13 @@
     <t>Billtrust</t>
   </si>
   <si>
-    <t>Corpay (FLYW)</t>
+    <t>EQT Private Equity</t>
   </si>
   <si>
     <t>AR invoicing / cash app SaaS</t>
   </si>
   <si>
-    <t>~$1.75B; ~9× Sales; scale player AR automation</t>
+    <t>~USD 1,7 Md take-private (annonce sept. 2022); ~9x Sales; scale player AR automation</t>
   </si>
   <si>
     <t>Pagero</t>
@@ -1310,9 +1313,6 @@
     <t>Bottomline Tech.</t>
   </si>
   <si>
-    <t>Symphony Technology</t>
-  </si>
-  <si>
     <t>B2B payments / cash management</t>
   </si>
   <si>
@@ -1322,7 +1322,7 @@
     <t>AGGREGATES</t>
   </si>
   <si>
-    <t>Coupa excluded from EBITDA aggregates (near-breakeven at deal, 161.6x n/m)</t>
+    <t>Coupa (161x n/m) et Esker (EBITDA n.d.) exclus des agregats EV/EBITDA</t>
   </si>
   <si>
     <t>IMPLIED CONTROL EV FOR SIDETRADE</t>
@@ -1358,7 +1358,7 @@
     <t>Selected transaction comp range  (€m EV)</t>
   </si>
   <si>
-    <t>Control premium ~40% vs. stand-alone. Base €410m consistent with Valo.docx.</t>
+    <t>Derive des multiples ligne 24 (mid = moyenne doc offre Esker ~6,8x NTM avec decote taille). Control premium ~40% vs stand-alone.</t>
   </si>
   <si>
     <t>IMPORTANT: Transaction comps include control premium. NOT directly comparable to DCF or trading comp EV.</t>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="B12" s="13">
         <f>Transaction_comps!F27</f>
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C12" s="14" t="s">
         <v>57</v>
@@ -3353,15 +3353,15 @@
       </c>
       <c r="B17" s="23">
         <f>Trading_comps!E26</f>
-        <v>185</v>
+        <v>211</v>
       </c>
       <c r="C17" s="23">
         <f>Trading_comps!F26</f>
-        <v>295</v>
+        <v>361</v>
       </c>
       <c r="D17" s="23">
         <f>Trading_comps!G26</f>
-        <v>425</v>
+        <v>548</v>
       </c>
       <c r="E17" s="24" t="s">
         <v>66</v>
@@ -3373,15 +3373,15 @@
       </c>
       <c r="B18" s="20">
         <f>Transaction_comps!E27</f>
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C18" s="20">
         <f>Transaction_comps!F27</f>
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D18" s="20">
         <f>Transaction_comps!G27</f>
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="E18" s="21" t="s">
         <v>68</v>
@@ -7576,23 +7576,23 @@
       </c>
       <c r="B6" s="89">
         <f>Trading_comps!E26</f>
-        <v>185</v>
+        <v>211</v>
       </c>
       <c r="C6" s="89">
         <f>Trading_comps!F26</f>
-        <v>295</v>
+        <v>361</v>
       </c>
       <c r="D6" s="89">
         <f>Trading_comps!G26</f>
-        <v>425</v>
+        <v>548</v>
       </c>
       <c r="E6" s="90">
         <f>C6/Inputs!B7</f>
-        <v>22.041243275552898</v>
+        <v>26.972504482964734</v>
       </c>
       <c r="F6" s="90">
         <f>C6/Inputs!B6</f>
-        <v>4.8033085840823242</v>
+        <v>5.8779471147583697</v>
       </c>
       <c r="G6" s="91" t="s">
         <v>653</v>
@@ -7604,23 +7604,23 @@
       </c>
       <c r="B7" s="92">
         <f>Transaction_comps!E27</f>
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C7" s="92">
         <f>Transaction_comps!F27</f>
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D7" s="92">
         <f>Transaction_comps!G27</f>
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="E7" s="93">
         <f>C7/Inputs!B7</f>
-        <v>30.63359234907352</v>
+        <v>30.708308427973698</v>
       </c>
       <c r="F7" s="93">
         <f>C7/Inputs!B6</f>
-        <v>6.6757848117754337</v>
+        <v>6.6920672137553732</v>
       </c>
       <c r="G7" s="94" t="s">
         <v>655</v>
@@ -7689,7 +7689,7 @@
       </c>
       <c r="C12" s="98">
         <f>Transaction_comps!F27</f>
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -7705,7 +7705,7 @@
       </c>
       <c r="D13" s="72">
         <f>Trading_comps!G26</f>
-        <v>425</v>
+        <v>548</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -7732,11 +7732,11 @@
       </c>
       <c r="B17" s="101" t="str">
         <f>REPT("░",ROUND(B6/600*48,0))&amp;REPT("█",MAX(1,ROUND((D6-B6)/600*48,0)))&amp;REPT("░",MAX(0,48-ROUND(B6/600*48,0)-MAX(1,ROUND((D6-B6)/600*48,0))))</f>
-        <v>░░░░░░░░░░░░░░░███████████████████░░░░░░░░░░░░░░</v>
+        <v>░░░░░░░░░░░░░░░░░███████████████████████████░░░░</v>
       </c>
       <c r="C17" s="102" t="str">
         <f>"Low €"&amp;TEXT(B6,"0")&amp;"m  |  Base €"&amp;TEXT(C6,"0")&amp;"m  |  High €"&amp;TEXT(D6,"0")&amp;"m"</f>
-        <v>Low €185m  |  Base €295m  |  High €425m</v>
+        <v>Low €211m  |  Base €361m  |  High €548m</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -7745,11 +7745,11 @@
       </c>
       <c r="B18" s="101" t="str">
         <f>REPT("░",ROUND(B7/600*48,0))&amp;REPT("█",MAX(1,ROUND((D7-B7)/600*48,0)))&amp;REPT("░",MAX(0,48-ROUND(B7/600*48,0)-MAX(1,ROUND((D7-B7)/600*48,0))))</f>
-        <v>░░░░░░░░░░░░░░░░░░░░░░░████████████████████░░░░░</v>
+        <v>░░░░░░░░░░░░░░░░░░░░░░░█████████████████████░░░░</v>
       </c>
       <c r="C18" s="102" t="str">
         <f>"Low €"&amp;TEXT(B7,"0")&amp;"m  |  Base €"&amp;TEXT(C7,"0")&amp;"m  |  High €"&amp;TEXT(D7,"0")&amp;"m"</f>
-        <v>Low €290m  |  Base €410m  |  High €545m</v>
+        <v>Low €289m  |  Base €411m  |  High €547m</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="C23" s="52">
         <f>Transaction_comps!F27</f>
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="C24" s="51">
         <f>C23-C12</f>
-        <v>395.346</v>
+        <v>396.346</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="C25" s="107">
         <f>C24/C19</f>
-        <v>257.2544069131111</v>
+        <v>257.90511390625915</v>
       </c>
       <c r="E25" s="28" t="s">
         <v>688</v>
@@ -12093,29 +12093,26 @@
         <v>374</v>
       </c>
       <c r="D9" s="66">
-        <v>1091</v>
+        <v>1576</v>
       </c>
       <c r="E9" s="66">
-        <v>158</v>
-      </c>
-      <c r="F9" s="66">
-        <v>32</v>
-      </c>
+        <v>205.3</v>
+      </c>
+      <c r="F9" s="66"/>
       <c r="G9" s="67">
         <f>D9/E9</f>
-        <v>6.9050632911392409</v>
-      </c>
-      <c r="H9" s="67">
-        <f>D9/F9</f>
-        <v>34.09375</v>
+        <v>7.6765708718947874</v>
+      </c>
+      <c r="H9" s="67" t="s">
+        <v>375</v>
       </c>
       <c r="I9" s="68" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="156" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B11" s="146"/>
       <c r="C11" s="146"/>
@@ -12128,7 +12125,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G12" s="42">
         <f>MEDIAN(G5:G8)</f>
@@ -12141,7 +12138,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="G13" s="42">
         <f>MIN(G5:G8)</f>
@@ -12154,7 +12151,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G14" s="42">
         <f>MAX(G5:G8)</f>
@@ -12167,7 +12164,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="156" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B16" s="146"/>
       <c r="C16" s="146"/>
@@ -12180,7 +12177,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E17" s="72">
         <f>DCF!C7</f>
@@ -12189,7 +12186,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F18" s="72">
         <f>DCF!C12</f>
@@ -12198,21 +12195,21 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F20" s="18" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E21" s="41">
         <v>3</v>
@@ -12226,7 +12223,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E22" s="51">
         <f>E17*E21</f>
@@ -12243,7 +12240,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E23" s="41">
         <v>12</v>
@@ -12257,7 +12254,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E24" s="51">
         <f>F18*E23</f>
@@ -12274,24 +12271,27 @@
     </row>
     <row r="26" spans="1:9" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E26" s="52">
-        <v>185</v>
+        <f>ROUND(AVERAGE(E22,E24),0)</f>
+        <v>211</v>
       </c>
       <c r="F26" s="52">
-        <v>295</v>
+        <f>ROUND(AVERAGE(F22,F24),0)</f>
+        <v>361</v>
       </c>
       <c r="G26" s="52">
-        <v>425</v>
+        <f>ROUND(AVERAGE(G22,G24),0)</f>
+        <v>548</v>
       </c>
       <c r="I26" s="28" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
   </sheetData>
@@ -12320,7 +12320,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="147" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B1" s="146"/>
       <c r="C1" s="146"/>
@@ -12334,36 +12334,36 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="73" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>350</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>28</v>
@@ -12371,50 +12371,47 @@
     </row>
     <row r="5" spans="1:10" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="71" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B5" s="74">
         <v>2024</v>
       </c>
       <c r="C5" s="65" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D5" s="65" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E5" s="66">
-        <v>1091</v>
+        <v>1576</v>
       </c>
       <c r="F5" s="66">
-        <v>158</v>
-      </c>
-      <c r="G5" s="66">
-        <v>32</v>
-      </c>
+        <v>205.3</v>
+      </c>
+      <c r="G5" s="66"/>
       <c r="H5" s="67">
         <f>E5/F5</f>
-        <v>6.9050632911392409</v>
-      </c>
-      <c r="I5" s="67">
-        <f>E5/G5</f>
-        <v>34.09375</v>
+        <v>7.6765708718947874</v>
+      </c>
+      <c r="I5" s="67" t="s">
+        <v>375</v>
       </c>
       <c r="J5" s="68" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B6" s="75">
         <v>2023</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E6" s="69">
         <v>7273</v>
@@ -12434,21 +12431,21 @@
         <v>161.62222222222223</v>
       </c>
       <c r="J6" s="24" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A7" s="71" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B7" s="74">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C7" s="65" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D7" s="65" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E7" s="66">
         <v>1591</v>
@@ -12468,21 +12465,21 @@
         <v>79.55</v>
       </c>
       <c r="J7" s="68" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B8" s="75">
         <v>2024</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E8" s="69">
         <v>600</v>
@@ -12502,18 +12499,18 @@
         <v>33.333333333333336</v>
       </c>
       <c r="J8" s="24" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="71" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B9" s="74">
         <v>2022</v>
       </c>
       <c r="C9" s="65" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="D9" s="65" t="s">
         <v>422</v>
@@ -12554,15 +12551,15 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H12" s="42">
         <f>MEDIAN(H5:H9)</f>
-        <v>6.9050632911392409</v>
+        <v>7.6765708718947874</v>
       </c>
       <c r="I12" s="42">
-        <f>MEDIAN(I5,I7,I8,I9)</f>
-        <v>33.713541666666671</v>
+        <f>MEDIAN(I7,I8,I9)</f>
+        <v>33.333333333333336</v>
       </c>
       <c r="J12" t="s">
         <v>425</v>
@@ -12570,27 +12567,27 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H13" s="42">
         <f>MIN(H5:H9)</f>
         <v>4.9249999999999998</v>
       </c>
       <c r="I13" s="42">
-        <f>MIN(I5,I7,I8,I9)</f>
+        <f>MIN(I7,I8,I9)</f>
         <v>23.64</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H14" s="42">
         <f>MAX(H5:H9)</f>
         <v>10.017906336088155</v>
       </c>
       <c r="I14" s="42">
-        <f>MAX(I5,I7,I8,I9)</f>
+        <f>MAX(I7,I8,I9)</f>
         <v>79.55</v>
       </c>
     </row>
@@ -12693,13 +12690,16 @@
         <v>436</v>
       </c>
       <c r="E27" s="52">
-        <v>290</v>
+        <f>ROUND(E25,0)</f>
+        <v>289</v>
       </c>
       <c r="F27" s="52">
-        <v>410</v>
+        <f>ROUND(F25,0)</f>
+        <v>411</v>
       </c>
       <c r="G27" s="52">
-        <v>545</v>
+        <f>ROUND(G25,0)</f>
+        <v>547</v>
       </c>
       <c r="J27" s="28" t="s">
         <v>437</v>

--- a/Sidetrade_Valuation_2026_v2.xlsx
+++ b/Sidetrade_Valuation_2026_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abbah\Downloads\Portefolio\Portefolio\Sidetrade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEABC4CA-E2F6-48EC-A88B-F64CDC90A3C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A60B031C-6690-4BE3-9586-58778867BA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21840" tabRatio="500" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,6 +26,7 @@
     <sheet name="Football_field" sheetId="11" r:id="rId11"/>
     <sheet name="Equity_bridge" sheetId="12" r:id="rId12"/>
     <sheet name="Caveats" sheetId="13" r:id="rId13"/>
+    <sheet name="Checks" sheetId="14" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="774">
   <si>
     <t>LBO AFFORDABILITY MODEL — BASE CASE  |  Max Entry EV for IRR targets</t>
   </si>
@@ -524,6 +525,69 @@
     <t>Aligned with TV cross-check (row 39).</t>
   </si>
   <si>
+    <t>WACC BUILD — bridge reproductible (Base) — ajouté 15/07/2026 (audit §4.3)</t>
+  </si>
+  <si>
+    <t>Taux sans risque (OAT 10 ans)</t>
+  </si>
+  <si>
+    <t>Niveau retenu dans le modèle ; re-vérifier sur Banque de France / BCE à la date de publication</t>
+  </si>
+  <si>
+    <t>Prime de risque actions zone euro (ERP)</t>
+  </si>
+  <si>
+    <t>Kroll — Recommended Eurozone ERP (kroll.com/en/reports/cost-of-capital) ; re-vérifier à date</t>
+  </si>
+  <si>
+    <t>Bêta relevered (peers SaaS B2B, structure cible)</t>
+  </si>
+  <si>
+    <t>Milieu de la fourchette 1,1-1,3 citée en E37 ; à documenter par régression peers en amélioration future</t>
+  </si>
+  <si>
+    <t>Prime de taille small/micro-cap</t>
+  </si>
+  <si>
+    <t>Kroll size premium, ordre de grandeur small-cap ; à confirmer</t>
+  </si>
+  <si>
+    <t>Coût des fonds propres = rf + beta x ERP + prime</t>
+  </si>
+  <si>
+    <t>Formule</t>
+  </si>
+  <si>
+    <t>Poids cible de la dette (D/(D+E))</t>
+  </si>
+  <si>
+    <t>Structure cible listée modérée (Cantor retient 15%)</t>
+  </si>
+  <si>
+    <t>Coût de la dette pre-tax</t>
+  </si>
+  <si>
+    <t>Corporate small-cap coté (hors structure LBO 7,16%)</t>
+  </si>
+  <si>
+    <t>Coût de la dette after-tax (IS 25,83%)</t>
+  </si>
+  <si>
+    <t>WACC bridgé</t>
+  </si>
+  <si>
+    <t>Formule — doit encadrer le WACC retenu</t>
+  </si>
+  <si>
+    <t>WACC retenu au modèle (C37)</t>
+  </si>
+  <si>
+    <t>Écart bridge vs retenu (pts)</t>
+  </si>
+  <si>
+    <t>Tolérance ±0,25 pt ; réf. externes : Cantor 8,5% (rf 3,0 / ERP 5,5 / beta 1,1 / 15% dette), build conservateur ~10,5%+ ; Bear 10,5% / Bull 8,5% = bornes de la fourchette</t>
+  </si>
+  <si>
     <t>FY25 BASE — FULL RECONCILIATION  (sources: Statutory Report 31-Dec-2025 + Press Release 30-Mar-2026)</t>
   </si>
   <si>
@@ -2198,19 +2262,19 @@
     <t>Terminal value weight</t>
   </si>
   <si>
-    <t>Gordon Growth TV = 55-65% of total EV at Base case (WACC 9.5%, TG 2.5%). High TV weight is normal for high-growth SaaS with long-term franchise. Exit multiple cross-check (15× EBITDA) gives ~10% lower EV. At 20× EBITDA (closer to trading comps), both methods converge.</t>
-  </si>
-  <si>
-    <t>±15-20% EV per ±1% WACC or TG. See Sensitivity tab.</t>
-  </si>
-  <si>
-    <t>Always present both TV methods. Gordon Growth is primary; exit multiple is floor cross-check.</t>
+    <t>Gordon Growth TV = 77.2% of total EV at Base (WACC 9.5%, TG 2.5%) — mechanically high with a 5-year explicit horizon (Cantor, with a much longer explicit + fade period, gets 61%). Exit-multiple cross-check at 15x gives EV ~413m, i.e. +37% ABOVE Gordon — the cross-check sits above, NOT ~10% below as previously stated (caveat corrected 15-Jul-2026, audit §4.2).</t>
+  </si>
+  <si>
+    <t>TV = 77.2% of Base EV; ±15-20% EV per ±1% WACC or TG. See Sensitivity tab.</t>
+  </si>
+  <si>
+    <t>Present both TV methods; Gordon is primary AND the more conservative here. Improvement: extend explicit horizon (10y fade) to cut TV weight.</t>
   </si>
   <si>
     <t>Transaction comps control premium</t>
   </si>
   <si>
-    <t>Esker (6.9× Sales, 34.6× EBITDA FY25E) is best read-across. All transaction comps include 30-50% control premium vs. trading. Sidetrade discount factors: ~40% smaller, less liquid (Euronext Growth vs. NYSE), AI-native monetization earlier stage. Control case EV = ~€410m, not a stand-alone fair value.</t>
+    <t>Esker (deal 2024: EV ~1,576m corrected, ~7.7x FY24A Sales, ~6.9x NTM per offer doc; EBITDA multiple n.d.) is best read-across. All transaction comps include 30-50% control premium vs. trading. Sidetrade discount factored via size/liquidity.</t>
   </si>
   <si>
     <t>+40% vs. stand-alone DCF</t>
@@ -2241,13 +2305,76 @@
   </si>
   <si>
     <t>Use normalized FCF as DCF starting point. Statutory FCF is the downside sensitivity.</t>
+  </si>
+  <si>
+    <t>CHECKS — CONTRÔLES D'INTÉGRITÉ DU CLASSEUR (ajouté 15/07/2026, audit §10.3)</t>
+  </si>
+  <si>
+    <t>Contrôle</t>
+  </si>
+  <si>
+    <t>Valeur</t>
+  </si>
+  <si>
+    <t>Tolérance</t>
+  </si>
+  <si>
+    <t>Statut</t>
+  </si>
+  <si>
+    <t>Tie-out CA FY25 = 61,416 (PR FY25 / Stat. Report Note 15)</t>
+  </si>
+  <si>
+    <t>Tie-out EBITDA FY25 incl. CIR = 13,384 (Stat. Report p.5)</t>
+  </si>
+  <si>
+    <t>Sources &amp; Uses LBO équilibrés — Bear</t>
+  </si>
+  <si>
+    <t>Sources &amp; Uses LBO équilibrés — Base</t>
+  </si>
+  <si>
+    <t>Sources &amp; Uses LBO équilibrés — Bull</t>
+  </si>
+  <si>
+    <t>IRR live = cible 22,5% au défaut — Bear</t>
+  </si>
+  <si>
+    <t>IRR live = cible 22,5% au défaut — Base</t>
+  </si>
+  <si>
+    <t>IRR live = cible 22,5% au défaut — Bull</t>
+  </si>
+  <si>
+    <t>Moteur vs formules — delta IRR Base (bloc vérification)</t>
+  </si>
+  <si>
+    <t>Moteur vs formules — delta sponsor entry Base</t>
+  </si>
+  <si>
+    <t>Trading comps: fourchette liée aux EV implicites (Base)</t>
+  </si>
+  <si>
+    <t>Transaction comps: fourchette liée aux EV implicites (Base)</t>
+  </si>
+  <si>
+    <t>WACC retenu dans la tolérance du bridge (±0,25 pt)</t>
+  </si>
+  <si>
+    <t>Football field: LBO Base = affordability 22,5%</t>
+  </si>
+  <si>
+    <t>STATUT GLOBAL</t>
+  </si>
+  <si>
+    <t>Notes : les constantes engine-solved (ligne 50, affordability, sensibilités, bloc vérification de LBO_full) sont régénérées par lbo_engine.py — si un input change sans relancer le moteur, les contrôles 6-10 passent en FAIL. Dernière régénération : 15/07/2026.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="11">
+  <numFmts count="12">
     <numFmt numFmtId="164" formatCode="#,##0.0;\(#,##0.0\);\-"/>
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
@@ -2259,8 +2386,9 @@
     <numFmt numFmtId="172" formatCode="0.00\x"/>
     <numFmt numFmtId="173" formatCode="0.0&quot;x&quot;"/>
     <numFmt numFmtId="174" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="175" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="36" x14ac:knownFonts="1">
+  <fonts count="41" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2494,8 +2622,36 @@
       <color rgb="FFC00000"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF808080"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FF1F3864"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2582,6 +2738,21 @@
         <fgColor rgb="FFF4E7E7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E2F3"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -2604,7 +2775,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="158">
+  <cellXfs count="168">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2862,6 +3033,16 @@
     <xf numFmtId="171" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="171" fontId="32" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="40" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="36" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3172,31 +3353,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="162" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="146"/>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
-      <c r="E1" s="146"/>
+      <c r="B1" s="156"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
     </row>
     <row r="2" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="151" t="s">
+      <c r="A2" s="161" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="146"/>
-      <c r="C2" s="146"/>
-      <c r="D2" s="146"/>
-      <c r="E2" s="146"/>
+      <c r="B2" s="156"/>
+      <c r="C2" s="156"/>
+      <c r="D2" s="156"/>
+      <c r="E2" s="156"/>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="148" t="s">
+      <c r="A4" s="158" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="146"/>
-      <c r="C4" s="146"/>
-      <c r="D4" s="146"/>
-      <c r="E4" s="146"/>
+      <c r="B4" s="156"/>
+      <c r="C4" s="156"/>
+      <c r="D4" s="156"/>
+      <c r="E4" s="156"/>
     </row>
     <row r="5" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
@@ -3284,13 +3465,13 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="148" t="s">
+      <c r="A11" s="158" t="s">
         <v>55</v>
       </c>
-      <c r="B11" s="146"/>
-      <c r="C11" s="146"/>
-      <c r="D11" s="146"/>
-      <c r="E11" s="146"/>
+      <c r="B11" s="156"/>
+      <c r="C11" s="156"/>
+      <c r="D11" s="156"/>
+      <c r="E11" s="156"/>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
@@ -3305,13 +3486,13 @@
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="148" t="s">
+      <c r="A14" s="158" t="s">
         <v>58</v>
       </c>
-      <c r="B14" s="146"/>
-      <c r="C14" s="146"/>
-      <c r="D14" s="146"/>
-      <c r="E14" s="146"/>
+      <c r="B14" s="156"/>
+      <c r="C14" s="156"/>
+      <c r="D14" s="156"/>
+      <c r="E14" s="156"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B15" s="15" t="s">
@@ -3408,13 +3589,13 @@
       </c>
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="148" t="s">
+      <c r="A21" s="158" t="s">
         <v>71</v>
       </c>
-      <c r="B21" s="146"/>
-      <c r="C21" s="146"/>
-      <c r="D21" s="146"/>
-      <c r="E21" s="146"/>
+      <c r="B21" s="156"/>
+      <c r="C21" s="156"/>
+      <c r="D21" s="156"/>
+      <c r="E21" s="156"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
@@ -3453,13 +3634,13 @@
       </c>
     </row>
     <row r="27" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="148" t="s">
+      <c r="A27" s="158" t="s">
         <v>76</v>
       </c>
-      <c r="B27" s="146"/>
-      <c r="C27" s="146"/>
-      <c r="D27" s="146"/>
-      <c r="E27" s="146"/>
+      <c r="B27" s="156"/>
+      <c r="C27" s="156"/>
+      <c r="D27" s="156"/>
+      <c r="E27" s="156"/>
     </row>
     <row r="28" spans="1:5" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="26" t="s">
@@ -3545,85 +3726,85 @@
       </c>
     </row>
     <row r="35" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="147" t="s">
+      <c r="A35" s="157" t="s">
         <v>89</v>
       </c>
-      <c r="B35" s="146"/>
-      <c r="C35" s="146"/>
-      <c r="D35" s="146"/>
-      <c r="E35" s="146"/>
+      <c r="B35" s="156"/>
+      <c r="C35" s="156"/>
+      <c r="D35" s="156"/>
+      <c r="E35" s="156"/>
     </row>
     <row r="36" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="150" t="s">
+      <c r="A36" s="160" t="s">
         <v>90</v>
       </c>
-      <c r="B36" s="146"/>
-      <c r="C36" s="146"/>
-      <c r="D36" s="146"/>
-      <c r="E36" s="146"/>
+      <c r="B36" s="156"/>
+      <c r="C36" s="156"/>
+      <c r="D36" s="156"/>
+      <c r="E36" s="156"/>
     </row>
     <row r="37" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="149" t="s">
+      <c r="A37" s="159" t="s">
         <v>91</v>
       </c>
-      <c r="B37" s="146"/>
-      <c r="C37" s="146"/>
-      <c r="D37" s="146"/>
-      <c r="E37" s="146"/>
+      <c r="B37" s="156"/>
+      <c r="C37" s="156"/>
+      <c r="D37" s="156"/>
+      <c r="E37" s="156"/>
     </row>
     <row r="38" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="150" t="s">
+      <c r="A38" s="160" t="s">
         <v>92</v>
       </c>
-      <c r="B38" s="146"/>
-      <c r="C38" s="146"/>
-      <c r="D38" s="146"/>
-      <c r="E38" s="146"/>
+      <c r="B38" s="156"/>
+      <c r="C38" s="156"/>
+      <c r="D38" s="156"/>
+      <c r="E38" s="156"/>
     </row>
     <row r="39" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="149" t="s">
+      <c r="A39" s="159" t="s">
         <v>93</v>
       </c>
-      <c r="B39" s="146"/>
-      <c r="C39" s="146"/>
-      <c r="D39" s="146"/>
-      <c r="E39" s="146"/>
+      <c r="B39" s="156"/>
+      <c r="C39" s="156"/>
+      <c r="D39" s="156"/>
+      <c r="E39" s="156"/>
     </row>
     <row r="40" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="150" t="s">
+      <c r="A40" s="160" t="s">
         <v>94</v>
       </c>
-      <c r="B40" s="146"/>
-      <c r="C40" s="146"/>
-      <c r="D40" s="146"/>
-      <c r="E40" s="146"/>
+      <c r="B40" s="156"/>
+      <c r="C40" s="156"/>
+      <c r="D40" s="156"/>
+      <c r="E40" s="156"/>
     </row>
     <row r="41" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="149" t="s">
+      <c r="A41" s="159" t="s">
         <v>95</v>
       </c>
-      <c r="B41" s="146"/>
-      <c r="C41" s="146"/>
-      <c r="D41" s="146"/>
-      <c r="E41" s="146"/>
+      <c r="B41" s="156"/>
+      <c r="C41" s="156"/>
+      <c r="D41" s="156"/>
+      <c r="E41" s="156"/>
     </row>
     <row r="42" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="150" t="s">
+      <c r="A42" s="160" t="s">
         <v>96</v>
       </c>
-      <c r="B42" s="146"/>
-      <c r="C42" s="146"/>
-      <c r="D42" s="146"/>
-      <c r="E42" s="146"/>
+      <c r="B42" s="156"/>
+      <c r="C42" s="156"/>
+      <c r="D42" s="156"/>
+      <c r="E42" s="156"/>
     </row>
     <row r="43" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="149" t="s">
+      <c r="A43" s="159" t="s">
         <v>97</v>
       </c>
-      <c r="B43" s="146"/>
-      <c r="C43" s="146"/>
-      <c r="D43" s="146"/>
-      <c r="E43" s="146"/>
+      <c r="B43" s="156"/>
+      <c r="C43" s="156"/>
+      <c r="D43" s="156"/>
+      <c r="E43" s="156"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -3661,22 +3842,22 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="117" t="s">
-        <v>439</v>
+        <v>460</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="118" t="s">
-        <v>440</v>
+        <v>461</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="118" t="s">
-        <v>441</v>
+        <v>462</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="119" t="s">
-        <v>442</v>
+        <v>463</v>
       </c>
       <c r="B4" s="120"/>
       <c r="C4" s="120"/>
@@ -3689,7 +3870,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="121" t="s">
-        <v>443</v>
+        <v>464</v>
       </c>
       <c r="B5" s="122"/>
       <c r="C5" s="122"/>
@@ -3702,7 +3883,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="123" t="s">
-        <v>444</v>
+        <v>465</v>
       </c>
       <c r="B6" s="130">
         <f>B27</f>
@@ -3719,7 +3900,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="123" t="s">
-        <v>445</v>
+        <v>466</v>
       </c>
       <c r="B7" s="137">
         <f>B29</f>
@@ -3736,7 +3917,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="121" t="s">
-        <v>446</v>
+        <v>467</v>
       </c>
       <c r="B9" s="121" t="s">
         <v>101</v>
@@ -3755,7 +3936,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="123" t="s">
-        <v>447</v>
+        <v>468</v>
       </c>
       <c r="B10" s="130">
         <f>B50</f>
@@ -3772,7 +3953,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="131" t="s">
-        <v>448</v>
+        <v>469</v>
       </c>
       <c r="B11" s="138">
         <f>C112</f>
@@ -3789,7 +3970,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="123" t="s">
-        <v>449</v>
+        <v>470</v>
       </c>
       <c r="B12" s="136">
         <f>C113</f>
@@ -3806,7 +3987,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="123" t="s">
-        <v>450</v>
+        <v>471</v>
       </c>
       <c r="B13" s="139">
         <f>B68</f>
@@ -3823,16 +4004,16 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="121" t="s">
-        <v>451</v>
+        <v>472</v>
       </c>
       <c r="B15" s="121" t="s">
-        <v>452</v>
+        <v>473</v>
       </c>
       <c r="C15" s="121" t="s">
-        <v>453</v>
+        <v>474</v>
       </c>
       <c r="D15" s="121" t="s">
-        <v>454</v>
+        <v>475</v>
       </c>
       <c r="E15" s="122"/>
       <c r="F15" s="122"/>
@@ -3854,7 +4035,7 @@
         <v>157.19999999999999</v>
       </c>
       <c r="I16" s="118" t="s">
-        <v>455</v>
+        <v>476</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -3871,7 +4052,7 @@
         <v>222.5</v>
       </c>
       <c r="I17" s="118" t="s">
-        <v>456</v>
+        <v>477</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -3890,7 +4071,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="119" t="s">
-        <v>457</v>
+        <v>478</v>
       </c>
       <c r="B21" s="120"/>
       <c r="C21" s="120"/>
@@ -3906,10 +4087,10 @@
         <v>100</v>
       </c>
       <c r="B22" s="121" t="s">
-        <v>458</v>
+        <v>479</v>
       </c>
       <c r="C22" s="121" t="s">
-        <v>459</v>
+        <v>480</v>
       </c>
       <c r="D22" s="122"/>
       <c r="E22" s="122"/>
@@ -3917,349 +4098,349 @@
       <c r="G22" s="122"/>
       <c r="H22" s="122"/>
       <c r="I22" s="121" t="s">
-        <v>460</v>
+        <v>481</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="123" t="s">
-        <v>461</v>
+        <v>482</v>
       </c>
       <c r="B23" s="124">
         <v>2.3730000000000001E-2</v>
       </c>
       <c r="C23" s="123" t="s">
-        <v>462</v>
+        <v>483</v>
       </c>
       <c r="I23" s="118" t="s">
-        <v>463</v>
+        <v>484</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="123" t="s">
-        <v>464</v>
+        <v>485</v>
       </c>
       <c r="B24" s="124">
         <v>4.7899999999999998E-2</v>
       </c>
       <c r="C24" s="123" t="s">
-        <v>462</v>
+        <v>483</v>
       </c>
       <c r="I24" s="118" t="s">
-        <v>465</v>
+        <v>486</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="123" t="s">
-        <v>466</v>
+        <v>487</v>
       </c>
       <c r="B25" s="125">
         <f>B23+B24</f>
         <v>7.1629999999999999E-2</v>
       </c>
       <c r="C25" s="123" t="s">
-        <v>467</v>
+        <v>488</v>
       </c>
       <c r="I25" s="118" t="s">
-        <v>468</v>
+        <v>489</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="123" t="s">
-        <v>469</v>
+        <v>490</v>
       </c>
       <c r="B26" s="126">
         <v>4</v>
       </c>
       <c r="C26" s="123" t="s">
-        <v>462</v>
+        <v>483</v>
       </c>
       <c r="I26" s="118" t="s">
-        <v>470</v>
+        <v>491</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="123" t="s">
-        <v>471</v>
+        <v>492</v>
       </c>
       <c r="B27" s="127">
         <f>B26*Inputs!B7</f>
         <v>53.536000000000001</v>
       </c>
       <c r="C27" s="123" t="s">
-        <v>467</v>
+        <v>488</v>
       </c>
       <c r="I27" s="118" t="s">
-        <v>472</v>
+        <v>493</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="123" t="s">
-        <v>473</v>
+        <v>494</v>
       </c>
       <c r="B28" s="124">
         <v>0.01</v>
       </c>
       <c r="C28" s="123" t="s">
-        <v>462</v>
+        <v>483</v>
       </c>
       <c r="I28" s="118" t="s">
-        <v>474</v>
+        <v>495</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="123" t="s">
-        <v>475</v>
+        <v>496</v>
       </c>
       <c r="B29" s="124">
         <v>0.75</v>
       </c>
       <c r="C29" s="123" t="s">
-        <v>462</v>
+        <v>483</v>
       </c>
       <c r="I29" s="118" t="s">
-        <v>476</v>
+        <v>497</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="123" t="s">
-        <v>477</v>
+        <v>498</v>
       </c>
       <c r="B30" s="128">
         <v>8</v>
       </c>
       <c r="C30" s="123" t="s">
-        <v>478</v>
+        <v>499</v>
       </c>
       <c r="I30" s="118" t="s">
-        <v>479</v>
+        <v>500</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="123" t="s">
-        <v>480</v>
+        <v>501</v>
       </c>
       <c r="B31" s="124">
         <v>0.03</v>
       </c>
       <c r="C31" s="123" t="s">
-        <v>462</v>
+        <v>483</v>
       </c>
       <c r="I31" s="118" t="s">
-        <v>481</v>
+        <v>502</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="123" t="s">
-        <v>482</v>
+        <v>503</v>
       </c>
       <c r="B32" s="124">
         <v>0.03</v>
       </c>
       <c r="C32" s="123" t="s">
-        <v>462</v>
+        <v>483</v>
       </c>
       <c r="I32" s="118" t="s">
-        <v>483</v>
+        <v>504</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="123" t="s">
-        <v>484</v>
+        <v>505</v>
       </c>
       <c r="B33" s="128">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="C33" s="123" t="s">
-        <v>478</v>
+        <v>499</v>
       </c>
       <c r="I33" s="118" t="s">
-        <v>485</v>
+        <v>506</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="123" t="s">
-        <v>486</v>
+        <v>507</v>
       </c>
       <c r="B34" s="124">
         <v>0.35</v>
       </c>
       <c r="C34" s="123" t="s">
-        <v>487</v>
+        <v>508</v>
       </c>
       <c r="I34" s="118" t="s">
-        <v>488</v>
+        <v>509</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="123" t="s">
-        <v>489</v>
+        <v>510</v>
       </c>
       <c r="B35" s="124">
         <v>0.35</v>
       </c>
       <c r="C35" s="123" t="s">
-        <v>478</v>
+        <v>499</v>
       </c>
       <c r="I35" s="118" t="s">
-        <v>490</v>
+        <v>511</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="123" t="s">
-        <v>491</v>
+        <v>512</v>
       </c>
       <c r="B36" s="126">
         <v>15</v>
       </c>
       <c r="C36" s="123" t="s">
-        <v>478</v>
+        <v>499</v>
       </c>
       <c r="I36" s="118" t="s">
-        <v>492</v>
+        <v>513</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="123" t="s">
-        <v>493</v>
+        <v>514</v>
       </c>
       <c r="B37" s="124">
         <v>0.25</v>
       </c>
       <c r="C37" s="123" t="s">
-        <v>494</v>
+        <v>515</v>
       </c>
       <c r="I37" s="118" t="s">
-        <v>495</v>
+        <v>516</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="123" t="s">
-        <v>496</v>
+        <v>517</v>
       </c>
       <c r="B38" s="124">
         <v>3.3000000000000002E-2</v>
       </c>
       <c r="C38" s="123" t="s">
-        <v>494</v>
+        <v>515</v>
       </c>
       <c r="I38" s="118" t="s">
-        <v>497</v>
+        <v>518</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="123" t="s">
-        <v>498</v>
+        <v>519</v>
       </c>
       <c r="B39" s="128">
         <v>0.76300000000000001</v>
       </c>
       <c r="C39" s="123" t="s">
-        <v>494</v>
+        <v>515</v>
       </c>
       <c r="I39" s="118" t="s">
-        <v>499</v>
+        <v>520</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="123" t="s">
-        <v>500</v>
+        <v>521</v>
       </c>
       <c r="B40" s="127">
         <f>Inputs!B34</f>
         <v>3.5</v>
       </c>
       <c r="C40" s="123" t="s">
-        <v>494</v>
+        <v>515</v>
       </c>
       <c r="I40" s="118" t="s">
-        <v>501</v>
+        <v>522</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="123" t="s">
-        <v>502</v>
+        <v>523</v>
       </c>
       <c r="B41" s="127">
         <f>FY25_base!B49</f>
         <v>14.654</v>
       </c>
       <c r="C41" s="123" t="s">
-        <v>494</v>
+        <v>515</v>
       </c>
       <c r="I41" s="118" t="s">
-        <v>503</v>
+        <v>524</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="123" t="s">
-        <v>504</v>
+        <v>525</v>
       </c>
       <c r="B42" s="127">
         <f>FY25_base!B46</f>
         <v>30.981000000000002</v>
       </c>
       <c r="C42" s="123" t="s">
-        <v>494</v>
+        <v>515</v>
       </c>
       <c r="I42" s="118" t="s">
-        <v>505</v>
+        <v>526</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="123" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="B43" s="127">
         <f>-(FY25_base!B47+FY25_base!B48)</f>
         <v>16.327000000000002</v>
       </c>
       <c r="C43" s="123" t="s">
-        <v>494</v>
+        <v>515</v>
       </c>
       <c r="I43" s="118" t="s">
-        <v>507</v>
+        <v>528</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="123" t="s">
-        <v>508</v>
+        <v>529</v>
       </c>
       <c r="B44" s="128">
         <v>0.45500000000000002</v>
       </c>
       <c r="C44" s="123" t="s">
-        <v>487</v>
+        <v>508</v>
       </c>
       <c r="I44" s="118" t="s">
-        <v>509</v>
+        <v>530</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="123" t="s">
-        <v>510</v>
+        <v>531</v>
       </c>
       <c r="B45" s="128">
         <v>1.4590000000000001</v>
       </c>
       <c r="C45" s="123" t="s">
-        <v>487</v>
+        <v>508</v>
       </c>
       <c r="I45" s="118" t="s">
-        <v>511</v>
+        <v>532</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="123" t="s">
-        <v>512</v>
+        <v>533</v>
       </c>
       <c r="B46" s="129">
         <v>5</v>
       </c>
       <c r="C46" s="123" t="s">
-        <v>478</v>
+        <v>499</v>
       </c>
       <c r="I46" s="118" t="s">
-        <v>513</v>
+        <v>534</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -4271,15 +4452,15 @@
         <v>13.384</v>
       </c>
       <c r="C47" s="123" t="s">
-        <v>494</v>
+        <v>515</v>
       </c>
       <c r="I47" s="118" t="s">
-        <v>514</v>
+        <v>535</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="121" t="s">
-        <v>515</v>
+        <v>536</v>
       </c>
       <c r="B49" s="121" t="s">
         <v>101</v>
@@ -4298,7 +4479,7 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="123" t="s">
-        <v>516</v>
+        <v>537</v>
       </c>
       <c r="B50" s="128">
         <v>169.7</v>
@@ -4310,12 +4491,12 @@
         <v>297.3</v>
       </c>
       <c r="I50" s="118" t="s">
-        <v>517</v>
+        <v>538</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="119" t="s">
-        <v>518</v>
+        <v>539</v>
       </c>
       <c r="B53" s="120"/>
       <c r="C53" s="120"/>
@@ -4347,7 +4528,7 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="123" t="s">
-        <v>519</v>
+        <v>540</v>
       </c>
       <c r="B55" s="130">
         <f>B50-$B$41</f>
@@ -4362,12 +4543,12 @@
         <v>282.64600000000002</v>
       </c>
       <c r="I55" s="118" t="s">
-        <v>520</v>
+        <v>541</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="123" t="s">
-        <v>521</v>
+        <v>542</v>
       </c>
       <c r="B56" s="130">
         <f>$B$42</f>
@@ -4382,12 +4563,12 @@
         <v>30.981000000000002</v>
       </c>
       <c r="I56" s="118" t="s">
-        <v>522</v>
+        <v>543</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="123" t="s">
-        <v>523</v>
+        <v>544</v>
       </c>
       <c r="B57" s="130">
         <f>$B$44</f>
@@ -4402,12 +4583,12 @@
         <v>0.45500000000000002</v>
       </c>
       <c r="I57" s="118" t="s">
-        <v>524</v>
+        <v>545</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="123" t="s">
-        <v>525</v>
+        <v>546</v>
       </c>
       <c r="B58" s="130">
         <f>$B$45</f>
@@ -4422,12 +4603,12 @@
         <v>1.4590000000000001</v>
       </c>
       <c r="I58" s="118" t="s">
-        <v>526</v>
+        <v>547</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="123" t="s">
-        <v>527</v>
+        <v>548</v>
       </c>
       <c r="B59" s="130">
         <f>B50*$B$31</f>
@@ -4442,12 +4623,12 @@
         <v>8.9190000000000005</v>
       </c>
       <c r="I59" s="118" t="s">
-        <v>528</v>
+        <v>549</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="123" t="s">
-        <v>529</v>
+        <v>550</v>
       </c>
       <c r="B60" s="130">
         <f>$B$27*$B$32</f>
@@ -4462,12 +4643,12 @@
         <v>1.60608</v>
       </c>
       <c r="I60" s="118" t="s">
-        <v>530</v>
+        <v>551</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="123" t="s">
-        <v>531</v>
+        <v>552</v>
       </c>
       <c r="B61" s="130">
         <f>$B$30</f>
@@ -4482,12 +4663,12 @@
         <v>8</v>
       </c>
       <c r="I61" s="118" t="s">
-        <v>532</v>
+        <v>553</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="131" t="s">
-        <v>533</v>
+        <v>554</v>
       </c>
       <c r="B62" s="132">
         <f>SUM(B55:B61)</f>
@@ -4504,7 +4685,7 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="123" t="s">
-        <v>534</v>
+        <v>555</v>
       </c>
       <c r="B63" s="130">
         <f>$B$27</f>
@@ -4519,12 +4700,12 @@
         <v>53.536000000000001</v>
       </c>
       <c r="I63" s="118" t="s">
-        <v>535</v>
+        <v>556</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="123" t="s">
-        <v>536</v>
+        <v>557</v>
       </c>
       <c r="B64" s="130">
         <f>$B$43</f>
@@ -4539,12 +4720,12 @@
         <v>16.327000000000002</v>
       </c>
       <c r="I64" s="118" t="s">
-        <v>537</v>
+        <v>558</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="123" t="s">
-        <v>538</v>
+        <v>559</v>
       </c>
       <c r="B65" s="130">
         <f>$B$34*$B$35*B55</f>
@@ -4559,12 +4740,12 @@
         <v>34.624134999999995</v>
       </c>
       <c r="I65" s="118" t="s">
-        <v>539</v>
+        <v>560</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="123" t="s">
-        <v>540</v>
+        <v>561</v>
       </c>
       <c r="B66" s="130">
         <f>B62-B63-B64-B65</f>
@@ -4581,7 +4762,7 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="131" t="s">
-        <v>541</v>
+        <v>562</v>
       </c>
       <c r="B67" s="132">
         <f>SUM(B63:B66)</f>
@@ -4598,7 +4779,7 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="131" t="s">
-        <v>542</v>
+        <v>563</v>
       </c>
       <c r="B68" s="133">
         <f>B67-B62</f>
@@ -4613,12 +4794,12 @@
         <v>0</v>
       </c>
       <c r="I68" s="118" t="s">
-        <v>543</v>
+        <v>564</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="119" t="s">
-        <v>544</v>
+        <v>565</v>
       </c>
       <c r="B70" s="119" t="s">
         <v>101</v>
@@ -4637,7 +4818,7 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="123" t="s">
-        <v>545</v>
+        <v>566</v>
       </c>
       <c r="B71" s="130">
         <f>$B$27-$B$30</f>
@@ -4646,19 +4827,19 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="123" t="s">
-        <v>546</v>
+        <v>567</v>
       </c>
       <c r="B72" s="134">
         <f>B71/$B$47</f>
         <v>3.4022713687985653</v>
       </c>
       <c r="I72" s="118" t="s">
-        <v>547</v>
+        <v>568</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="123" t="s">
-        <v>548</v>
+        <v>569</v>
       </c>
       <c r="B73" s="130">
         <f>B50-$B71</f>
@@ -4675,7 +4856,7 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="123" t="s">
-        <v>549</v>
+        <v>570</v>
       </c>
       <c r="B74" s="125">
         <f>B65/B73</f>
@@ -4690,12 +4871,12 @@
         <v>0.13752615544716479</v>
       </c>
       <c r="I74" s="118" t="s">
-        <v>550</v>
+        <v>571</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="123" t="s">
-        <v>551</v>
+        <v>572</v>
       </c>
       <c r="B75" s="125">
         <f>1-B74</f>
@@ -4712,7 +4893,7 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="119" t="s">
-        <v>552</v>
+        <v>573</v>
       </c>
       <c r="B80" s="120"/>
       <c r="C80" s="120"/>
@@ -4725,7 +4906,7 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="121" t="s">
-        <v>553</v>
+        <v>574</v>
       </c>
       <c r="B81" s="121"/>
       <c r="C81" s="121" t="s">
@@ -4748,7 +4929,7 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="123" t="s">
-        <v>554</v>
+        <v>575</v>
       </c>
       <c r="C82" s="127">
         <f>DCF!B7</f>
@@ -4773,7 +4954,7 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="123" t="s">
-        <v>555</v>
+        <v>576</v>
       </c>
       <c r="C83" s="127">
         <f>DCF!B12</f>
@@ -4798,7 +4979,7 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="123" t="s">
-        <v>556</v>
+        <v>577</v>
       </c>
       <c r="C84" s="127">
         <f>DCF!B13</f>
@@ -4823,7 +5004,7 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="123" t="s">
-        <v>557</v>
+        <v>578</v>
       </c>
       <c r="C85" s="127">
         <f>DCF!B14</f>
@@ -4848,7 +5029,7 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="123" t="s">
-        <v>558</v>
+        <v>579</v>
       </c>
       <c r="C86" s="127">
         <f>DCF!B19</f>
@@ -4873,7 +5054,7 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="123" t="s">
-        <v>559</v>
+        <v>580</v>
       </c>
       <c r="C87" s="127">
         <f>DCF!B20</f>
@@ -4898,7 +5079,7 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="121" t="s">
-        <v>560</v>
+        <v>581</v>
       </c>
       <c r="B88" s="122"/>
       <c r="C88" s="122"/>
@@ -4911,7 +5092,7 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="123" t="s">
-        <v>561</v>
+        <v>582</v>
       </c>
       <c r="C89" s="130">
         <f>$B$27</f>
@@ -4936,7 +5117,7 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="123" t="s">
-        <v>562</v>
+        <v>583</v>
       </c>
       <c r="C90" s="130">
         <f>C89*$B$25</f>
@@ -4961,7 +5142,7 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="123" t="s">
-        <v>563</v>
+        <v>584</v>
       </c>
       <c r="C91" s="130">
         <f>$B$33</f>
@@ -4986,7 +5167,7 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="123" t="s">
-        <v>564</v>
+        <v>585</v>
       </c>
       <c r="C92" s="130">
         <f>C90+C91</f>
@@ -5011,7 +5192,7 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="123" t="s">
-        <v>565</v>
+        <v>586</v>
       </c>
       <c r="C93" s="130">
         <f>MAX(3,0.3*C83)</f>
@@ -5036,7 +5217,7 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="123" t="s">
-        <v>566</v>
+        <v>587</v>
       </c>
       <c r="C94" s="130">
         <f>MIN(C92,C93)</f>
@@ -5061,7 +5242,7 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="123" t="s">
-        <v>567</v>
+        <v>588</v>
       </c>
       <c r="C95" s="130">
         <f>0+C92-C94</f>
@@ -5086,7 +5267,7 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="123" t="s">
-        <v>568</v>
+        <v>589</v>
       </c>
       <c r="C96" s="130">
         <f>C85-$B$40-C94</f>
@@ -5111,7 +5292,7 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="123" t="s">
-        <v>569</v>
+        <v>590</v>
       </c>
       <c r="C97" s="130">
         <f>MAX(0,$B$37*C96)</f>
@@ -5136,7 +5317,7 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="123" t="s">
-        <v>570</v>
+        <v>591</v>
       </c>
       <c r="C98" s="130">
         <f>$B$38*MAX(0,C97-$B$39)</f>
@@ -5161,7 +5342,7 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="123" t="s">
-        <v>571</v>
+        <v>592</v>
       </c>
       <c r="C99" s="130">
         <f>MAX(0,C97+C98)</f>
@@ -5186,7 +5367,7 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="131" t="s">
-        <v>572</v>
+        <v>593</v>
       </c>
       <c r="C100" s="132">
         <f>C85-C92-C99</f>
@@ -5211,7 +5392,7 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="123" t="s">
-        <v>573</v>
+        <v>594</v>
       </c>
       <c r="C101" s="130">
         <f>MIN($B$28*$B$27,C89)</f>
@@ -5236,7 +5417,7 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="123" t="s">
-        <v>574</v>
+        <v>595</v>
       </c>
       <c r="C102" s="130">
         <f>$B$30+C100+C84+C86+C87-C101</f>
@@ -5261,7 +5442,7 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="123" t="s">
-        <v>575</v>
+        <v>596</v>
       </c>
       <c r="C103" s="130">
         <f>MAX(0,C102-$B$30)</f>
@@ -5286,7 +5467,7 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="123" t="s">
-        <v>576</v>
+        <v>597</v>
       </c>
       <c r="C104" s="130">
         <f>MIN($B$29*C103,C89-C101)</f>
@@ -5311,7 +5492,7 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="131" t="s">
-        <v>577</v>
+        <v>598</v>
       </c>
       <c r="C105" s="132">
         <f>C89-C101-C104</f>
@@ -5336,7 +5517,7 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="131" t="s">
-        <v>578</v>
+        <v>599</v>
       </c>
       <c r="C106" s="132">
         <f>C102-C104</f>
@@ -5361,7 +5542,7 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="121" t="s">
-        <v>579</v>
+        <v>600</v>
       </c>
       <c r="B107" s="122"/>
       <c r="C107" s="122"/>
@@ -5374,7 +5555,7 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="123" t="s">
-        <v>580</v>
+        <v>601</v>
       </c>
       <c r="C108" s="130">
         <f>G83*$B$36</f>
@@ -5383,7 +5564,7 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="123" t="s">
-        <v>581</v>
+        <v>602</v>
       </c>
       <c r="C109" s="130">
         <f>C108-G105+G106</f>
@@ -5392,7 +5573,7 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="123" t="s">
-        <v>582</v>
+        <v>603</v>
       </c>
       <c r="C110" s="130">
         <f>C109*(1-B74)</f>
@@ -5401,7 +5582,7 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="123" t="s">
-        <v>583</v>
+        <v>604</v>
       </c>
       <c r="C111" s="130">
         <f>B66</f>
@@ -5410,19 +5591,19 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="131" t="s">
-        <v>584</v>
+        <v>605</v>
       </c>
       <c r="C112" s="135">
         <f>(C110/C111)^(1/5)-1</f>
         <v>0.22509032702462251</v>
       </c>
       <c r="I112" s="118" t="s">
-        <v>585</v>
+        <v>606</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="123" t="s">
-        <v>586</v>
+        <v>607</v>
       </c>
       <c r="C113" s="136">
         <f>C110/C111</f>
@@ -5431,7 +5612,7 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="119" t="s">
-        <v>587</v>
+        <v>608</v>
       </c>
       <c r="B118" s="120"/>
       <c r="C118" s="120"/>
@@ -5444,7 +5625,7 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="121" t="s">
-        <v>553</v>
+        <v>574</v>
       </c>
       <c r="B119" s="121"/>
       <c r="C119" s="121" t="s">
@@ -5467,7 +5648,7 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="123" t="s">
-        <v>554</v>
+        <v>575</v>
       </c>
       <c r="C120" s="127">
         <f>DCF!C7</f>
@@ -5492,7 +5673,7 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="123" t="s">
-        <v>555</v>
+        <v>576</v>
       </c>
       <c r="C121" s="127">
         <f>DCF!C12</f>
@@ -5517,7 +5698,7 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="123" t="s">
-        <v>556</v>
+        <v>577</v>
       </c>
       <c r="C122" s="127">
         <f>DCF!C13</f>
@@ -5542,7 +5723,7 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="123" t="s">
-        <v>557</v>
+        <v>578</v>
       </c>
       <c r="C123" s="127">
         <f>DCF!C14</f>
@@ -5567,7 +5748,7 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="123" t="s">
-        <v>558</v>
+        <v>579</v>
       </c>
       <c r="C124" s="127">
         <f>DCF!C19</f>
@@ -5592,7 +5773,7 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="123" t="s">
-        <v>559</v>
+        <v>580</v>
       </c>
       <c r="C125" s="127">
         <f>DCF!C20</f>
@@ -5617,7 +5798,7 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="121" t="s">
-        <v>560</v>
+        <v>581</v>
       </c>
       <c r="B126" s="122"/>
       <c r="C126" s="122"/>
@@ -5630,7 +5811,7 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="123" t="s">
-        <v>561</v>
+        <v>582</v>
       </c>
       <c r="C127" s="130">
         <f>$B$27</f>
@@ -5655,7 +5836,7 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="123" t="s">
-        <v>562</v>
+        <v>583</v>
       </c>
       <c r="C128" s="130">
         <f>C127*$B$25</f>
@@ -5680,7 +5861,7 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="123" t="s">
-        <v>563</v>
+        <v>584</v>
       </c>
       <c r="C129" s="130">
         <f>$B$33</f>
@@ -5705,7 +5886,7 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="123" t="s">
-        <v>564</v>
+        <v>585</v>
       </c>
       <c r="C130" s="130">
         <f>C128+C129</f>
@@ -5730,7 +5911,7 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="123" t="s">
-        <v>565</v>
+        <v>586</v>
       </c>
       <c r="C131" s="130">
         <f>MAX(3,0.3*C121)</f>
@@ -5755,7 +5936,7 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="123" t="s">
-        <v>566</v>
+        <v>587</v>
       </c>
       <c r="C132" s="130">
         <f>MIN(C130,C131)</f>
@@ -5780,7 +5961,7 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="123" t="s">
-        <v>567</v>
+        <v>588</v>
       </c>
       <c r="C133" s="130">
         <f>0+C130-C132</f>
@@ -5805,7 +5986,7 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="123" t="s">
-        <v>568</v>
+        <v>589</v>
       </c>
       <c r="C134" s="130">
         <f>C123-$B$40-C132</f>
@@ -5830,7 +6011,7 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="123" t="s">
-        <v>569</v>
+        <v>590</v>
       </c>
       <c r="C135" s="130">
         <f>MAX(0,$B$37*C134)</f>
@@ -5855,7 +6036,7 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="123" t="s">
-        <v>570</v>
+        <v>591</v>
       </c>
       <c r="C136" s="130">
         <f>$B$38*MAX(0,C135-$B$39)</f>
@@ -5880,7 +6061,7 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="123" t="s">
-        <v>571</v>
+        <v>592</v>
       </c>
       <c r="C137" s="130">
         <f>MAX(0,C135+C136)</f>
@@ -5905,7 +6086,7 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="131" t="s">
-        <v>572</v>
+        <v>593</v>
       </c>
       <c r="C138" s="132">
         <f>C123-C130-C137</f>
@@ -5930,7 +6111,7 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="123" t="s">
-        <v>573</v>
+        <v>594</v>
       </c>
       <c r="C139" s="130">
         <f>MIN($B$28*$B$27,C127)</f>
@@ -5955,7 +6136,7 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="123" t="s">
-        <v>574</v>
+        <v>595</v>
       </c>
       <c r="C140" s="130">
         <f>$B$30+C138+C122+C124+C125-C139</f>
@@ -5980,7 +6161,7 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="123" t="s">
-        <v>575</v>
+        <v>596</v>
       </c>
       <c r="C141" s="130">
         <f>MAX(0,C140-$B$30)</f>
@@ -6005,7 +6186,7 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="123" t="s">
-        <v>576</v>
+        <v>597</v>
       </c>
       <c r="C142" s="130">
         <f>MIN($B$29*C141,C127-C139)</f>
@@ -6030,7 +6211,7 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="131" t="s">
-        <v>577</v>
+        <v>598</v>
       </c>
       <c r="C143" s="132">
         <f>C127-C139-C142</f>
@@ -6055,7 +6236,7 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="131" t="s">
-        <v>578</v>
+        <v>599</v>
       </c>
       <c r="C144" s="132">
         <f>C140-C142</f>
@@ -6080,7 +6261,7 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="121" t="s">
-        <v>579</v>
+        <v>600</v>
       </c>
       <c r="B145" s="122"/>
       <c r="C145" s="122"/>
@@ -6093,7 +6274,7 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="123" t="s">
-        <v>580</v>
+        <v>601</v>
       </c>
       <c r="C146" s="130">
         <f>G121*$B$36</f>
@@ -6102,7 +6283,7 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="123" t="s">
-        <v>581</v>
+        <v>602</v>
       </c>
       <c r="C147" s="130">
         <f>C146-G143+G144</f>
@@ -6111,7 +6292,7 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="123" t="s">
-        <v>582</v>
+        <v>603</v>
       </c>
       <c r="C148" s="130">
         <f>C147*(1-C74)</f>
@@ -6120,7 +6301,7 @@
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="123" t="s">
-        <v>583</v>
+        <v>604</v>
       </c>
       <c r="C149" s="130">
         <f>C66</f>
@@ -6129,19 +6310,19 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="131" t="s">
-        <v>584</v>
+        <v>605</v>
       </c>
       <c r="C150" s="135">
         <f>(C148/C149)^(1/5)-1</f>
         <v>0.22503769786231054</v>
       </c>
       <c r="I150" s="118" t="s">
-        <v>585</v>
+        <v>606</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="123" t="s">
-        <v>586</v>
+        <v>607</v>
       </c>
       <c r="C151" s="136">
         <f>C148/C149</f>
@@ -6150,7 +6331,7 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="119" t="s">
-        <v>588</v>
+        <v>609</v>
       </c>
       <c r="B156" s="120"/>
       <c r="C156" s="120"/>
@@ -6163,7 +6344,7 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="121" t="s">
-        <v>553</v>
+        <v>574</v>
       </c>
       <c r="B157" s="121"/>
       <c r="C157" s="121" t="s">
@@ -6186,7 +6367,7 @@
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="123" t="s">
-        <v>554</v>
+        <v>575</v>
       </c>
       <c r="C158" s="127">
         <f>DCF!D7</f>
@@ -6211,7 +6392,7 @@
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="123" t="s">
-        <v>555</v>
+        <v>576</v>
       </c>
       <c r="C159" s="127">
         <f>DCF!D12</f>
@@ -6236,7 +6417,7 @@
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="123" t="s">
-        <v>556</v>
+        <v>577</v>
       </c>
       <c r="C160" s="127">
         <f>DCF!D13</f>
@@ -6261,7 +6442,7 @@
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="123" t="s">
-        <v>557</v>
+        <v>578</v>
       </c>
       <c r="C161" s="127">
         <f>DCF!D14</f>
@@ -6286,7 +6467,7 @@
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="123" t="s">
-        <v>558</v>
+        <v>579</v>
       </c>
       <c r="C162" s="127">
         <f>DCF!D19</f>
@@ -6311,7 +6492,7 @@
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="123" t="s">
-        <v>559</v>
+        <v>580</v>
       </c>
       <c r="C163" s="127">
         <f>DCF!D20</f>
@@ -6336,7 +6517,7 @@
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="121" t="s">
-        <v>560</v>
+        <v>581</v>
       </c>
       <c r="B164" s="122"/>
       <c r="C164" s="122"/>
@@ -6349,7 +6530,7 @@
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="123" t="s">
-        <v>561</v>
+        <v>582</v>
       </c>
       <c r="C165" s="130">
         <f>$B$27</f>
@@ -6374,7 +6555,7 @@
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="123" t="s">
-        <v>562</v>
+        <v>583</v>
       </c>
       <c r="C166" s="130">
         <f>C165*$B$25</f>
@@ -6399,7 +6580,7 @@
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="123" t="s">
-        <v>563</v>
+        <v>584</v>
       </c>
       <c r="C167" s="130">
         <f>$B$33</f>
@@ -6424,7 +6605,7 @@
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="123" t="s">
-        <v>564</v>
+        <v>585</v>
       </c>
       <c r="C168" s="130">
         <f>C166+C167</f>
@@ -6449,7 +6630,7 @@
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="123" t="s">
-        <v>565</v>
+        <v>586</v>
       </c>
       <c r="C169" s="130">
         <f>MAX(3,0.3*C159)</f>
@@ -6474,7 +6655,7 @@
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="123" t="s">
-        <v>566</v>
+        <v>587</v>
       </c>
       <c r="C170" s="130">
         <f>MIN(C168,C169)</f>
@@ -6499,7 +6680,7 @@
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="123" t="s">
-        <v>567</v>
+        <v>588</v>
       </c>
       <c r="C171" s="130">
         <f>0+C168-C170</f>
@@ -6524,7 +6705,7 @@
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="123" t="s">
-        <v>568</v>
+        <v>589</v>
       </c>
       <c r="C172" s="130">
         <f>C161-$B$40-C170</f>
@@ -6549,7 +6730,7 @@
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="123" t="s">
-        <v>569</v>
+        <v>590</v>
       </c>
       <c r="C173" s="130">
         <f>MAX(0,$B$37*C172)</f>
@@ -6574,7 +6755,7 @@
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="123" t="s">
-        <v>570</v>
+        <v>591</v>
       </c>
       <c r="C174" s="130">
         <f>$B$38*MAX(0,C173-$B$39)</f>
@@ -6599,7 +6780,7 @@
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="123" t="s">
-        <v>571</v>
+        <v>592</v>
       </c>
       <c r="C175" s="130">
         <f>MAX(0,C173+C174)</f>
@@ -6624,7 +6805,7 @@
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="131" t="s">
-        <v>572</v>
+        <v>593</v>
       </c>
       <c r="C176" s="132">
         <f>C161-C168-C175</f>
@@ -6649,7 +6830,7 @@
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="123" t="s">
-        <v>573</v>
+        <v>594</v>
       </c>
       <c r="C177" s="130">
         <f>MIN($B$28*$B$27,C165)</f>
@@ -6674,7 +6855,7 @@
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="123" t="s">
-        <v>574</v>
+        <v>595</v>
       </c>
       <c r="C178" s="130">
         <f>$B$30+C176+C160+C162+C163-C177</f>
@@ -6699,7 +6880,7 @@
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="123" t="s">
-        <v>575</v>
+        <v>596</v>
       </c>
       <c r="C179" s="130">
         <f>MAX(0,C178-$B$30)</f>
@@ -6724,7 +6905,7 @@
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="123" t="s">
-        <v>576</v>
+        <v>597</v>
       </c>
       <c r="C180" s="130">
         <f>MIN($B$29*C179,C165-C177)</f>
@@ -6749,7 +6930,7 @@
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="131" t="s">
-        <v>577</v>
+        <v>598</v>
       </c>
       <c r="C181" s="132">
         <f>C165-C177-C180</f>
@@ -6774,7 +6955,7 @@
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="131" t="s">
-        <v>578</v>
+        <v>599</v>
       </c>
       <c r="C182" s="132">
         <f>C178-C180</f>
@@ -6799,7 +6980,7 @@
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="121" t="s">
-        <v>579</v>
+        <v>600</v>
       </c>
       <c r="B183" s="122"/>
       <c r="C183" s="122"/>
@@ -6812,7 +6993,7 @@
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" s="123" t="s">
-        <v>580</v>
+        <v>601</v>
       </c>
       <c r="C184" s="130">
         <f>G159*$B$36</f>
@@ -6821,7 +7002,7 @@
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="123" t="s">
-        <v>581</v>
+        <v>602</v>
       </c>
       <c r="C185" s="130">
         <f>C184-G181+G182</f>
@@ -6830,7 +7011,7 @@
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="123" t="s">
-        <v>582</v>
+        <v>603</v>
       </c>
       <c r="C186" s="130">
         <f>C185*(1-D74)</f>
@@ -6839,7 +7020,7 @@
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="123" t="s">
-        <v>583</v>
+        <v>604</v>
       </c>
       <c r="C187" s="130">
         <f>D66</f>
@@ -6848,19 +7029,19 @@
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="131" t="s">
-        <v>584</v>
+        <v>605</v>
       </c>
       <c r="C188" s="135">
         <f>(C186/C187)^(1/5)-1</f>
         <v>0.22495363264703361</v>
       </c>
       <c r="I188" s="118" t="s">
-        <v>585</v>
+        <v>606</v>
       </c>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" s="123" t="s">
-        <v>586</v>
+        <v>607</v>
       </c>
       <c r="C189" s="136">
         <f>C186/C187</f>
@@ -6869,7 +7050,7 @@
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" s="119" t="s">
-        <v>589</v>
+        <v>610</v>
       </c>
       <c r="B196" s="120"/>
       <c r="C196" s="120"/>
@@ -6882,23 +7063,23 @@
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" s="121" t="s">
-        <v>590</v>
+        <v>611</v>
       </c>
       <c r="B197" s="121" t="s">
-        <v>452</v>
+        <v>473</v>
       </c>
       <c r="C197" s="121" t="s">
-        <v>453</v>
+        <v>474</v>
       </c>
       <c r="D197" s="121" t="s">
-        <v>454</v>
+        <v>475</v>
       </c>
       <c r="E197" s="122"/>
       <c r="F197" s="122"/>
       <c r="G197" s="122"/>
       <c r="H197" s="122"/>
       <c r="I197" s="118" t="s">
-        <v>591</v>
+        <v>612</v>
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
@@ -6945,7 +7126,7 @@
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" s="119" t="s">
-        <v>592</v>
+        <v>613</v>
       </c>
       <c r="B203" s="120"/>
       <c r="C203" s="120"/>
@@ -6958,7 +7139,7 @@
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" s="121" t="s">
-        <v>593</v>
+        <v>614</v>
       </c>
       <c r="B204" s="122"/>
       <c r="C204" s="122"/>
@@ -6971,22 +7152,22 @@
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" s="121" t="s">
-        <v>594</v>
+        <v>615</v>
       </c>
       <c r="B205" s="121" t="s">
-        <v>595</v>
+        <v>616</v>
       </c>
       <c r="C205" s="121" t="s">
-        <v>596</v>
+        <v>617</v>
       </c>
       <c r="D205" s="121" t="s">
-        <v>597</v>
+        <v>618</v>
       </c>
       <c r="E205" s="121" t="s">
-        <v>598</v>
+        <v>619</v>
       </c>
       <c r="F205" s="121" t="s">
-        <v>599</v>
+        <v>620</v>
       </c>
       <c r="G205" s="122"/>
       <c r="H205" s="122"/>
@@ -7012,7 +7193,7 @@
         <v>0.27110156747905417</v>
       </c>
       <c r="I206" s="118" t="s">
-        <v>600</v>
+        <v>621</v>
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
@@ -7097,7 +7278,7 @@
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="121" t="s">
-        <v>601</v>
+        <v>622</v>
       </c>
       <c r="B212" s="122"/>
       <c r="C212" s="122"/>
@@ -7110,22 +7291,22 @@
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="121" t="s">
-        <v>602</v>
+        <v>623</v>
       </c>
       <c r="B213" s="121" t="s">
-        <v>595</v>
+        <v>616</v>
       </c>
       <c r="C213" s="121" t="s">
-        <v>596</v>
+        <v>617</v>
       </c>
       <c r="D213" s="121" t="s">
-        <v>597</v>
+        <v>618</v>
       </c>
       <c r="E213" s="121" t="s">
-        <v>598</v>
+        <v>619</v>
       </c>
       <c r="F213" s="121" t="s">
-        <v>599</v>
+        <v>620</v>
       </c>
       <c r="G213" s="122"/>
       <c r="H213" s="122"/>
@@ -7133,7 +7314,7 @@
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="123" t="s">
-        <v>603</v>
+        <v>624</v>
       </c>
       <c r="B214" s="137">
         <v>0.1145288791638157</v>
@@ -7151,12 +7332,12 @@
         <v>0.21223737156791561</v>
       </c>
       <c r="I214" s="118" t="s">
-        <v>604</v>
+        <v>625</v>
       </c>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="123" t="s">
-        <v>605</v>
+        <v>626</v>
       </c>
       <c r="B215" s="137">
         <v>0.1158470645624543</v>
@@ -7176,7 +7357,7 @@
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="123" t="s">
-        <v>606</v>
+        <v>627</v>
       </c>
       <c r="B216" s="137">
         <v>0.11711132812578651</v>
@@ -7196,7 +7377,7 @@
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="123" t="s">
-        <v>607</v>
+        <v>628</v>
       </c>
       <c r="B217" s="137">
         <v>0.1183258062810979</v>
@@ -7216,7 +7397,7 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="123" t="s">
-        <v>608</v>
+        <v>629</v>
       </c>
       <c r="B218" s="137">
         <v>0.1195898410241119</v>
@@ -7236,7 +7417,7 @@
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="119" t="s">
-        <v>609</v>
+        <v>630</v>
       </c>
       <c r="B220" s="120"/>
       <c r="C220" s="120"/>
@@ -7249,16 +7430,16 @@
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="121" t="s">
-        <v>610</v>
+        <v>631</v>
       </c>
       <c r="B221" s="121" t="s">
-        <v>611</v>
+        <v>632</v>
       </c>
       <c r="C221" s="121" t="s">
-        <v>612</v>
+        <v>633</v>
       </c>
       <c r="D221" s="121" t="s">
-        <v>613</v>
+        <v>634</v>
       </c>
       <c r="E221" s="122"/>
       <c r="F221" s="122"/>
@@ -7268,7 +7449,7 @@
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="123" t="s">
-        <v>614</v>
+        <v>635</v>
       </c>
       <c r="B222" s="137">
         <f>C112</f>
@@ -7282,12 +7463,12 @@
         <v>3.2702462249289965E-7</v>
       </c>
       <c r="I222" s="118" t="s">
-        <v>615</v>
+        <v>636</v>
       </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="123" t="s">
-        <v>616</v>
+        <v>637</v>
       </c>
       <c r="B223" s="137">
         <f>C150</f>
@@ -7303,7 +7484,7 @@
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="123" t="s">
-        <v>617</v>
+        <v>638</v>
       </c>
       <c r="B224" s="137">
         <f>C188</f>
@@ -7319,7 +7500,7 @@
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="123" t="s">
-        <v>618</v>
+        <v>639</v>
       </c>
       <c r="B225" s="130">
         <f>G143</f>
@@ -7335,7 +7516,7 @@
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="123" t="s">
-        <v>619</v>
+        <v>640</v>
       </c>
       <c r="B226" s="130">
         <f>G144</f>
@@ -7351,7 +7532,7 @@
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" s="123" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="B227" s="130">
         <f>C149</f>
@@ -7367,7 +7548,7 @@
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" s="119" t="s">
-        <v>621</v>
+        <v>642</v>
       </c>
       <c r="B230" s="120"/>
       <c r="C230" s="120"/>
@@ -7380,52 +7561,52 @@
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" s="144" t="s">
-        <v>622</v>
+        <v>643</v>
       </c>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" s="118" t="s">
-        <v>623</v>
+        <v>644</v>
       </c>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" s="118" t="s">
-        <v>624</v>
+        <v>645</v>
       </c>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" s="118" t="s">
-        <v>625</v>
+        <v>646</v>
       </c>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" s="118" t="s">
-        <v>626</v>
+        <v>647</v>
       </c>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" s="118" t="s">
-        <v>627</v>
+        <v>648</v>
       </c>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" s="118" t="s">
-        <v>628</v>
+        <v>649</v>
       </c>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" s="118" t="s">
-        <v>629</v>
+        <v>650</v>
       </c>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" s="118" t="s">
-        <v>630</v>
+        <v>651</v>
       </c>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" s="119" t="s">
-        <v>631</v>
+        <v>652</v>
       </c>
       <c r="B242" s="120"/>
       <c r="C242" s="120"/>
@@ -7438,57 +7619,57 @@
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" s="118" t="s">
-        <v>632</v>
+        <v>653</v>
       </c>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" s="118" t="s">
-        <v>633</v>
+        <v>654</v>
       </c>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" s="118" t="s">
-        <v>634</v>
+        <v>655</v>
       </c>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" s="118" t="s">
-        <v>635</v>
+        <v>656</v>
       </c>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" s="118" t="s">
-        <v>636</v>
+        <v>657</v>
       </c>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" s="118" t="s">
-        <v>637</v>
+        <v>658</v>
       </c>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" s="118" t="s">
-        <v>638</v>
+        <v>659</v>
       </c>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" s="118" t="s">
-        <v>639</v>
+        <v>660</v>
       </c>
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" s="118" t="s">
-        <v>640</v>
+        <v>661</v>
       </c>
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" s="118" t="s">
-        <v>641</v>
+        <v>662</v>
       </c>
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" s="118" t="s">
-        <v>642</v>
+        <v>663</v>
       </c>
     </row>
   </sheetData>
@@ -7507,44 +7688,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="153" t="s">
-        <v>643</v>
-      </c>
-      <c r="B1" s="146"/>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
-      <c r="E1" s="146"/>
-      <c r="F1" s="146"/>
-      <c r="G1" s="146"/>
+      <c r="A1" s="163" t="s">
+        <v>664</v>
+      </c>
+      <c r="B1" s="156"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
+      <c r="F1" s="156"/>
+      <c r="G1" s="156"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>644</v>
+        <v>665</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
-        <v>645</v>
+        <v>666</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>646</v>
+        <v>667</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>647</v>
+        <v>668</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>648</v>
+        <v>669</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>649</v>
+        <v>670</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>650</v>
+        <v>671</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="84" t="s">
-        <v>651</v>
+        <v>672</v>
       </c>
       <c r="B5" s="85">
         <f>DCF!Q34</f>
@@ -7567,7 +7748,7 @@
         <v>4.9041703491122766</v>
       </c>
       <c r="G5" s="87" t="s">
-        <v>652</v>
+        <v>673</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -7595,12 +7776,12 @@
         <v>5.8779471147583697</v>
       </c>
       <c r="G6" s="91" t="s">
-        <v>653</v>
+        <v>674</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="47" t="s">
-        <v>654</v>
+        <v>675</v>
       </c>
       <c r="B7" s="92">
         <f>Transaction_comps!E27</f>
@@ -7623,7 +7804,7 @@
         <v>6.6920672137553732</v>
       </c>
       <c r="G7" s="94" t="s">
-        <v>655</v>
+        <v>676</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -7651,7 +7832,7 @@
         <v>3.938713038947506</v>
       </c>
       <c r="G8" s="96" t="s">
-        <v>656</v>
+        <v>677</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -7664,19 +7845,19 @@
       <c r="G9" s="97"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="156" t="s">
-        <v>657</v>
-      </c>
-      <c r="B10" s="146"/>
-      <c r="C10" s="146"/>
-      <c r="D10" s="146"/>
-      <c r="E10" s="146"/>
-      <c r="F10" s="146"/>
-      <c r="G10" s="146"/>
+      <c r="A10" s="166" t="s">
+        <v>678</v>
+      </c>
+      <c r="B10" s="156"/>
+      <c r="C10" s="156"/>
+      <c r="D10" s="156"/>
+      <c r="E10" s="156"/>
+      <c r="F10" s="156"/>
+      <c r="G10" s="156"/>
     </row>
     <row r="11" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>658</v>
+        <v>679</v>
       </c>
       <c r="C11" s="98">
         <f>DCF!R34</f>
@@ -7685,7 +7866,7 @@
     </row>
     <row r="12" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>659</v>
+        <v>680</v>
       </c>
       <c r="C12" s="98">
         <f>Transaction_comps!F27</f>
@@ -7694,14 +7875,14 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>660</v>
+        <v>681</v>
       </c>
       <c r="B13" s="72">
         <f>DCF!Q34</f>
         <v>157.92188754137794</v>
       </c>
       <c r="C13" s="61" t="s">
-        <v>661</v>
+        <v>682</v>
       </c>
       <c r="D13" s="72">
         <f>Trading_comps!G26</f>
@@ -7710,12 +7891,12 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="99" t="s">
-        <v>662</v>
+        <v>683</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="100" t="s">
-        <v>663</v>
+        <v>684</v>
       </c>
       <c r="B16" s="101" t="str">
         <f>REPT("░",ROUND(B5/600*48,0))&amp;REPT("█",MAX(1,ROUND((D5-B5)/600*48,0)))&amp;REPT("░",MAX(0,48-ROUND(B5/600*48,0)-MAX(1,ROUND((D5-B5)/600*48,0))))</f>
@@ -7728,7 +7909,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="100" t="s">
-        <v>664</v>
+        <v>685</v>
       </c>
       <c r="B17" s="101" t="str">
         <f>REPT("░",ROUND(B6/600*48,0))&amp;REPT("█",MAX(1,ROUND((D6-B6)/600*48,0)))&amp;REPT("░",MAX(0,48-ROUND(B6/600*48,0)-MAX(1,ROUND((D6-B6)/600*48,0))))</f>
@@ -7741,7 +7922,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="100" t="s">
-        <v>665</v>
+        <v>686</v>
       </c>
       <c r="B18" s="101" t="str">
         <f>REPT("░",ROUND(B7/600*48,0))&amp;REPT("█",MAX(1,ROUND((D7-B7)/600*48,0)))&amp;REPT("░",MAX(0,48-ROUND(B7/600*48,0)-MAX(1,ROUND((D7-B7)/600*48,0))))</f>
@@ -7754,7 +7935,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="100" t="s">
-        <v>666</v>
+        <v>687</v>
       </c>
       <c r="B19" s="101" t="str">
         <f>REPT("░",ROUND(B8/600*48,0))&amp;REPT("█",MAX(1,ROUND((D8-B8)/600*48,0)))&amp;REPT("░",MAX(0,48-ROUND(B8/600*48,0)-MAX(1,ROUND((D8-B8)/600*48,0))))</f>
@@ -7767,7 +7948,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B20" s="103" t="s">
-        <v>667</v>
+        <v>688</v>
       </c>
     </row>
   </sheetData>
@@ -7791,17 +7972,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="153" t="s">
-        <v>668</v>
-      </c>
-      <c r="B1" s="146"/>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
-      <c r="E1" s="146"/>
+      <c r="A1" s="163" t="s">
+        <v>689</v>
+      </c>
+      <c r="B1" s="156"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>669</v>
+        <v>690</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7819,16 +8000,16 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="145" t="s">
-        <v>670</v>
-      </c>
-      <c r="B5" s="146"/>
-      <c r="C5" s="146"/>
-      <c r="D5" s="146"/>
+      <c r="A5" s="155" t="s">
+        <v>691</v>
+      </c>
+      <c r="B5" s="156"/>
+      <c r="C5" s="156"/>
+      <c r="D5" s="156"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>341</v>
+        <v>362</v>
       </c>
       <c r="B6" s="52">
         <f>DCF!Q34</f>
@@ -7844,16 +8025,16 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="145" t="s">
-        <v>671</v>
-      </c>
-      <c r="B8" s="146"/>
-      <c r="C8" s="146"/>
-      <c r="D8" s="146"/>
+      <c r="A8" s="155" t="s">
+        <v>692</v>
+      </c>
+      <c r="B8" s="156"/>
+      <c r="C8" s="156"/>
+      <c r="D8" s="156"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>672</v>
+        <v>693</v>
       </c>
       <c r="B9" s="72">
         <f>FY25_base!B46</f>
@@ -7868,12 +8049,12 @@
         <v>30.981000000000002</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>673</v>
+        <v>694</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>229</v>
+        <v>250</v>
       </c>
       <c r="B10" s="72">
         <f>FY25_base!B47</f>
@@ -7888,12 +8069,12 @@
         <v>-5.4020000000000001</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>674</v>
+        <v>695</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="B11" s="72">
         <f>FY25_base!B48</f>
@@ -7908,12 +8089,12 @@
         <v>-10.925000000000001</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>675</v>
+        <v>696</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="B12" s="104">
         <f>FY25_base!B49</f>
@@ -7928,20 +8109,20 @@
         <v>14.654</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>676</v>
+        <v>697</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="145" t="s">
-        <v>677</v>
-      </c>
-      <c r="B14" s="146"/>
-      <c r="C14" s="146"/>
-      <c r="D14" s="146"/>
+      <c r="A14" s="155" t="s">
+        <v>698</v>
+      </c>
+      <c r="B14" s="156"/>
+      <c r="C14" s="156"/>
+      <c r="D14" s="156"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>678</v>
+        <v>699</v>
       </c>
       <c r="B15" s="51">
         <f>B6-B12</f>
@@ -7957,16 +8138,16 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="145" t="s">
-        <v>679</v>
-      </c>
-      <c r="B17" s="146"/>
-      <c r="C17" s="146"/>
-      <c r="D17" s="146"/>
+      <c r="A17" s="155" t="s">
+        <v>700</v>
+      </c>
+      <c r="B17" s="156"/>
+      <c r="C17" s="156"/>
+      <c r="D17" s="156"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>680</v>
+        <v>701</v>
       </c>
       <c r="B18" s="105">
         <f>FY25_base!B69</f>
@@ -7981,12 +8162,12 @@
         <v>1536790</v>
       </c>
       <c r="E18" s="28" t="s">
-        <v>681</v>
+        <v>702</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>682</v>
+        <v>703</v>
       </c>
       <c r="B19" s="106">
         <f>B18/1000000</f>
@@ -8003,7 +8184,7 @@
     </row>
     <row r="20" spans="1:5" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>683</v>
+        <v>704</v>
       </c>
       <c r="B20" s="107">
         <f>B15/B19</f>
@@ -8019,16 +8200,16 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="145" t="s">
-        <v>684</v>
-      </c>
-      <c r="B22" s="146"/>
-      <c r="C22" s="146"/>
-      <c r="D22" s="146"/>
+      <c r="A22" s="155" t="s">
+        <v>705</v>
+      </c>
+      <c r="B22" s="156"/>
+      <c r="C22" s="156"/>
+      <c r="D22" s="156"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>685</v>
+        <v>706</v>
       </c>
       <c r="C23" s="52">
         <f>Transaction_comps!F27</f>
@@ -8037,7 +8218,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
-        <v>686</v>
+        <v>707</v>
       </c>
       <c r="C24" s="51">
         <f>C23-C12</f>
@@ -8046,28 +8227,28 @@
     </row>
     <row r="25" spans="1:5" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>687</v>
+        <v>708</v>
       </c>
       <c r="C25" s="107">
         <f>C24/C19</f>
         <v>257.90511390625915</v>
       </c>
       <c r="E25" s="28" t="s">
-        <v>688</v>
+        <v>709</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="157" t="s">
-        <v>689</v>
-      </c>
-      <c r="B27" s="146"/>
-      <c r="C27" s="146"/>
-      <c r="D27" s="146"/>
-      <c r="E27" s="146"/>
+      <c r="A27" s="167" t="s">
+        <v>710</v>
+      </c>
+      <c r="B27" s="156"/>
+      <c r="C27" s="156"/>
+      <c r="D27" s="156"/>
+      <c r="E27" s="156"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>690</v>
+        <v>711</v>
       </c>
       <c r="C28" s="108">
         <f>C6</f>
@@ -8076,7 +8257,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>691</v>
+        <v>712</v>
       </c>
       <c r="C29" s="108">
         <f>C12</f>
@@ -8085,7 +8266,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>692</v>
+        <v>713</v>
       </c>
       <c r="C30" s="108">
         <f>C15</f>
@@ -8094,7 +8275,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>693</v>
+        <v>714</v>
       </c>
       <c r="C31" s="109">
         <f>C19</f>
@@ -8103,7 +8284,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>694</v>
+        <v>715</v>
       </c>
       <c r="C32" s="110">
         <f>C20</f>
@@ -8137,137 +8318,137 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="153" t="s">
-        <v>695</v>
-      </c>
-      <c r="B1" s="146"/>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
+      <c r="A1" s="163" t="s">
+        <v>716</v>
+      </c>
+      <c r="B1" s="156"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>696</v>
+        <v>717</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>697</v>
+        <v>718</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>698</v>
+        <v>719</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>699</v>
+        <v>720</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="111" t="s">
-        <v>700</v>
+        <v>721</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>701</v>
+        <v>722</v>
       </c>
       <c r="C4" s="112" t="s">
-        <v>702</v>
+        <v>723</v>
       </c>
       <c r="D4" s="113" t="s">
-        <v>703</v>
+        <v>724</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="114" t="s">
-        <v>704</v>
+        <v>725</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>705</v>
+        <v>726</v>
       </c>
       <c r="C5" s="115" t="s">
-        <v>706</v>
+        <v>727</v>
       </c>
       <c r="D5" s="116" t="s">
-        <v>707</v>
+        <v>728</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="111" t="s">
-        <v>708</v>
+        <v>729</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>709</v>
+        <v>730</v>
       </c>
       <c r="C6" s="112" t="s">
-        <v>710</v>
+        <v>731</v>
       </c>
       <c r="D6" s="113" t="s">
-        <v>711</v>
+        <v>732</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="114" t="s">
-        <v>712</v>
+        <v>733</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>713</v>
+        <v>734</v>
       </c>
       <c r="C7" s="115" t="s">
-        <v>714</v>
+        <v>735</v>
       </c>
       <c r="D7" s="116" t="s">
-        <v>715</v>
+        <v>736</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="111" t="s">
-        <v>716</v>
+        <v>737</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>717</v>
+        <v>738</v>
       </c>
       <c r="C8" s="112" t="s">
-        <v>718</v>
+        <v>739</v>
       </c>
       <c r="D8" s="113" t="s">
-        <v>719</v>
+        <v>740</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="114" t="s">
-        <v>720</v>
+        <v>741</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>721</v>
+        <v>742</v>
       </c>
       <c r="C9" s="115" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="D9" s="116" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="111" t="s">
-        <v>724</v>
+        <v>745</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>725</v>
+        <v>746</v>
       </c>
       <c r="C10" s="112" t="s">
-        <v>726</v>
+        <v>747</v>
       </c>
       <c r="D10" s="113" t="s">
-        <v>727</v>
+        <v>748</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="114" t="s">
-        <v>728</v>
+        <v>749</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>729</v>
+        <v>750</v>
       </c>
       <c r="C11" s="115" t="s">
-        <v>730</v>
+        <v>751</v>
       </c>
       <c r="D11" s="116" t="s">
-        <v>731</v>
+        <v>752</v>
       </c>
     </row>
   </sheetData>
@@ -8279,9 +8460,282 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="62" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A1" s="151" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="152" t="s">
+        <v>754</v>
+      </c>
+      <c r="B3" s="152" t="s">
+        <v>755</v>
+      </c>
+      <c r="C3" s="152" t="s">
+        <v>756</v>
+      </c>
+      <c r="D3" s="152" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>758</v>
+      </c>
+      <c r="B4" s="153">
+        <f>Inputs!C6-61.416</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="153">
+        <v>1E-3</v>
+      </c>
+      <c r="D4" s="145" t="str">
+        <f t="shared" ref="D4:D17" si="0">IF(ABS(B4)&lt;=C4,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>759</v>
+      </c>
+      <c r="B5" s="153">
+        <f>Inputs!C7-13.384</f>
+        <v>0</v>
+      </c>
+      <c r="C5" s="153">
+        <v>1E-3</v>
+      </c>
+      <c r="D5" s="145" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>760</v>
+      </c>
+      <c r="B6" s="153">
+        <f>LBO_full!B68</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="153">
+        <v>1E-3</v>
+      </c>
+      <c r="D6" s="145" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>761</v>
+      </c>
+      <c r="B7" s="153">
+        <f>LBO_full!C68</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="153">
+        <v>1E-3</v>
+      </c>
+      <c r="D7" s="145" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>762</v>
+      </c>
+      <c r="B8" s="153">
+        <f>LBO_full!D68</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="153">
+        <v>1E-3</v>
+      </c>
+      <c r="D8" s="145" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>763</v>
+      </c>
+      <c r="B9" s="153">
+        <f>LBO_full!B11-0.225</f>
+        <v>9.0327024622499641E-5</v>
+      </c>
+      <c r="C9" s="153">
+        <v>1E-3</v>
+      </c>
+      <c r="D9" s="145" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>764</v>
+      </c>
+      <c r="B10" s="153">
+        <f>LBO_full!C11-0.225</f>
+        <v>3.7697862310531738E-5</v>
+      </c>
+      <c r="C10" s="153">
+        <v>1E-3</v>
+      </c>
+      <c r="D10" s="145" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>765</v>
+      </c>
+      <c r="B11" s="153">
+        <f>LBO_full!D11-0.225</f>
+        <v>-4.6367352966397712E-5</v>
+      </c>
+      <c r="C11" s="153">
+        <v>1E-3</v>
+      </c>
+      <c r="D11" s="145" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>766</v>
+      </c>
+      <c r="B12" s="153">
+        <f>LBO_full!D223</f>
+        <v>-3.0213768945075437E-7</v>
+      </c>
+      <c r="C12" s="153">
+        <v>1E-4</v>
+      </c>
+      <c r="D12" s="145" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>767</v>
+      </c>
+      <c r="B13" s="153">
+        <f>LBO_full!D227</f>
+        <v>0</v>
+      </c>
+      <c r="C13" s="153">
+        <v>0.01</v>
+      </c>
+      <c r="D13" s="145" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>768</v>
+      </c>
+      <c r="B14" s="153">
+        <f>Trading_comps!F26-ROUND(AVERAGE(Trading_comps!F22,Trading_comps!F24),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C14" s="153">
+        <v>1E-3</v>
+      </c>
+      <c r="D14" s="145" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>769</v>
+      </c>
+      <c r="B15" s="153">
+        <f>Transaction_comps!F27-ROUND(Transaction_comps!F25,0)</f>
+        <v>0</v>
+      </c>
+      <c r="C15" s="153">
+        <v>1E-3</v>
+      </c>
+      <c r="D15" s="145" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>770</v>
+      </c>
+      <c r="B16" s="153">
+        <f>Inputs!C56</f>
+        <v>1.7587000000000158E-3</v>
+      </c>
+      <c r="C16" s="153">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="D16" s="145" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>771</v>
+      </c>
+      <c r="B17" s="153">
+        <f>Football_field!C8-LBO_full!C199</f>
+        <v>0</v>
+      </c>
+      <c r="C17" s="153">
+        <v>1E-3</v>
+      </c>
+      <c r="D17" s="145" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="145" t="s">
+        <v>772</v>
+      </c>
+      <c r="D18" s="154" t="str">
+        <f>IF(COUNTIF(D4:D17,"FAIL")=0,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="147" t="s">
+        <v>773</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -8290,13 +8744,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="153" t="s">
+      <c r="A1" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="146"/>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
-      <c r="E1" s="146"/>
+      <c r="B1" s="156"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
@@ -8321,13 +8775,13 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="145" t="s">
+      <c r="A5" s="155" t="s">
         <v>105</v>
       </c>
-      <c r="B5" s="146"/>
-      <c r="C5" s="146"/>
-      <c r="D5" s="146"/>
-      <c r="E5" s="146"/>
+      <c r="B5" s="156"/>
+      <c r="C5" s="156"/>
+      <c r="D5" s="156"/>
+      <c r="E5" s="156"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
@@ -8435,13 +8889,13 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="145" t="s">
+      <c r="A13" s="155" t="s">
         <v>118</v>
       </c>
-      <c r="B13" s="146"/>
-      <c r="C13" s="146"/>
-      <c r="D13" s="146"/>
-      <c r="E13" s="146"/>
+      <c r="B13" s="156"/>
+      <c r="C13" s="156"/>
+      <c r="D13" s="156"/>
+      <c r="E13" s="156"/>
     </row>
     <row r="14" spans="1:5" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
@@ -8523,13 +8977,13 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="145" t="s">
+      <c r="A20" s="155" t="s">
         <v>127</v>
       </c>
-      <c r="B20" s="146"/>
-      <c r="C20" s="146"/>
-      <c r="D20" s="146"/>
-      <c r="E20" s="146"/>
+      <c r="B20" s="156"/>
+      <c r="C20" s="156"/>
+      <c r="D20" s="156"/>
+      <c r="E20" s="156"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
@@ -8657,13 +9111,13 @@
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="145" t="s">
+      <c r="A29" s="155" t="s">
         <v>138</v>
       </c>
-      <c r="B29" s="146"/>
-      <c r="C29" s="146"/>
-      <c r="D29" s="146"/>
-      <c r="E29" s="146"/>
+      <c r="B29" s="156"/>
+      <c r="C29" s="156"/>
+      <c r="D29" s="156"/>
+      <c r="E29" s="156"/>
     </row>
     <row r="30" spans="1:5" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
@@ -8751,13 +9205,13 @@
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="145" t="s">
+      <c r="A36" s="155" t="s">
         <v>149</v>
       </c>
-      <c r="B36" s="146"/>
-      <c r="C36" s="146"/>
-      <c r="D36" s="146"/>
-      <c r="E36" s="146"/>
+      <c r="B36" s="156"/>
+      <c r="C36" s="156"/>
+      <c r="D36" s="156"/>
+      <c r="E36" s="156"/>
     </row>
     <row r="37" spans="1:5" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
@@ -8811,13 +9265,13 @@
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="145" t="s">
+      <c r="A41" s="155" t="s">
         <v>156</v>
       </c>
-      <c r="B41" s="146"/>
-      <c r="C41" s="146"/>
-      <c r="D41" s="146"/>
-      <c r="E41" s="146"/>
+      <c r="B41" s="156"/>
+      <c r="C41" s="156"/>
+      <c r="D41" s="156"/>
+      <c r="E41" s="156"/>
     </row>
     <row r="42" spans="1:5" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
@@ -8855,6 +9309,134 @@
       </c>
       <c r="E43" s="28" t="s">
         <v>158</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="145" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>160</v>
+      </c>
+      <c r="C46" s="146">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="E46" s="147" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>162</v>
+      </c>
+      <c r="C47" s="146">
+        <v>5.5E-2</v>
+      </c>
+      <c r="E47" s="147" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>164</v>
+      </c>
+      <c r="C48" s="148">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="E48" s="147" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>166</v>
+      </c>
+      <c r="C49" s="146">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="E49" s="147" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>168</v>
+      </c>
+      <c r="C50" s="149">
+        <f>C46+C48*C47+C49</f>
+        <v>0.11075</v>
+      </c>
+      <c r="E50" s="147" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>170</v>
+      </c>
+      <c r="C51" s="146">
+        <v>0.2</v>
+      </c>
+      <c r="E51" s="147" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>172</v>
+      </c>
+      <c r="C52" s="146">
+        <v>5.5E-2</v>
+      </c>
+      <c r="E52" s="147" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>174</v>
+      </c>
+      <c r="C53" s="149">
+        <f>C52*(1-0.2583)</f>
+        <v>4.0793500000000003E-2</v>
+      </c>
+      <c r="E53" s="147" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>175</v>
+      </c>
+      <c r="C54" s="150">
+        <f>(1-C51)*C50+C51*C53</f>
+        <v>9.6758700000000017E-2</v>
+      </c>
+      <c r="E54" s="147" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>177</v>
+      </c>
+      <c r="C55" s="149">
+        <f>C37</f>
+        <v>9.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>178</v>
+      </c>
+      <c r="C56" s="149">
+        <f>C54-C55</f>
+        <v>1.7587000000000158E-3</v>
+      </c>
+      <c r="E56" s="147" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -8883,28 +9465,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="147" t="s">
-        <v>159</v>
-      </c>
-      <c r="B1" s="146"/>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
+      <c r="A1" s="157" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1" s="156"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="145" t="s">
-        <v>160</v>
-      </c>
-      <c r="B3" s="146"/>
+      <c r="A3" s="155" t="s">
+        <v>181</v>
+      </c>
+      <c r="B3" s="156"/>
       <c r="C3" s="3" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="B4" s="43">
         <v>61416</v>
@@ -8913,12 +9495,12 @@
         <v>54977</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>164</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="29" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="B5" s="44">
         <v>53594</v>
@@ -8927,12 +9509,12 @@
         <v>45467</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="26" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="B6" s="43">
         <v>7904</v>
@@ -8941,12 +9523,12 @@
         <v>9510</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="29" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="B7" s="44">
         <v>4048</v>
@@ -8955,12 +9537,12 @@
         <v>2942</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="26" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="B8" s="43">
         <v>-15280</v>
@@ -8969,12 +9551,12 @@
         <v>-13219</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="29" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="B9" s="44">
         <v>-38170</v>
@@ -8983,12 +9565,12 @@
         <v>-35252</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="26" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="B10" s="43">
         <v>-876</v>
@@ -8997,12 +9579,12 @@
         <v>-298</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="29" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="B11" s="44">
         <v>-425</v>
@@ -9011,12 +9593,12 @@
         <v>-412</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="26" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="B12" s="43">
         <v>-3633</v>
@@ -9025,12 +9607,12 @@
         <v>-2710</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="B13" s="45">
         <f>B4+B7+B8+B9+B10+B11+B12</f>
@@ -9041,12 +9623,12 @@
         <v>6028</v>
       </c>
       <c r="D13" s="28" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="B14" s="46">
         <v>-296</v>
@@ -9055,12 +9637,12 @@
         <v>-221</v>
       </c>
       <c r="D14" s="28" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="B15" s="45">
         <f>B13+B14</f>
@@ -9073,7 +9655,7 @@
     </row>
     <row r="16" spans="1:4" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="B16" s="46">
         <v>3482</v>
@@ -9082,12 +9664,12 @@
         <v>2560</v>
       </c>
       <c r="D16" s="28" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="47" t="s">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="B17" s="48">
         <f>B15+B16</f>
@@ -9098,24 +9680,24 @@
         <v>8367</v>
       </c>
       <c r="D17" s="50" t="s">
-        <v>187</v>
+        <v>208</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="145" t="s">
-        <v>188</v>
-      </c>
-      <c r="B19" s="146"/>
+      <c r="A19" s="155" t="s">
+        <v>209</v>
+      </c>
+      <c r="B19" s="156"/>
       <c r="C19" s="3" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="B20" s="45">
         <f>B17</f>
@@ -9128,7 +9710,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="B21" s="46">
         <v>3929</v>
@@ -9137,12 +9719,12 @@
         <v>2931</v>
       </c>
       <c r="D21" s="28" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="B22" s="46">
         <v>-812</v>
@@ -9151,12 +9733,12 @@
         <v>-321</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>193</v>
+        <v>214</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="47" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="B23" s="48">
         <f>B20+B21+B22</f>
@@ -9167,12 +9749,12 @@
         <v>10977</v>
       </c>
       <c r="D23" s="50" t="s">
-        <v>195</v>
+        <v>216</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="B24" s="36">
         <f>B23/B4</f>
@@ -9183,112 +9765,112 @@
         <v>0.19966531458609965</v>
       </c>
       <c r="D24" s="28" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="145" t="s">
-        <v>198</v>
-      </c>
-      <c r="B26" s="146"/>
+      <c r="A26" s="155" t="s">
+        <v>219</v>
+      </c>
+      <c r="B26" s="156"/>
       <c r="C26" s="3" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="B27" s="46">
         <v>266</v>
       </c>
       <c r="D27" s="28" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="B28" s="46">
         <v>296</v>
       </c>
       <c r="D28" s="28" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="B29" s="46">
         <v>575</v>
       </c>
       <c r="D29" s="28" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="B30" s="46">
         <v>296</v>
       </c>
       <c r="D30" s="28" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="B31" s="45">
         <f>B27+B29</f>
         <v>841</v>
       </c>
       <c r="D31" s="28" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="B32" s="46">
         <v>280</v>
       </c>
       <c r="D32" s="28" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="B33" s="45">
         <f>B31+B32</f>
         <v>1121</v>
       </c>
       <c r="D33" s="28" t="s">
-        <v>211</v>
+        <v>232</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="145" t="s">
-        <v>212</v>
-      </c>
-      <c r="B35" s="146"/>
+      <c r="A35" s="155" t="s">
+        <v>233</v>
+      </c>
+      <c r="B35" s="156"/>
       <c r="C35" s="3" t="s">
-        <v>213</v>
+        <v>234</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="26" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="B36" s="43">
         <v>112987</v>
@@ -9297,12 +9879,12 @@
         <v>76705</v>
       </c>
       <c r="D36" s="28" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="29" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="B37" s="44">
         <v>69194</v>
@@ -9313,7 +9895,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="26" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="B38" s="43">
         <v>831</v>
@@ -9324,7 +9906,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="29" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="B39" s="44">
         <v>11926</v>
@@ -9335,7 +9917,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="26" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="B40" s="43">
         <v>5402</v>
@@ -9346,7 +9928,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="29" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="B41" s="44">
         <v>10925</v>
@@ -9357,7 +9939,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="26" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="B42" s="43">
         <v>50183</v>
@@ -9368,7 +9950,7 @@
     </row>
     <row r="43" spans="1:4" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="29" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="B43" s="44">
         <v>30981</v>
@@ -9377,33 +9959,33 @@
         <v>7912</v>
       </c>
       <c r="D43" s="28" t="s">
-        <v>224</v>
+        <v>245</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="145" t="s">
-        <v>225</v>
-      </c>
-      <c r="B45" s="146"/>
+      <c r="A45" s="155" t="s">
+        <v>246</v>
+      </c>
+      <c r="B45" s="156"/>
       <c r="C45" s="3" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="B46" s="51">
         <f>B43/1000</f>
         <v>30.981000000000002</v>
       </c>
       <c r="D46" s="28" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
-        <v>229</v>
+        <v>250</v>
       </c>
       <c r="B47" s="51">
         <f>-B40/1000</f>
@@ -9412,7 +9994,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="B48" s="51">
         <f>-B41/1000</f>
@@ -9421,7 +10003,7 @@
     </row>
     <row r="49" spans="1:4" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="47" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="B49" s="52">
         <f>B46+B47+B48</f>
@@ -9429,32 +10011,32 @@
       </c>
       <c r="C49" s="53"/>
       <c r="D49" s="28" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="145" t="s">
-        <v>233</v>
-      </c>
-      <c r="B51" s="146"/>
+      <c r="A51" s="155" t="s">
+        <v>254</v>
+      </c>
+      <c r="B51" s="156"/>
       <c r="C51" s="3" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="B52" s="35">
         <v>5.24</v>
       </c>
       <c r="D52" s="28" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="9" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="B53" s="51">
         <f>-Inputs!B10</f>
@@ -9463,30 +10045,30 @@
     </row>
     <row r="54" spans="1:4" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>237</v>
+        <v>258</v>
       </c>
       <c r="B54" s="51">
         <f>B52+B53</f>
         <v>4.2160000000000002</v>
       </c>
       <c r="D54" s="28" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="9" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="B55" s="39">
         <v>2.9470000000000001</v>
       </c>
       <c r="D55" s="28" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="47" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="B56" s="52">
         <f>B54+B55</f>
@@ -9494,21 +10076,21 @@
       </c>
       <c r="C56" s="53"/>
       <c r="D56" s="28" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="145" t="s">
-        <v>243</v>
-      </c>
-      <c r="B58" s="146"/>
+      <c r="A58" s="155" t="s">
+        <v>264</v>
+      </c>
+      <c r="B58" s="156"/>
       <c r="C58" s="3" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="9" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="B59" s="51">
         <f>Inputs!B8</f>
@@ -9517,19 +10099,19 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="9" t="s">
-        <v>245</v>
+        <v>266</v>
       </c>
       <c r="B60" s="36">
         <f>1-Inputs!B31</f>
         <v>0.75</v>
       </c>
       <c r="D60" s="28" t="s">
-        <v>246</v>
+        <v>267</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="9" t="s">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="B61" s="51">
         <f>B59*(1-Inputs!B31)</f>
@@ -9538,7 +10120,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="9" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="B62" s="51">
         <f>Inputs!B9</f>
@@ -9547,7 +10129,7 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="9" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="B63" s="51">
         <f>-Inputs!B10</f>
@@ -9556,53 +10138,53 @@
     </row>
     <row r="64" spans="1:4" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="9" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="B64" s="35">
         <v>-0.52100000000000002</v>
       </c>
       <c r="D64" s="28" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="B65" s="52">
         <f>B61+B62+B63+B64</f>
         <v>7.2762499999999992</v>
       </c>
       <c r="D65" s="28" t="s">
-        <v>252</v>
+        <v>273</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="145" t="s">
-        <v>253</v>
-      </c>
-      <c r="B67" s="146"/>
+      <c r="A67" s="155" t="s">
+        <v>274</v>
+      </c>
+      <c r="B67" s="156"/>
     </row>
     <row r="68" spans="1:4" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="9" t="s">
-        <v>254</v>
+        <v>275</v>
       </c>
       <c r="B68" s="46">
         <v>1497346</v>
       </c>
       <c r="D68" s="28" t="s">
-        <v>255</v>
+        <v>276</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="9" t="s">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="B69" s="46">
         <v>1536790</v>
       </c>
       <c r="D69" s="28" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
     </row>
   </sheetData>
@@ -9633,64 +10215,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="153" t="s">
-        <v>258</v>
-      </c>
-      <c r="B1" s="146"/>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
-      <c r="E1" s="146"/>
-      <c r="F1" s="146"/>
-      <c r="G1" s="146"/>
-      <c r="H1" s="146"/>
-      <c r="I1" s="146"/>
-      <c r="J1" s="146"/>
-      <c r="K1" s="146"/>
-      <c r="L1" s="146"/>
-      <c r="M1" s="146"/>
-      <c r="N1" s="146"/>
-      <c r="O1" s="146"/>
-      <c r="P1" s="146"/>
-      <c r="Q1" s="146"/>
-      <c r="R1" s="146"/>
-      <c r="S1" s="146"/>
+      <c r="A1" s="163" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1" s="156"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
+      <c r="F1" s="156"/>
+      <c r="G1" s="156"/>
+      <c r="H1" s="156"/>
+      <c r="I1" s="156"/>
+      <c r="J1" s="156"/>
+      <c r="K1" s="156"/>
+      <c r="L1" s="156"/>
+      <c r="M1" s="156"/>
+      <c r="N1" s="156"/>
+      <c r="O1" s="156"/>
+      <c r="P1" s="156"/>
+      <c r="Q1" s="156"/>
+      <c r="R1" s="156"/>
+      <c r="S1" s="156"/>
     </row>
     <row r="2" spans="1:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="54" t="s">
-        <v>259</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="154" t="s">
+      <c r="B3" s="164" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="146"/>
-      <c r="D3" s="146"/>
-      <c r="E3" s="154" t="s">
+      <c r="C3" s="156"/>
+      <c r="D3" s="156"/>
+      <c r="E3" s="164" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="146"/>
-      <c r="G3" s="146"/>
-      <c r="H3" s="154" t="s">
+      <c r="F3" s="156"/>
+      <c r="G3" s="156"/>
+      <c r="H3" s="164" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="146"/>
-      <c r="J3" s="146"/>
-      <c r="K3" s="154" t="s">
+      <c r="I3" s="156"/>
+      <c r="J3" s="156"/>
+      <c r="K3" s="164" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="146"/>
-      <c r="M3" s="146"/>
-      <c r="N3" s="154" t="s">
+      <c r="L3" s="156"/>
+      <c r="M3" s="156"/>
+      <c r="N3" s="164" t="s">
         <v>13</v>
       </c>
-      <c r="O3" s="146"/>
-      <c r="P3" s="146"/>
-      <c r="Q3" s="155" t="s">
-        <v>260</v>
-      </c>
-      <c r="R3" s="146"/>
-      <c r="S3" s="146"/>
+      <c r="O3" s="156"/>
+      <c r="P3" s="156"/>
+      <c r="Q3" s="165" t="s">
+        <v>281</v>
+      </c>
+      <c r="R3" s="156"/>
+      <c r="S3" s="156"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B4" s="55" t="s">
@@ -9739,23 +10321,23 @@
         <v>103</v>
       </c>
       <c r="Q4" s="55" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="R4" s="56" t="s">
-        <v>262</v>
+        <v>283</v>
       </c>
       <c r="S4" s="57" t="s">
-        <v>263</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>265</v>
+        <v>286</v>
       </c>
       <c r="B7" s="51">
         <f>Inputs!B6*(1+Inputs!B14)</f>
@@ -9820,7 +10402,7 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="B8" s="36">
         <f>Inputs!B14</f>
@@ -9885,12 +10467,12 @@
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="B11" s="36">
         <f>Inputs!B23</f>
@@ -9955,7 +10537,7 @@
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="B12" s="51">
         <f t="shared" ref="B12:P12" si="0">B7*B11</f>
@@ -10020,7 +10602,7 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="B13" s="51">
         <f>B7*Inputs!B30</f>
@@ -10085,7 +10667,7 @@
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="B14" s="51">
         <f t="shared" ref="B14:P14" si="1">B12-B13</f>
@@ -10150,12 +10732,12 @@
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>273</v>
+        <v>294</v>
       </c>
       <c r="B17" s="51">
         <f>B14*Inputs!B31</f>
@@ -10220,7 +10802,7 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="B18" s="51">
         <f>B14*(1-Inputs!B31)</f>
@@ -10285,7 +10867,7 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="B19" s="51">
         <f>-B7*Inputs!B32</f>
@@ -10350,7 +10932,7 @@
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="B20" s="51">
         <f>-(B7-Inputs!B6)*Inputs!B33</f>
@@ -10415,7 +10997,7 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="B21" s="58">
         <f t="shared" ref="B21:P21" si="2">B18+B13+B19+B20</f>
@@ -10480,7 +11062,7 @@
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="B22" s="51">
         <f t="shared" ref="B22:P22" si="3">B12-B17+B19+B20</f>
@@ -10545,12 +11127,12 @@
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
-        <v>280</v>
+        <v>301</v>
       </c>
       <c r="B25" s="59">
         <v>0.5</v>
@@ -10600,7 +11182,7 @@
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="B26" s="51">
         <f>1/(1+Inputs!B37)^0.5</f>
@@ -10665,7 +11247,7 @@
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
-        <v>282</v>
+        <v>303</v>
       </c>
       <c r="B27" s="51">
         <f t="shared" ref="B27:P27" si="4">B21*B26</f>
@@ -10730,7 +11312,7 @@
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>283</v>
+        <v>304</v>
       </c>
       <c r="Q29" s="15" t="s">
         <v>101</v>
@@ -10744,7 +11326,7 @@
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="Q30" s="51">
         <f>B27+E27+H27+K27+N27</f>
@@ -10761,7 +11343,7 @@
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="Q31" s="51">
         <f>N21*(1+Inputs!B38)</f>
@@ -10778,7 +11360,7 @@
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="Q32" s="51">
         <f>Q31/(Inputs!B37-Inputs!B38)</f>
@@ -10795,7 +11377,7 @@
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="Q33" s="51">
         <f>Q32/(1+Inputs!B37)^5</f>
@@ -10812,7 +11394,7 @@
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="Q34" s="52">
         <f>Q30+Q33</f>
@@ -10829,7 +11411,7 @@
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="Q36" s="51">
         <f>N12*Inputs!B39</f>
@@ -10846,7 +11428,7 @@
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
-        <v>290</v>
+        <v>311</v>
       </c>
       <c r="Q37" s="51">
         <f>Q36/(1+Inputs!B37)^5</f>
@@ -10863,7 +11445,7 @@
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="Q38" s="52">
         <f>Q30+Q37</f>
@@ -10880,7 +11462,7 @@
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="s">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="Q40" s="42">
         <f>Q32/N12</f>
@@ -10897,7 +11479,7 @@
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" s="9" t="s">
-        <v>293</v>
+        <v>314</v>
       </c>
       <c r="Q41" s="36">
         <f>Q33/Q34</f>
@@ -10914,7 +11496,7 @@
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="Q42" s="42">
         <f>Q34/Inputs!B7</f>
@@ -10931,7 +11513,7 @@
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" s="9" t="s">
-        <v>295</v>
+        <v>316</v>
       </c>
       <c r="Q43" s="42">
         <f>Q34/Inputs!B6</f>
@@ -10971,36 +11553,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="147" t="s">
-        <v>296</v>
-      </c>
-      <c r="B1" s="146"/>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
-      <c r="E1" s="146"/>
-      <c r="F1" s="146"/>
-      <c r="G1" s="146"/>
-      <c r="H1" s="146"/>
+      <c r="A1" s="157" t="s">
+        <v>317</v>
+      </c>
+      <c r="B1" s="156"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
+      <c r="F1" s="156"/>
+      <c r="G1" s="156"/>
+      <c r="H1" s="156"/>
     </row>
     <row r="2" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>297</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="156" t="s">
-        <v>298</v>
-      </c>
-      <c r="B4" s="146"/>
-      <c r="C4" s="146"/>
-      <c r="D4" s="146"/>
-      <c r="E4" s="146"/>
-      <c r="F4" s="146"/>
-      <c r="G4" s="146"/>
+      <c r="A4" s="166" t="s">
+        <v>319</v>
+      </c>
+      <c r="B4" s="156"/>
+      <c r="C4" s="156"/>
+      <c r="D4" s="156"/>
+      <c r="E4" s="156"/>
+      <c r="F4" s="156"/>
+      <c r="G4" s="156"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="C5" s="60">
         <v>1.4999999999999999E-2</v>
@@ -11145,23 +11727,23 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="61" t="s">
-        <v>300</v>
+        <v>321</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="156" t="s">
-        <v>301</v>
-      </c>
-      <c r="B14" s="146"/>
-      <c r="C14" s="146"/>
-      <c r="D14" s="146"/>
-      <c r="E14" s="146"/>
-      <c r="F14" s="146"/>
-      <c r="G14" s="146"/>
+      <c r="A14" s="166" t="s">
+        <v>322</v>
+      </c>
+      <c r="B14" s="156"/>
+      <c r="C14" s="156"/>
+      <c r="D14" s="156"/>
+      <c r="E14" s="156"/>
+      <c r="F14" s="156"/>
+      <c r="G14" s="156"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>302</v>
+        <v>323</v>
       </c>
       <c r="C15" s="62">
         <v>10</v>
@@ -11306,12 +11888,12 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="61" t="s">
-        <v>303</v>
+        <v>324</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>304</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -11336,28 +11918,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="147" t="s">
-        <v>305</v>
-      </c>
-      <c r="B1" s="146"/>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
-      <c r="E1" s="146"/>
+      <c r="A1" s="157" t="s">
+        <v>326</v>
+      </c>
+      <c r="B1" s="156"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>306</v>
+        <v>327</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="18" t="s">
-        <v>307</v>
+        <v>328</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>309</v>
+        <v>330</v>
       </c>
       <c r="E4" s="63" t="s">
         <v>28</v>
@@ -11365,7 +11947,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>310</v>
+        <v>331</v>
       </c>
       <c r="B5" s="36">
         <f>Inputs!C21</f>
@@ -11398,13 +11980,13 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="156" t="s">
-        <v>311</v>
-      </c>
-      <c r="B8" s="146"/>
-      <c r="C8" s="146"/>
-      <c r="D8" s="146"/>
-      <c r="E8" s="146"/>
+      <c r="A8" s="166" t="s">
+        <v>332</v>
+      </c>
+      <c r="B8" s="156"/>
+      <c r="C8" s="156"/>
+      <c r="D8" s="156"/>
+      <c r="E8" s="156"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
@@ -11423,7 +12005,7 @@
         <v>0.22813130128956624</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>312</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -11443,7 +12025,7 @@
         <v>0.24446351439364336</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>313</v>
+        <v>334</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -11463,7 +12045,7 @@
         <v>0.26692030741174938</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -11483,7 +12065,7 @@
         <v>0.29243939038686989</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -11503,21 +12085,21 @@
         <v>0.32</v>
       </c>
       <c r="E13" s="28" t="s">
-        <v>316</v>
+        <v>337</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="156" t="s">
-        <v>317</v>
-      </c>
-      <c r="B15" s="146"/>
-      <c r="C15" s="146"/>
-      <c r="D15" s="146"/>
-      <c r="E15" s="146"/>
+      <c r="A15" s="166" t="s">
+        <v>338</v>
+      </c>
+      <c r="B15" s="156"/>
+      <c r="C15" s="156"/>
+      <c r="D15" s="156"/>
+      <c r="E15" s="156"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="B16" s="51">
         <f>DCF!C7*(C5+(C6-C5)*0.2)</f>
@@ -11532,12 +12114,12 @@
         <v>16.392767039999999</v>
       </c>
       <c r="E16" s="28" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>320</v>
+        <v>341</v>
       </c>
       <c r="B17" s="51">
         <f>DCF!F7*(C5+(C6-C5)*0.4)</f>
@@ -11552,12 +12134,12 @@
         <v>20.201298249599997</v>
       </c>
       <c r="E17" s="28" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>322</v>
+        <v>343</v>
       </c>
       <c r="B18" s="51">
         <f>DCF!I7*(C5+(C6-C5)*0.6)</f>
@@ -11572,12 +12154,12 @@
         <v>24.924433120703991</v>
       </c>
       <c r="E18" s="28" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>324</v>
+        <v>345</v>
       </c>
       <c r="B19" s="51">
         <f>DCF!L7*(C5+(C6-C5)*0.8)</f>
@@ -11592,12 +12174,12 @@
         <v>30.311157547513435</v>
       </c>
       <c r="E19" s="28" t="s">
-        <v>325</v>
+        <v>346</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>326</v>
+        <v>347</v>
       </c>
       <c r="B20" s="51">
         <f>DCF!O7*(C5+(C6-C5)*1)</f>
@@ -11612,12 +12194,12 @@
         <v>36.152899028363514</v>
       </c>
       <c r="E20" s="28" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
       <c r="B21" s="51">
         <f>(B16-DCF!C7*Inputs!C30)*(1-Inputs!C31)+DCF!C7*Inputs!C30-DCF!C7*Inputs!C32-(DCF!C7-Inputs!C6)*Inputs!C33</f>
@@ -11634,7 +12216,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>329</v>
+        <v>350</v>
       </c>
       <c r="B22" s="51">
         <f>(B17-DCF!F7*Inputs!C30)*(1-Inputs!C31)+DCF!F7*Inputs!C30-DCF!F7*Inputs!C32-(DCF!F7-DCF!C7)*Inputs!C33</f>
@@ -11651,7 +12233,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>330</v>
+        <v>351</v>
       </c>
       <c r="B23" s="51">
         <f>(B18-DCF!I7*Inputs!C30)*(1-Inputs!C31)+DCF!I7*Inputs!C30-DCF!I7*Inputs!C32-(DCF!I7-DCF!F7)*Inputs!C33</f>
@@ -11668,7 +12250,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
-        <v>331</v>
+        <v>352</v>
       </c>
       <c r="B24" s="51">
         <f>(B19-DCF!L7*Inputs!C30)*(1-Inputs!C31)+DCF!L7*Inputs!C30-DCF!L7*Inputs!C32-(DCF!L7-DCF!I7)*Inputs!C33</f>
@@ -11685,7 +12267,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
-        <v>332</v>
+        <v>353</v>
       </c>
       <c r="B25" s="51">
         <f>(B20-DCF!O7*Inputs!C30)*(1-Inputs!C31)+DCF!O7*Inputs!C30-DCF!O7*Inputs!C32-(DCF!O7-DCF!L7)*Inputs!C33</f>
@@ -11701,17 +12283,17 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="156" t="s">
-        <v>333</v>
-      </c>
-      <c r="B27" s="146"/>
-      <c r="C27" s="146"/>
-      <c r="D27" s="146"/>
-      <c r="E27" s="146"/>
+      <c r="A27" s="166" t="s">
+        <v>354</v>
+      </c>
+      <c r="B27" s="156"/>
+      <c r="C27" s="156"/>
+      <c r="D27" s="156"/>
+      <c r="E27" s="156"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="B28" s="51">
         <f>B21/(1+Inputs!C37)^0.5</f>
@@ -11728,7 +12310,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
-        <v>335</v>
+        <v>356</v>
       </c>
       <c r="B29" s="51">
         <f>B22/(1+Inputs!C37)^1.5</f>
@@ -11745,7 +12327,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
-        <v>336</v>
+        <v>357</v>
       </c>
       <c r="B30" s="51">
         <f>B23/(1+Inputs!C37)^2.5</f>
@@ -11762,7 +12344,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
-        <v>337</v>
+        <v>358</v>
       </c>
       <c r="B31" s="51">
         <f>B24/(1+Inputs!C37)^3.5</f>
@@ -11779,7 +12361,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
-        <v>338</v>
+        <v>359</v>
       </c>
       <c r="B32" s="51">
         <f>B25/(1+Inputs!C37)^4.5</f>
@@ -11796,7 +12378,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>339</v>
+        <v>360</v>
       </c>
       <c r="B33" s="51">
         <f>SUM(B28:B32)</f>
@@ -11813,7 +12395,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
-        <v>340</v>
+        <v>361</v>
       </c>
       <c r="B34" s="51">
         <f>B25*(1+Inputs!C38)/(Inputs!C37-Inputs!C38)/(1+Inputs!C37)^5</f>
@@ -11830,7 +12412,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>341</v>
+        <v>362</v>
       </c>
       <c r="B35" s="52">
         <f>B33+B34</f>
@@ -11847,7 +12429,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
-        <v>342</v>
+        <v>363</v>
       </c>
       <c r="B36" s="51">
         <f>B35-B35</f>
@@ -11864,7 +12446,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
-        <v>343</v>
+        <v>364</v>
       </c>
       <c r="B37" s="36">
         <f>0</f>
@@ -11881,7 +12463,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="64" t="s">
-        <v>344</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -11912,61 +12494,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="147" t="s">
-        <v>345</v>
-      </c>
-      <c r="B1" s="146"/>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
-      <c r="E1" s="146"/>
-      <c r="F1" s="146"/>
-      <c r="G1" s="146"/>
-      <c r="H1" s="146"/>
-      <c r="I1" s="146"/>
+      <c r="A1" s="157" t="s">
+        <v>366</v>
+      </c>
+      <c r="B1" s="156"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
+      <c r="F1" s="156"/>
+      <c r="G1" s="156"/>
+      <c r="H1" s="156"/>
+      <c r="I1" s="156"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>346</v>
+        <v>367</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>347</v>
+        <v>368</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>348</v>
+        <v>369</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>349</v>
+        <v>370</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>350</v>
+        <v>371</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>351</v>
+        <v>372</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>352</v>
+        <v>373</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>353</v>
+        <v>374</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>354</v>
+        <v>375</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>355</v>
+        <v>376</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="65" t="s">
-        <v>356</v>
+        <v>377</v>
       </c>
       <c r="B5" s="65" t="s">
-        <v>357</v>
+        <v>378</v>
       </c>
       <c r="C5" s="65" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="D5" s="66">
         <v>3636</v>
@@ -11986,18 +12568,18 @@
         <v>25.971428571428572</v>
       </c>
       <c r="I5" s="68" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="29" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>362</v>
+        <v>383</v>
       </c>
       <c r="D6" s="69">
         <v>1818</v>
@@ -12017,18 +12599,18 @@
         <v>9.09</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>363</v>
+        <v>384</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="65" t="s">
-        <v>364</v>
+        <v>385</v>
       </c>
       <c r="B7" s="65" t="s">
-        <v>365</v>
+        <v>386</v>
       </c>
       <c r="C7" s="65" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
       <c r="D7" s="66">
         <v>2273</v>
@@ -12048,18 +12630,18 @@
         <v>33.426470588235297</v>
       </c>
       <c r="I7" s="68" t="s">
-        <v>367</v>
+        <v>388</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">
-        <v>368</v>
+        <v>389</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>370</v>
+        <v>391</v>
       </c>
       <c r="D8" s="69">
         <v>4091</v>
@@ -12079,18 +12661,18 @@
         <v>33.532786885245905</v>
       </c>
       <c r="I8" s="24" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="71" t="s">
-        <v>372</v>
+        <v>393</v>
       </c>
       <c r="B9" s="65" t="s">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="C9" s="65" t="s">
-        <v>374</v>
+        <v>395</v>
       </c>
       <c r="D9" s="66">
         <v>1576</v>
@@ -12104,28 +12686,28 @@
         <v>7.6765708718947874</v>
       </c>
       <c r="H9" s="67" t="s">
-        <v>375</v>
+        <v>396</v>
       </c>
       <c r="I9" s="68" t="s">
-        <v>376</v>
+        <v>397</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="156" t="s">
-        <v>377</v>
-      </c>
-      <c r="B11" s="146"/>
-      <c r="C11" s="146"/>
-      <c r="D11" s="146"/>
-      <c r="E11" s="146"/>
-      <c r="F11" s="146"/>
-      <c r="G11" s="146"/>
-      <c r="H11" s="146"/>
-      <c r="I11" s="146"/>
+      <c r="A11" s="166" t="s">
+        <v>398</v>
+      </c>
+      <c r="B11" s="156"/>
+      <c r="C11" s="156"/>
+      <c r="D11" s="156"/>
+      <c r="E11" s="156"/>
+      <c r="F11" s="156"/>
+      <c r="G11" s="156"/>
+      <c r="H11" s="156"/>
+      <c r="I11" s="156"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="G12" s="42">
         <f>MEDIAN(G5:G8)</f>
@@ -12138,7 +12720,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>379</v>
+        <v>400</v>
       </c>
       <c r="G13" s="42">
         <f>MIN(G5:G8)</f>
@@ -12151,7 +12733,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>380</v>
+        <v>401</v>
       </c>
       <c r="G14" s="42">
         <f>MAX(G5:G8)</f>
@@ -12163,21 +12745,21 @@
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="156" t="s">
-        <v>381</v>
-      </c>
-      <c r="B16" s="146"/>
-      <c r="C16" s="146"/>
-      <c r="D16" s="146"/>
-      <c r="E16" s="146"/>
-      <c r="F16" s="146"/>
-      <c r="G16" s="146"/>
-      <c r="H16" s="146"/>
-      <c r="I16" s="146"/>
+      <c r="A16" s="166" t="s">
+        <v>402</v>
+      </c>
+      <c r="B16" s="156"/>
+      <c r="C16" s="156"/>
+      <c r="D16" s="156"/>
+      <c r="E16" s="156"/>
+      <c r="F16" s="156"/>
+      <c r="G16" s="156"/>
+      <c r="H16" s="156"/>
+      <c r="I16" s="156"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>382</v>
+        <v>403</v>
       </c>
       <c r="E17" s="72">
         <f>DCF!C7</f>
@@ -12186,7 +12768,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>383</v>
+        <v>404</v>
       </c>
       <c r="F18" s="72">
         <f>DCF!C12</f>
@@ -12195,21 +12777,21 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>385</v>
+        <v>406</v>
       </c>
       <c r="F20" s="18" t="s">
-        <v>386</v>
+        <v>407</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>387</v>
+        <v>408</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>388</v>
+        <v>409</v>
       </c>
       <c r="E21" s="41">
         <v>3</v>
@@ -12223,7 +12805,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>389</v>
+        <v>410</v>
       </c>
       <c r="E22" s="51">
         <f>E17*E21</f>
@@ -12240,7 +12822,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>390</v>
+        <v>411</v>
       </c>
       <c r="E23" s="41">
         <v>12</v>
@@ -12254,7 +12836,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
-        <v>391</v>
+        <v>412</v>
       </c>
       <c r="E24" s="51">
         <f>F18*E23</f>
@@ -12271,7 +12853,7 @@
     </row>
     <row r="26" spans="1:9" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>392</v>
+        <v>413</v>
       </c>
       <c r="E26" s="52">
         <f>ROUND(AVERAGE(E22,E24),0)</f>
@@ -12286,12 +12868,12 @@
         <v>548</v>
       </c>
       <c r="I26" s="28" t="s">
-        <v>393</v>
+        <v>414</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
-        <v>394</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -12319,51 +12901,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="147" t="s">
-        <v>395</v>
-      </c>
-      <c r="B1" s="146"/>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
-      <c r="E1" s="146"/>
-      <c r="F1" s="146"/>
-      <c r="G1" s="146"/>
-      <c r="H1" s="146"/>
-      <c r="I1" s="146"/>
-      <c r="J1" s="146"/>
+      <c r="A1" s="157" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1" s="156"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
+      <c r="F1" s="156"/>
+      <c r="G1" s="156"/>
+      <c r="H1" s="156"/>
+      <c r="I1" s="156"/>
+      <c r="J1" s="156"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="73" t="s">
-        <v>396</v>
+        <v>417</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>397</v>
+        <v>418</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>398</v>
+        <v>419</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>399</v>
+        <v>420</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>400</v>
+        <v>421</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>350</v>
+        <v>371</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>401</v>
+        <v>422</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>402</v>
+        <v>423</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>403</v>
+        <v>424</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>404</v>
+        <v>425</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>28</v>
@@ -12371,16 +12953,16 @@
     </row>
     <row r="5" spans="1:10" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="71" t="s">
-        <v>405</v>
+        <v>426</v>
       </c>
       <c r="B5" s="74">
         <v>2024</v>
       </c>
       <c r="C5" s="65" t="s">
-        <v>406</v>
+        <v>427</v>
       </c>
       <c r="D5" s="65" t="s">
-        <v>407</v>
+        <v>428</v>
       </c>
       <c r="E5" s="66">
         <v>1576</v>
@@ -12394,24 +12976,24 @@
         <v>7.6765708718947874</v>
       </c>
       <c r="I5" s="67" t="s">
-        <v>375</v>
+        <v>396</v>
       </c>
       <c r="J5" s="68" t="s">
-        <v>408</v>
+        <v>429</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
-        <v>409</v>
+        <v>430</v>
       </c>
       <c r="B6" s="75">
         <v>2023</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>411</v>
+        <v>432</v>
       </c>
       <c r="E6" s="69">
         <v>7273</v>
@@ -12431,21 +13013,21 @@
         <v>161.62222222222223</v>
       </c>
       <c r="J6" s="24" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="71" t="s">
-        <v>413</v>
+        <v>434</v>
       </c>
       <c r="B7" s="74">
         <v>2022</v>
       </c>
       <c r="C7" s="65" t="s">
-        <v>414</v>
+        <v>435</v>
       </c>
       <c r="D7" s="65" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="E7" s="66">
         <v>1591</v>
@@ -12465,21 +13047,21 @@
         <v>79.55</v>
       </c>
       <c r="J7" s="68" t="s">
-        <v>416</v>
+        <v>437</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>417</v>
+        <v>438</v>
       </c>
       <c r="B8" s="75">
         <v>2024</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>418</v>
+        <v>439</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>419</v>
+        <v>440</v>
       </c>
       <c r="E8" s="69">
         <v>600</v>
@@ -12499,21 +13081,21 @@
         <v>33.333333333333336</v>
       </c>
       <c r="J8" s="24" t="s">
-        <v>420</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="71" t="s">
-        <v>421</v>
+        <v>442</v>
       </c>
       <c r="B9" s="74">
         <v>2022</v>
       </c>
       <c r="C9" s="65" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="D9" s="65" t="s">
-        <v>422</v>
+        <v>443</v>
       </c>
       <c r="E9" s="66">
         <v>2364</v>
@@ -12533,25 +13115,25 @@
         <v>23.64</v>
       </c>
       <c r="J9" s="68" t="s">
-        <v>423</v>
+        <v>444</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="156" t="s">
-        <v>424</v>
-      </c>
-      <c r="B11" s="146"/>
-      <c r="C11" s="146"/>
-      <c r="D11" s="146"/>
-      <c r="E11" s="146"/>
-      <c r="F11" s="146"/>
-      <c r="G11" s="146"/>
-      <c r="H11" s="146"/>
-      <c r="I11" s="146"/>
+      <c r="A11" s="166" t="s">
+        <v>445</v>
+      </c>
+      <c r="B11" s="156"/>
+      <c r="C11" s="156"/>
+      <c r="D11" s="156"/>
+      <c r="E11" s="156"/>
+      <c r="F11" s="156"/>
+      <c r="G11" s="156"/>
+      <c r="H11" s="156"/>
+      <c r="I11" s="156"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="H12" s="42">
         <f>MEDIAN(H5:H9)</f>
@@ -12562,12 +13144,12 @@
         <v>33.333333333333336</v>
       </c>
       <c r="J12" t="s">
-        <v>425</v>
+        <v>446</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>379</v>
+        <v>400</v>
       </c>
       <c r="H13" s="42">
         <f>MIN(H5:H9)</f>
@@ -12580,7 +13162,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>380</v>
+        <v>401</v>
       </c>
       <c r="H14" s="42">
         <f>MAX(H5:H9)</f>
@@ -12592,27 +13174,27 @@
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="156" t="s">
-        <v>426</v>
-      </c>
-      <c r="B16" s="146"/>
-      <c r="C16" s="146"/>
-      <c r="D16" s="146"/>
-      <c r="E16" s="146"/>
-      <c r="F16" s="146"/>
-      <c r="G16" s="146"/>
-      <c r="H16" s="146"/>
-      <c r="I16" s="146"/>
-      <c r="J16" s="146"/>
+      <c r="A16" s="166" t="s">
+        <v>447</v>
+      </c>
+      <c r="B16" s="156"/>
+      <c r="C16" s="156"/>
+      <c r="D16" s="156"/>
+      <c r="E16" s="156"/>
+      <c r="F16" s="156"/>
+      <c r="G16" s="156"/>
+      <c r="H16" s="156"/>
+      <c r="I16" s="156"/>
+      <c r="J16" s="156"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="76" t="s">
-        <v>427</v>
+        <v>448</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>428</v>
+        <v>449</v>
       </c>
       <c r="F19" s="72">
         <f>Inputs!B6</f>
@@ -12621,7 +13203,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>429</v>
+        <v>450</v>
       </c>
       <c r="F20" s="72">
         <f>DCF!C7</f>
@@ -12630,7 +13212,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>430</v>
+        <v>451</v>
       </c>
       <c r="G21" s="72">
         <f>Inputs!B7</f>
@@ -12639,13 +13221,13 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="E23" s="18" t="s">
         <v>59</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>432</v>
+        <v>453</v>
       </c>
       <c r="G23" s="18" t="s">
         <v>61</v>
@@ -12653,7 +13235,7 @@
     </row>
     <row r="24" spans="1:10" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
-        <v>433</v>
+        <v>454</v>
       </c>
       <c r="E24" s="41">
         <v>4.7</v>
@@ -12665,12 +13247,12 @@
         <v>8.9</v>
       </c>
       <c r="J24" s="28" t="s">
-        <v>434</v>
+        <v>455</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
-        <v>435</v>
+        <v>456</v>
       </c>
       <c r="E25" s="51">
         <f>F19*E24</f>
@@ -12687,7 +13269,7 @@
     </row>
     <row r="27" spans="1:10" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>436</v>
+        <v>457</v>
       </c>
       <c r="E27" s="52">
         <f>ROUND(E25,0)</f>
@@ -12702,12 +13284,12 @@
         <v>547</v>
       </c>
       <c r="J27" s="28" t="s">
-        <v>437</v>
+        <v>458</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="77" t="s">
-        <v>438</v>
+        <v>459</v>
       </c>
     </row>
   </sheetData>
@@ -12733,17 +13315,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="157" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="146"/>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
-      <c r="E1" s="146"/>
-      <c r="F1" s="146"/>
-      <c r="G1" s="146"/>
-      <c r="H1" s="146"/>
-      <c r="I1" s="146"/>
+      <c r="B1" s="156"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
+      <c r="F1" s="156"/>
+      <c r="G1" s="156"/>
+      <c r="H1" s="156"/>
+      <c r="I1" s="156"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
@@ -12751,10 +13333,10 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="145" t="s">
+      <c r="A4" s="155" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="146"/>
+      <c r="B4" s="156"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
@@ -12795,10 +13377,10 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="145" t="s">
+      <c r="A10" s="155" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="146"/>
+      <c r="B10" s="156"/>
       <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
@@ -12931,10 +13513,10 @@
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="145" t="s">
+      <c r="A16" s="155" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="146"/>
+      <c r="B16" s="156"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
@@ -13064,10 +13646,10 @@
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="145" t="s">
+      <c r="A26" s="155" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="146"/>
+      <c r="B26" s="156"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">

--- a/Sidetrade_Valuation_2026_v2.xlsx
+++ b/Sidetrade_Valuation_2026_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abbah\Downloads\Portefolio\Portefolio\Sidetrade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A60B031C-6690-4BE3-9586-58778867BA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37EC532F-F88E-478B-9DE1-41EBD5C363BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21840" tabRatio="500" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="774">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="776">
   <si>
     <t>LBO AFFORDABILITY MODEL — BASE CASE  |  Max Entry EV for IRR targets</t>
   </si>
@@ -1146,10 +1146,10 @@
     <t>Point estimate for all other tabs: Linear interpolation (col B). Front-loaded / back-loaded show ±EV sensitivity.</t>
   </si>
   <si>
-    <t>TRADING COMPS — SaaS B2B / Finance Automation / O2C peers  |  Forward multiples FY2026E</t>
-  </si>
-  <si>
-    <t>ATTENTION - Multiples approx. H1-2025, PERIMES: rafraichir prix/guidances 2026 des 4 peers avant toute diffusion (sources: communiques guidance 2026, cf. note audit 12.5). Metriques non homogenes entre peers (EBITDA adj. / non-GAAP OI). EUR/USD ~1.10. Derniere revue: 15-Jul-2026.</t>
+    <t>TRADING COMPS — SaaS B2B / Finance Automation / O2C peers | VALORISATION AU 15/07/2026</t>
+  </si>
+  <si>
+    <t>Cours du 15/07/2026 (cotations intraday désynchronisées — précision au jour) ; EUR/USD 1,1424 au 15/07/2026 ; guidances publiées en mai 2026. Méthode PRIMAIRE : EV/Sales forward (guidance midpoint). Méthode de CONTRÔLE : EV/résultat opérationnel non-GAAP — ce n'est PAS un EBITDA (D&amp;A non réintégrée, SBC exclue selon les émetteurs) : proxy assumé, homogénéité imparfaite entre peers.</t>
   </si>
   <si>
     <t>Company</t>
@@ -1158,25 +1158,25 @@
     <t>Ticker</t>
   </si>
   <si>
-    <t>Description</t>
+    <t>Cours USD</t>
   </si>
   <si>
     <t>EV (€m)</t>
   </si>
   <si>
-    <t>Rev 2026E (€m)</t>
-  </si>
-  <si>
-    <t>EBITDA 2026E (€m)</t>
-  </si>
-  <si>
-    <t>EV/Sales 2026E</t>
-  </si>
-  <si>
-    <t>EV/EBITDA 2026E</t>
-  </si>
-  <si>
-    <t>Note</t>
+    <t>Rev fwd guidée (€m)</t>
+  </si>
+  <si>
+    <t>Rés. op. non-GAAP (€m)</t>
+  </si>
+  <si>
+    <t>EV/Sales fwd</t>
+  </si>
+  <si>
+    <t>EV/OpInc</t>
+  </si>
+  <si>
+    <t>Période guidée / note</t>
   </si>
   <si>
     <t>BlackLine</t>
@@ -1185,10 +1185,7 @@
     <t>BL US</t>
   </si>
   <si>
-    <t>Financial close &amp; AR automation SaaS</t>
-  </si>
-  <si>
-    <t>NYSE; fiscal yr Sep; EBITDA adj (non-GAAP); high NRR</t>
+    <t>FY26 clos 31/12/26 — calendaire 2026 ; marge op. 24,0-24,5%</t>
   </si>
   <si>
     <t>BILL Holdings</t>
@@ -1197,10 +1194,7 @@
     <t>BILL US</t>
   </si>
   <si>
-    <t>SMB financial ops platform (core only)</t>
-  </si>
-  <si>
-    <t>NYSE; float income excluded; core SaaS ~2× Sales</t>
+    <t>FY26 clos 30/06/26 — QUASI-TRAILING (exercice déjà clos) ; fonds clients neutralisés dans l'EV ; core revenue 1 501 M$ (EV/core 2,61x)</t>
   </si>
   <si>
     <t>nCino</t>
@@ -1209,10 +1203,7 @@
     <t>NCNO US</t>
   </si>
   <si>
-    <t>Cloud banking OS — vertical SaaS</t>
-  </si>
-  <si>
-    <t>Nasdaq; land &amp; expand in financial institutions</t>
+    <t>FY27 clos 31/01/27 ≈ calendaire 2026 ; FCF guidé 135-140 M$</t>
   </si>
   <si>
     <t>Workiva</t>
@@ -1221,171 +1212,168 @@
     <t>WK US</t>
   </si>
   <si>
-    <t>Cloud reporting &amp; compliance platform</t>
-  </si>
-  <si>
-    <t>NYSE; high NRR, finance/audit/ESG use cases</t>
-  </si>
-  <si>
-    <t>Esker (ref.)*</t>
-  </si>
-  <si>
-    <t>(delisted)</t>
-  </si>
-  <si>
-    <t>O2C SaaS — Bridgepoint/GA acq. 2024</t>
+    <t>FY26 clos 31/12/26 — calendaire 2026 ; marge op. 16,0-16,5% ; FCF ≈ 20%</t>
+  </si>
+  <si>
+    <t>Esker (réf.)*</t>
+  </si>
+  <si>
+    <t>(retirée de la cote)</t>
+  </si>
+  <si>
+    <t>* Deal Bridgepoint/GA 2024 : ~7,7x CA 2024A / ~6,9x NTM (doc offre). Référence M&amp;A, exclue des agrégats.</t>
+  </si>
+  <si>
+    <t>AGRÉGATS (4 peers cotés, hors Esker)</t>
+  </si>
+  <si>
+    <t>Médiane</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>IMPLIED EV SIDETRADE — multiples appliqués aux estimations 2026E Base</t>
+  </si>
+  <si>
+    <t>Sidetrade Revenue 2026E (Base, €m)</t>
+  </si>
+  <si>
+    <t>Sidetrade EBITDA 2026E (Base, €m — incl. CIR)</t>
+  </si>
+  <si>
+    <t>Fourchette</t>
+  </si>
+  <si>
+    <t>Low (min peers)</t>
+  </si>
+  <si>
+    <t>Mid (médiane)</t>
+  </si>
+  <si>
+    <t>High (max peers)</t>
+  </si>
+  <si>
+    <t>Multiple EV/Sales fwd — dérivé de la table</t>
+  </si>
+  <si>
+    <t>EV implicite via EV/Sales (€m)</t>
+  </si>
+  <si>
+    <t>Multiple EV/OpInc (proxy EBITDA) — dérivé de la table</t>
+  </si>
+  <si>
+    <t>EV implicite via proxy EBITDA (€m)</t>
+  </si>
+  <si>
+    <t>Fourchette trading retenue (€m EV)</t>
+  </si>
+  <si>
+    <t>Moyenne des deux méthodes, 100% dérivée de la table : changer un peer change la fourchette et le football field.</t>
+  </si>
+  <si>
+    <t>Lecture au 15/07/2026 : les peers US se sont fortement dératés vs H1-2025 (médiane EV/Sales fwd ~2,6x vs ~4,7x). La fourchette trading devient un PLANCHER de sentiment de marché US — à confronter à l'EV de marché de Sidetrade elle-même (~282 M€ au 15/07, ~3,9x son CA 2026E) : le marché paie déjà Sidetrade au-dessus du haut de fourchette peers. Écart DCF (301) vs comps = débat de prime assumé (croissance organique + profitabilité + small-cap FR vs mid-caps US), pas une convergence.</t>
+  </si>
+  <si>
+    <t>TRANSACTION COMPS — Precedent M&amp;A in Office-of-CFO / O2C / Fintech SaaS  (control transactions)</t>
+  </si>
+  <si>
+    <t>All deals include control premium (30-50% vs. trading). Faits verifies et corriges le 15-Jul-2026 (audit 4.5): Billtrust-&gt;EQT, Bottomline-&gt;Thoma Bravo, Esker EV/CA restates.</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Acquirer</t>
+  </si>
+  <si>
+    <t>Segment</t>
+  </si>
+  <si>
+    <t>LTM Rev (€m)</t>
+  </si>
+  <si>
+    <t>LTM EBITDA (€m)</t>
+  </si>
+  <si>
+    <t>EV/Sales</t>
+  </si>
+  <si>
+    <t>EV/EBITDA</t>
+  </si>
+  <si>
+    <t>Esker</t>
+  </si>
+  <si>
+    <t>Bridgepoint / GA</t>
+  </si>
+  <si>
+    <t>O2C / AR automation (France)</t>
   </si>
   <si>
     <t>"n.m."</t>
   </si>
   <si>
-    <t>* Last traded pre-announcement. Deal 2024: ~7,7x CA 2024A / ~6,9x FY25E Sales (doc offre). EBITDA n.d.</t>
-  </si>
-  <si>
-    <t>AGGREGATES (excl. Esker * reference row — row 9)</t>
+    <t>Offre 262 EUR/action (sept. 2024): equity ~1 619 M, EV ~1 576 M; ~7,7x CA 2024A (205,3 M). Doc offre: moyenne transactions ~6,8x NTM Sales. EBITDA LTM non retraite -&gt; exclu des agregats.</t>
+  </si>
+  <si>
+    <t>Coupa</t>
+  </si>
+  <si>
+    <t>Thoma Bravo</t>
+  </si>
+  <si>
+    <t>Source-to-pay / procurement</t>
+  </si>
+  <si>
+    <t>~$8B; ~11× Sales; EBITDA near breakeven at time of deal</t>
+  </si>
+  <si>
+    <t>Billtrust</t>
+  </si>
+  <si>
+    <t>EQT Private Equity</t>
+  </si>
+  <si>
+    <t>AR invoicing / cash app SaaS</t>
+  </si>
+  <si>
+    <t>~USD 1,7 Md take-private (annonce sept. 2022); ~9x Sales; scale player AR automation</t>
+  </si>
+  <si>
+    <t>Pagero</t>
+  </si>
+  <si>
+    <t>Thomson Reuters</t>
+  </si>
+  <si>
+    <t>E-invoicing / tax compliance</t>
+  </si>
+  <si>
+    <t>SEK 7.3B (~€0.6B); ~6.7× Sales; ~33× EBITDA</t>
+  </si>
+  <si>
+    <t>Bottomline Tech.</t>
+  </si>
+  <si>
+    <t>B2B payments / cash management</t>
+  </si>
+  <si>
+    <t>~$2.6B; ~5.4× Sales; ~26× EBITDA. Mature but OCF-positive</t>
+  </si>
+  <si>
+    <t>AGGREGATES</t>
   </si>
   <si>
     <t>Median</t>
   </si>
   <si>
-    <t>Min</t>
-  </si>
-  <si>
-    <t>Max</t>
-  </si>
-  <si>
-    <t>IMPLIED EV FOR SIDETRADE — applying multiples to 2026E Base estimates</t>
-  </si>
-  <si>
-    <t>Sidetrade Revenue 2026E (Base, €m)</t>
-  </si>
-  <si>
-    <t>Sidetrade EBITDA 2026E (Base, €m)</t>
-  </si>
-  <si>
-    <t>Implied EV range</t>
-  </si>
-  <si>
-    <t>Low (3.0× / 12×)</t>
-  </si>
-  <si>
-    <t>Median (4.8× / 22×)</t>
-  </si>
-  <si>
-    <t>High (6.9× / 35×)</t>
-  </si>
-  <si>
-    <t>Multiple used — EV/Sales</t>
-  </si>
-  <si>
-    <t>Implied EV via EV/Sales (€m)</t>
-  </si>
-  <si>
-    <t>Multiple used — EV/EBITDA</t>
-  </si>
-  <si>
-    <t>Implied EV via EV/EBITDA (€m)</t>
-  </si>
-  <si>
-    <t>Selected trading comp range  (€m EV)</t>
-  </si>
-  <si>
-    <t>Derive: moyenne des EV implicites Sales/EBITDA aux multiples retenus (l.21/23). Plus de midpoint saisi en dur (audit 4.4) - la fourchette bouge si les multiples ou le DCF bougent.</t>
-  </si>
-  <si>
-    <t>* Esker (row 9): taken private. Included as directional reference only; use Transaction_comps for control multiples.</t>
-  </si>
-  <si>
-    <t>TRANSACTION COMPS — Precedent M&amp;A in Office-of-CFO / O2C / Fintech SaaS  (control transactions)</t>
-  </si>
-  <si>
-    <t>All deals include control premium (30-50% vs. trading). Faits verifies et corriges le 15-Jul-2026 (audit 4.5): Billtrust-&gt;EQT, Bottomline-&gt;Thoma Bravo, Esker EV/CA restates.</t>
-  </si>
-  <si>
-    <t>Target</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>Acquirer</t>
-  </si>
-  <si>
-    <t>Segment</t>
-  </si>
-  <si>
-    <t>LTM Rev (€m)</t>
-  </si>
-  <si>
-    <t>LTM EBITDA (€m)</t>
-  </si>
-  <si>
-    <t>EV/Sales</t>
-  </si>
-  <si>
-    <t>EV/EBITDA</t>
-  </si>
-  <si>
-    <t>Esker</t>
-  </si>
-  <si>
-    <t>Bridgepoint / GA</t>
-  </si>
-  <si>
-    <t>O2C / AR automation (France)</t>
-  </si>
-  <si>
-    <t>Offre 262 EUR/action (sept. 2024): equity ~1 619 M, EV ~1 576 M; ~7,7x CA 2024A (205,3 M). Doc offre: moyenne transactions ~6,8x NTM Sales. EBITDA LTM non retraite -&gt; exclu des agregats.</t>
-  </si>
-  <si>
-    <t>Coupa</t>
-  </si>
-  <si>
-    <t>Thoma Bravo</t>
-  </si>
-  <si>
-    <t>Source-to-pay / procurement</t>
-  </si>
-  <si>
-    <t>~$8B; ~11× Sales; EBITDA near breakeven at time of deal</t>
-  </si>
-  <si>
-    <t>Billtrust</t>
-  </si>
-  <si>
-    <t>EQT Private Equity</t>
-  </si>
-  <si>
-    <t>AR invoicing / cash app SaaS</t>
-  </si>
-  <si>
-    <t>~USD 1,7 Md take-private (annonce sept. 2022); ~9x Sales; scale player AR automation</t>
-  </si>
-  <si>
-    <t>Pagero</t>
-  </si>
-  <si>
-    <t>Thomson Reuters</t>
-  </si>
-  <si>
-    <t>E-invoicing / tax compliance</t>
-  </si>
-  <si>
-    <t>SEK 7.3B (~€0.6B); ~6.7× Sales; ~33× EBITDA</t>
-  </si>
-  <si>
-    <t>Bottomline Tech.</t>
-  </si>
-  <si>
-    <t>B2B payments / cash management</t>
-  </si>
-  <si>
-    <t>~$2.6B; ~5.4× Sales; ~26× EBITDA. Mature but OCF-positive</t>
-  </si>
-  <si>
-    <t>AGGREGATES</t>
-  </si>
-  <si>
     <t>Coupa (161x n/m) et Esker (EBITDA n.d.) exclus des agregats EV/EBITDA</t>
   </si>
   <si>
@@ -2097,6 +2085,12 @@
     <t>to</t>
   </si>
   <si>
+    <t>MARKET CHECK — EV de marché Sidetrade (ALBFR) au 15/07/2026</t>
+  </si>
+  <si>
+    <t>Cours 174,00 € (+0,35%, fourchette du jour 170,00-175,20) x 1 536 790 actions diluées + dette nette stricte 14,7. Le DCF Base (301) ressort ~7% au-dessus du marché ; le marché paie Sidetrade au-dessus du haut de fourchette des peers US dératés.</t>
+  </si>
+  <si>
     <t>VISUAL RANGE MAP  (0 – 600 €m scale)</t>
   </si>
   <si>
@@ -2262,7 +2256,7 @@
     <t>Terminal value weight</t>
   </si>
   <si>
-    <t>Gordon Growth TV = 77.2% of total EV at Base (WACC 9.5%, TG 2.5%) — mechanically high with a 5-year explicit horizon (Cantor, with a much longer explicit + fade period, gets 61%). Exit-multiple cross-check at 15x gives EV ~413m, i.e. +37% ABOVE Gordon — the cross-check sits above, NOT ~10% below as previously stated (caveat corrected 15-Jul-2026, audit §4.2).</t>
+    <t>Gordon Growth TV = 77.2% of total EV at Base (WACC 9.5%, TG 2.5%) — mechanically high with a 5-year explicit horizon (Cantor, with a much longer explicit + fade period, gets 61%). Exit-multiple cross-check at 15x gives EV ~413m, i.e. +37% ABOVE Gordon — the cross-check sits above, NOT ~10% below as previously stated (corrected 15-Jul-2026). ANCHORING of the 15x (updated 15-Jul-2026): it now sits ABOVE derated US peers (~12.6x median op-income proxy) but ~30% BELOW Sidetrade's own current market multiple (~21x EBITDA FY25 at €174/share) — the exit is anchored on the asset's own trading level, not on US peer sentiment; 12x is the stress anchor (Sensitivity/LBO tables).</t>
   </si>
   <si>
     <t>TV = 77.2% of Base EV; ±15-20% EV per ±1% WACC or TG. See Sensitivity tab.</t>
@@ -2305,6 +2299,18 @@
   </si>
   <si>
     <t>Use normalized FCF as DCF starting point. Statutory FCF is the downside sensitivity.</t>
+  </si>
+  <si>
+    <t>Comps refresh 15/07/2026 — peer derating</t>
+  </si>
+  <si>
+    <t>US peers derated sharply vs H1-2025 (median fwd EV/Sales ~2.6x vs ~4.7x; op-income proxy ~12.6x vs ~30x EBITDA). Trading range falls to 171/202/264 and now sits BELOW Sidetrade's own market EV (~282 at 15-Jul-2026). Reading: the peer set is a US-sentiment floor, not the value; the market already pays Sidetrade a premium (organic growth + profitability + FR small-cap scarcity). DCF (301) vs market (282) gap is ~7% — the model's central tension is DCF/market vs peers, an assumed premium debate, not a convergence story.</t>
+  </si>
+  <si>
+    <t>Trading range −45% vs previous refresh; DCF unchanged</t>
+  </si>
+  <si>
+    <t>Re-refresh quotes before any external use; keep the premium-debate framing explicit in interviews.</t>
   </si>
   <si>
     <t>CHECKS — CONTRÔLES D'INTÉGRITÉ DU CLASSEUR (ajouté 15/07/2026, audit §10.3)</t>
@@ -2388,7 +2394,7 @@
     <numFmt numFmtId="174" formatCode="0.00&quot;x&quot;"/>
     <numFmt numFmtId="175" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="41" x14ac:knownFonts="1">
+  <fonts count="45" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2650,8 +2656,28 @@
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF808080"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF008000"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="19">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2753,6 +2779,11 @@
         <fgColor rgb="FFD9E2F3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E2F3"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -2775,7 +2806,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="168">
+  <cellXfs count="197">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3043,6 +3074,55 @@
     <xf numFmtId="0" fontId="40" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="36" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="43" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="43" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="43" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="172" fontId="42" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="42" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="41" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="43" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="43" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="43" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="172" fontId="42" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="42" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="41" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="36" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3075,6 +3155,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3353,31 +3439,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="162" t="s">
+      <c r="A1" s="189" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="156"/>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
-      <c r="E1" s="156"/>
+      <c r="B1" s="183"/>
+      <c r="C1" s="183"/>
+      <c r="D1" s="183"/>
+      <c r="E1" s="183"/>
     </row>
     <row r="2" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="161" t="s">
+      <c r="A2" s="188" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="156"/>
-      <c r="C2" s="156"/>
-      <c r="D2" s="156"/>
-      <c r="E2" s="156"/>
+      <c r="B2" s="183"/>
+      <c r="C2" s="183"/>
+      <c r="D2" s="183"/>
+      <c r="E2" s="183"/>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="158" t="s">
+      <c r="A4" s="185" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="156"/>
-      <c r="C4" s="156"/>
-      <c r="D4" s="156"/>
-      <c r="E4" s="156"/>
+      <c r="B4" s="183"/>
+      <c r="C4" s="183"/>
+      <c r="D4" s="183"/>
+      <c r="E4" s="183"/>
     </row>
     <row r="5" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
@@ -3465,13 +3551,13 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="158" t="s">
+      <c r="A11" s="185" t="s">
         <v>55</v>
       </c>
-      <c r="B11" s="156"/>
-      <c r="C11" s="156"/>
-      <c r="D11" s="156"/>
-      <c r="E11" s="156"/>
+      <c r="B11" s="183"/>
+      <c r="C11" s="183"/>
+      <c r="D11" s="183"/>
+      <c r="E11" s="183"/>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
@@ -3486,13 +3572,13 @@
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="158" t="s">
+      <c r="A14" s="185" t="s">
         <v>58</v>
       </c>
-      <c r="B14" s="156"/>
-      <c r="C14" s="156"/>
-      <c r="D14" s="156"/>
-      <c r="E14" s="156"/>
+      <c r="B14" s="183"/>
+      <c r="C14" s="183"/>
+      <c r="D14" s="183"/>
+      <c r="E14" s="183"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B15" s="15" t="s">
@@ -3534,15 +3620,15 @@
       </c>
       <c r="B17" s="23">
         <f>Trading_comps!E26</f>
-        <v>211</v>
+        <v>171</v>
       </c>
       <c r="C17" s="23">
         <f>Trading_comps!F26</f>
-        <v>361</v>
+        <v>202</v>
       </c>
       <c r="D17" s="23">
         <f>Trading_comps!G26</f>
-        <v>548</v>
+        <v>264</v>
       </c>
       <c r="E17" s="24" t="s">
         <v>66</v>
@@ -3589,13 +3675,13 @@
       </c>
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="158" t="s">
+      <c r="A21" s="185" t="s">
         <v>71</v>
       </c>
-      <c r="B21" s="156"/>
-      <c r="C21" s="156"/>
-      <c r="D21" s="156"/>
-      <c r="E21" s="156"/>
+      <c r="B21" s="183"/>
+      <c r="C21" s="183"/>
+      <c r="D21" s="183"/>
+      <c r="E21" s="183"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
@@ -3634,13 +3720,13 @@
       </c>
     </row>
     <row r="27" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="158" t="s">
+      <c r="A27" s="185" t="s">
         <v>76</v>
       </c>
-      <c r="B27" s="156"/>
-      <c r="C27" s="156"/>
-      <c r="D27" s="156"/>
-      <c r="E27" s="156"/>
+      <c r="B27" s="183"/>
+      <c r="C27" s="183"/>
+      <c r="D27" s="183"/>
+      <c r="E27" s="183"/>
     </row>
     <row r="28" spans="1:5" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="26" t="s">
@@ -3726,85 +3812,85 @@
       </c>
     </row>
     <row r="35" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="157" t="s">
+      <c r="A35" s="184" t="s">
         <v>89</v>
       </c>
-      <c r="B35" s="156"/>
-      <c r="C35" s="156"/>
-      <c r="D35" s="156"/>
-      <c r="E35" s="156"/>
+      <c r="B35" s="183"/>
+      <c r="C35" s="183"/>
+      <c r="D35" s="183"/>
+      <c r="E35" s="183"/>
     </row>
     <row r="36" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="160" t="s">
+      <c r="A36" s="187" t="s">
         <v>90</v>
       </c>
-      <c r="B36" s="156"/>
-      <c r="C36" s="156"/>
-      <c r="D36" s="156"/>
-      <c r="E36" s="156"/>
+      <c r="B36" s="183"/>
+      <c r="C36" s="183"/>
+      <c r="D36" s="183"/>
+      <c r="E36" s="183"/>
     </row>
     <row r="37" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="159" t="s">
+      <c r="A37" s="186" t="s">
         <v>91</v>
       </c>
-      <c r="B37" s="156"/>
-      <c r="C37" s="156"/>
-      <c r="D37" s="156"/>
-      <c r="E37" s="156"/>
+      <c r="B37" s="183"/>
+      <c r="C37" s="183"/>
+      <c r="D37" s="183"/>
+      <c r="E37" s="183"/>
     </row>
     <row r="38" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="160" t="s">
+      <c r="A38" s="187" t="s">
         <v>92</v>
       </c>
-      <c r="B38" s="156"/>
-      <c r="C38" s="156"/>
-      <c r="D38" s="156"/>
-      <c r="E38" s="156"/>
+      <c r="B38" s="183"/>
+      <c r="C38" s="183"/>
+      <c r="D38" s="183"/>
+      <c r="E38" s="183"/>
     </row>
     <row r="39" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="159" t="s">
+      <c r="A39" s="186" t="s">
         <v>93</v>
       </c>
-      <c r="B39" s="156"/>
-      <c r="C39" s="156"/>
-      <c r="D39" s="156"/>
-      <c r="E39" s="156"/>
+      <c r="B39" s="183"/>
+      <c r="C39" s="183"/>
+      <c r="D39" s="183"/>
+      <c r="E39" s="183"/>
     </row>
     <row r="40" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="160" t="s">
+      <c r="A40" s="187" t="s">
         <v>94</v>
       </c>
-      <c r="B40" s="156"/>
-      <c r="C40" s="156"/>
-      <c r="D40" s="156"/>
-      <c r="E40" s="156"/>
+      <c r="B40" s="183"/>
+      <c r="C40" s="183"/>
+      <c r="D40" s="183"/>
+      <c r="E40" s="183"/>
     </row>
     <row r="41" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="159" t="s">
+      <c r="A41" s="186" t="s">
         <v>95</v>
       </c>
-      <c r="B41" s="156"/>
-      <c r="C41" s="156"/>
-      <c r="D41" s="156"/>
-      <c r="E41" s="156"/>
+      <c r="B41" s="183"/>
+      <c r="C41" s="183"/>
+      <c r="D41" s="183"/>
+      <c r="E41" s="183"/>
     </row>
     <row r="42" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="160" t="s">
+      <c r="A42" s="187" t="s">
         <v>96</v>
       </c>
-      <c r="B42" s="156"/>
-      <c r="C42" s="156"/>
-      <c r="D42" s="156"/>
-      <c r="E42" s="156"/>
+      <c r="B42" s="183"/>
+      <c r="C42" s="183"/>
+      <c r="D42" s="183"/>
+      <c r="E42" s="183"/>
     </row>
     <row r="43" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="159" t="s">
+      <c r="A43" s="186" t="s">
         <v>97</v>
       </c>
-      <c r="B43" s="156"/>
-      <c r="C43" s="156"/>
-      <c r="D43" s="156"/>
-      <c r="E43" s="156"/>
+      <c r="B43" s="183"/>
+      <c r="C43" s="183"/>
+      <c r="D43" s="183"/>
+      <c r="E43" s="183"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -3842,22 +3928,22 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="117" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="118" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="118" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="119" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B4" s="120"/>
       <c r="C4" s="120"/>
@@ -3870,7 +3956,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="121" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="B5" s="122"/>
       <c r="C5" s="122"/>
@@ -3883,7 +3969,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="123" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="B6" s="130">
         <f>B27</f>
@@ -3900,7 +3986,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="123" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="B7" s="137">
         <f>B29</f>
@@ -3917,7 +4003,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="121" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="B9" s="121" t="s">
         <v>101</v>
@@ -3936,7 +4022,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="123" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="B10" s="130">
         <f>B50</f>
@@ -3953,7 +4039,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="131" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="B11" s="138">
         <f>C112</f>
@@ -3970,7 +4056,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="123" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B12" s="136">
         <f>C113</f>
@@ -3987,7 +4073,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="123" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="B13" s="139">
         <f>B68</f>
@@ -4004,16 +4090,16 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="121" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="B15" s="121" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="C15" s="121" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="D15" s="121" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="E15" s="122"/>
       <c r="F15" s="122"/>
@@ -4035,7 +4121,7 @@
         <v>157.19999999999999</v>
       </c>
       <c r="I16" s="118" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -4052,7 +4138,7 @@
         <v>222.5</v>
       </c>
       <c r="I17" s="118" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -4071,7 +4157,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="119" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="B21" s="120"/>
       <c r="C21" s="120"/>
@@ -4087,10 +4173,10 @@
         <v>100</v>
       </c>
       <c r="B22" s="121" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="C22" s="121" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="D22" s="122"/>
       <c r="E22" s="122"/>
@@ -4098,349 +4184,349 @@
       <c r="G22" s="122"/>
       <c r="H22" s="122"/>
       <c r="I22" s="121" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="123" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="B23" s="124">
         <v>2.3730000000000001E-2</v>
       </c>
       <c r="C23" s="123" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="I23" s="118" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="123" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="B24" s="124">
         <v>4.7899999999999998E-2</v>
       </c>
       <c r="C24" s="123" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="I24" s="118" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="123" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="B25" s="125">
         <f>B23+B24</f>
         <v>7.1629999999999999E-2</v>
       </c>
       <c r="C25" s="123" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="I25" s="118" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="123" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="B26" s="126">
         <v>4</v>
       </c>
       <c r="C26" s="123" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="I26" s="118" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="123" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B27" s="127">
         <f>B26*Inputs!B7</f>
         <v>53.536000000000001</v>
       </c>
       <c r="C27" s="123" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="I27" s="118" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="123" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="B28" s="124">
         <v>0.01</v>
       </c>
       <c r="C28" s="123" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="I28" s="118" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="123" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="B29" s="124">
         <v>0.75</v>
       </c>
       <c r="C29" s="123" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="I29" s="118" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="123" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="B30" s="128">
         <v>8</v>
       </c>
       <c r="C30" s="123" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="I30" s="118" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="123" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="B31" s="124">
         <v>0.03</v>
       </c>
       <c r="C31" s="123" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="I31" s="118" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="123" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="B32" s="124">
         <v>0.03</v>
       </c>
       <c r="C32" s="123" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="I32" s="118" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="123" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="B33" s="128">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="C33" s="123" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="I33" s="118" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="123" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="B34" s="124">
         <v>0.35</v>
       </c>
       <c r="C34" s="123" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="I34" s="118" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="123" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="B35" s="124">
         <v>0.35</v>
       </c>
       <c r="C35" s="123" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="I35" s="118" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="123" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="B36" s="126">
         <v>15</v>
       </c>
       <c r="C36" s="123" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="I36" s="118" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="123" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="B37" s="124">
         <v>0.25</v>
       </c>
       <c r="C37" s="123" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="I37" s="118" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="123" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="B38" s="124">
         <v>3.3000000000000002E-2</v>
       </c>
       <c r="C38" s="123" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="I38" s="118" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="123" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="B39" s="128">
         <v>0.76300000000000001</v>
       </c>
       <c r="C39" s="123" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="I39" s="118" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="123" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="B40" s="127">
         <f>Inputs!B34</f>
         <v>3.5</v>
       </c>
       <c r="C40" s="123" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="I40" s="118" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="123" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="B41" s="127">
         <f>FY25_base!B49</f>
         <v>14.654</v>
       </c>
       <c r="C41" s="123" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="I41" s="118" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="123" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="B42" s="127">
         <f>FY25_base!B46</f>
         <v>30.981000000000002</v>
       </c>
       <c r="C42" s="123" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="I42" s="118" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="123" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="B43" s="127">
         <f>-(FY25_base!B47+FY25_base!B48)</f>
         <v>16.327000000000002</v>
       </c>
       <c r="C43" s="123" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="I43" s="118" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="123" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="B44" s="128">
         <v>0.45500000000000002</v>
       </c>
       <c r="C44" s="123" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="I44" s="118" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="123" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="B45" s="128">
         <v>1.4590000000000001</v>
       </c>
       <c r="C45" s="123" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="I45" s="118" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="123" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="B46" s="129">
         <v>5</v>
       </c>
       <c r="C46" s="123" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="I46" s="118" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -4452,15 +4538,15 @@
         <v>13.384</v>
       </c>
       <c r="C47" s="123" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="I47" s="118" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="121" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="B49" s="121" t="s">
         <v>101</v>
@@ -4479,7 +4565,7 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="123" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="B50" s="128">
         <v>169.7</v>
@@ -4491,12 +4577,12 @@
         <v>297.3</v>
       </c>
       <c r="I50" s="118" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="119" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="B53" s="120"/>
       <c r="C53" s="120"/>
@@ -4528,7 +4614,7 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="123" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="B55" s="130">
         <f>B50-$B$41</f>
@@ -4543,12 +4629,12 @@
         <v>282.64600000000002</v>
       </c>
       <c r="I55" s="118" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="123" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="B56" s="130">
         <f>$B$42</f>
@@ -4563,12 +4649,12 @@
         <v>30.981000000000002</v>
       </c>
       <c r="I56" s="118" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="123" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="B57" s="130">
         <f>$B$44</f>
@@ -4583,12 +4669,12 @@
         <v>0.45500000000000002</v>
       </c>
       <c r="I57" s="118" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="123" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="B58" s="130">
         <f>$B$45</f>
@@ -4603,12 +4689,12 @@
         <v>1.4590000000000001</v>
       </c>
       <c r="I58" s="118" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="123" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="B59" s="130">
         <f>B50*$B$31</f>
@@ -4623,12 +4709,12 @@
         <v>8.9190000000000005</v>
       </c>
       <c r="I59" s="118" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="123" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="B60" s="130">
         <f>$B$27*$B$32</f>
@@ -4643,12 +4729,12 @@
         <v>1.60608</v>
       </c>
       <c r="I60" s="118" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="123" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="B61" s="130">
         <f>$B$30</f>
@@ -4663,12 +4749,12 @@
         <v>8</v>
       </c>
       <c r="I61" s="118" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="131" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="B62" s="132">
         <f>SUM(B55:B61)</f>
@@ -4685,7 +4771,7 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="123" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="B63" s="130">
         <f>$B$27</f>
@@ -4700,12 +4786,12 @@
         <v>53.536000000000001</v>
       </c>
       <c r="I63" s="118" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="123" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="B64" s="130">
         <f>$B$43</f>
@@ -4720,12 +4806,12 @@
         <v>16.327000000000002</v>
       </c>
       <c r="I64" s="118" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="123" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="B65" s="130">
         <f>$B$34*$B$35*B55</f>
@@ -4740,12 +4826,12 @@
         <v>34.624134999999995</v>
       </c>
       <c r="I65" s="118" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="123" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="B66" s="130">
         <f>B62-B63-B64-B65</f>
@@ -4762,7 +4848,7 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="131" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B67" s="132">
         <f>SUM(B63:B66)</f>
@@ -4779,7 +4865,7 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="131" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="B68" s="133">
         <f>B67-B62</f>
@@ -4794,12 +4880,12 @@
         <v>0</v>
       </c>
       <c r="I68" s="118" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="119" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="B70" s="119" t="s">
         <v>101</v>
@@ -4818,7 +4904,7 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="123" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="B71" s="130">
         <f>$B$27-$B$30</f>
@@ -4827,19 +4913,19 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="123" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="B72" s="134">
         <f>B71/$B$47</f>
         <v>3.4022713687985653</v>
       </c>
       <c r="I72" s="118" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="123" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="B73" s="130">
         <f>B50-$B71</f>
@@ -4856,7 +4942,7 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="123" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="B74" s="125">
         <f>B65/B73</f>
@@ -4871,12 +4957,12 @@
         <v>0.13752615544716479</v>
       </c>
       <c r="I74" s="118" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="123" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="B75" s="125">
         <f>1-B74</f>
@@ -4893,7 +4979,7 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="119" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="B80" s="120"/>
       <c r="C80" s="120"/>
@@ -4906,7 +4992,7 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="121" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="B81" s="121"/>
       <c r="C81" s="121" t="s">
@@ -4929,7 +5015,7 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="123" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="C82" s="127">
         <f>DCF!B7</f>
@@ -4954,7 +5040,7 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="123" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="C83" s="127">
         <f>DCF!B12</f>
@@ -4979,7 +5065,7 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="123" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="C84" s="127">
         <f>DCF!B13</f>
@@ -5004,7 +5090,7 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="123" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="C85" s="127">
         <f>DCF!B14</f>
@@ -5029,7 +5115,7 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="123" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C86" s="127">
         <f>DCF!B19</f>
@@ -5054,7 +5140,7 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="123" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="C87" s="127">
         <f>DCF!B20</f>
@@ -5079,7 +5165,7 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="121" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="B88" s="122"/>
       <c r="C88" s="122"/>
@@ -5092,7 +5178,7 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="123" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="C89" s="130">
         <f>$B$27</f>
@@ -5117,7 +5203,7 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="123" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="C90" s="130">
         <f>C89*$B$25</f>
@@ -5142,7 +5228,7 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="123" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="C91" s="130">
         <f>$B$33</f>
@@ -5167,7 +5253,7 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="123" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="C92" s="130">
         <f>C90+C91</f>
@@ -5192,7 +5278,7 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="123" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="C93" s="130">
         <f>MAX(3,0.3*C83)</f>
@@ -5217,7 +5303,7 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="123" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="C94" s="130">
         <f>MIN(C92,C93)</f>
@@ -5242,7 +5328,7 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="123" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="C95" s="130">
         <f>0+C92-C94</f>
@@ -5267,7 +5353,7 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="123" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="C96" s="130">
         <f>C85-$B$40-C94</f>
@@ -5292,7 +5378,7 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="123" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="C97" s="130">
         <f>MAX(0,$B$37*C96)</f>
@@ -5317,7 +5403,7 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="123" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C98" s="130">
         <f>$B$38*MAX(0,C97-$B$39)</f>
@@ -5342,7 +5428,7 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="123" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="C99" s="130">
         <f>MAX(0,C97+C98)</f>
@@ -5367,7 +5453,7 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="131" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="C100" s="132">
         <f>C85-C92-C99</f>
@@ -5392,7 +5478,7 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="123" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="C101" s="130">
         <f>MIN($B$28*$B$27,C89)</f>
@@ -5417,7 +5503,7 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="123" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="C102" s="130">
         <f>$B$30+C100+C84+C86+C87-C101</f>
@@ -5442,7 +5528,7 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="123" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="C103" s="130">
         <f>MAX(0,C102-$B$30)</f>
@@ -5467,7 +5553,7 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="123" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="C104" s="130">
         <f>MIN($B$29*C103,C89-C101)</f>
@@ -5492,7 +5578,7 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="131" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="C105" s="132">
         <f>C89-C101-C104</f>
@@ -5517,7 +5603,7 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="131" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="C106" s="132">
         <f>C102-C104</f>
@@ -5542,7 +5628,7 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="121" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="B107" s="122"/>
       <c r="C107" s="122"/>
@@ -5555,7 +5641,7 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="123" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="C108" s="130">
         <f>G83*$B$36</f>
@@ -5564,7 +5650,7 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="123" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="C109" s="130">
         <f>C108-G105+G106</f>
@@ -5573,7 +5659,7 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="123" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="C110" s="130">
         <f>C109*(1-B74)</f>
@@ -5582,7 +5668,7 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="123" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="C111" s="130">
         <f>B66</f>
@@ -5591,19 +5677,19 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="131" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="C112" s="135">
         <f>(C110/C111)^(1/5)-1</f>
         <v>0.22509032702462251</v>
       </c>
       <c r="I112" s="118" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="123" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="C113" s="136">
         <f>C110/C111</f>
@@ -5612,7 +5698,7 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="119" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="B118" s="120"/>
       <c r="C118" s="120"/>
@@ -5625,7 +5711,7 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="121" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="B119" s="121"/>
       <c r="C119" s="121" t="s">
@@ -5648,7 +5734,7 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="123" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="C120" s="127">
         <f>DCF!C7</f>
@@ -5673,7 +5759,7 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="123" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="C121" s="127">
         <f>DCF!C12</f>
@@ -5698,7 +5784,7 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="123" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="C122" s="127">
         <f>DCF!C13</f>
@@ -5723,7 +5809,7 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="123" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="C123" s="127">
         <f>DCF!C14</f>
@@ -5748,7 +5834,7 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="123" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C124" s="127">
         <f>DCF!C19</f>
@@ -5773,7 +5859,7 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="123" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="C125" s="127">
         <f>DCF!C20</f>
@@ -5798,7 +5884,7 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="121" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="B126" s="122"/>
       <c r="C126" s="122"/>
@@ -5811,7 +5897,7 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="123" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="C127" s="130">
         <f>$B$27</f>
@@ -5836,7 +5922,7 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="123" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="C128" s="130">
         <f>C127*$B$25</f>
@@ -5861,7 +5947,7 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="123" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="C129" s="130">
         <f>$B$33</f>
@@ -5886,7 +5972,7 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="123" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="C130" s="130">
         <f>C128+C129</f>
@@ -5911,7 +5997,7 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="123" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="C131" s="130">
         <f>MAX(3,0.3*C121)</f>
@@ -5936,7 +6022,7 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="123" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="C132" s="130">
         <f>MIN(C130,C131)</f>
@@ -5961,7 +6047,7 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="123" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="C133" s="130">
         <f>0+C130-C132</f>
@@ -5986,7 +6072,7 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="123" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="C134" s="130">
         <f>C123-$B$40-C132</f>
@@ -6011,7 +6097,7 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="123" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="C135" s="130">
         <f>MAX(0,$B$37*C134)</f>
@@ -6036,7 +6122,7 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="123" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C136" s="130">
         <f>$B$38*MAX(0,C135-$B$39)</f>
@@ -6061,7 +6147,7 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="123" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="C137" s="130">
         <f>MAX(0,C135+C136)</f>
@@ -6086,7 +6172,7 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="131" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="C138" s="132">
         <f>C123-C130-C137</f>
@@ -6111,7 +6197,7 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="123" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="C139" s="130">
         <f>MIN($B$28*$B$27,C127)</f>
@@ -6136,7 +6222,7 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="123" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="C140" s="130">
         <f>$B$30+C138+C122+C124+C125-C139</f>
@@ -6161,7 +6247,7 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="123" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="C141" s="130">
         <f>MAX(0,C140-$B$30)</f>
@@ -6186,7 +6272,7 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="123" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="C142" s="130">
         <f>MIN($B$29*C141,C127-C139)</f>
@@ -6211,7 +6297,7 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="131" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="C143" s="132">
         <f>C127-C139-C142</f>
@@ -6236,7 +6322,7 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="131" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="C144" s="132">
         <f>C140-C142</f>
@@ -6261,7 +6347,7 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="121" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="B145" s="122"/>
       <c r="C145" s="122"/>
@@ -6274,7 +6360,7 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="123" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="C146" s="130">
         <f>G121*$B$36</f>
@@ -6283,7 +6369,7 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="123" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="C147" s="130">
         <f>C146-G143+G144</f>
@@ -6292,7 +6378,7 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="123" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="C148" s="130">
         <f>C147*(1-C74)</f>
@@ -6301,7 +6387,7 @@
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="123" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="C149" s="130">
         <f>C66</f>
@@ -6310,19 +6396,19 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="131" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="C150" s="135">
         <f>(C148/C149)^(1/5)-1</f>
         <v>0.22503769786231054</v>
       </c>
       <c r="I150" s="118" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="123" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="C151" s="136">
         <f>C148/C149</f>
@@ -6331,7 +6417,7 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="119" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="B156" s="120"/>
       <c r="C156" s="120"/>
@@ -6344,7 +6430,7 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="121" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="B157" s="121"/>
       <c r="C157" s="121" t="s">
@@ -6367,7 +6453,7 @@
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="123" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="C158" s="127">
         <f>DCF!D7</f>
@@ -6392,7 +6478,7 @@
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="123" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="C159" s="127">
         <f>DCF!D12</f>
@@ -6417,7 +6503,7 @@
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="123" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="C160" s="127">
         <f>DCF!D13</f>
@@ -6442,7 +6528,7 @@
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="123" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="C161" s="127">
         <f>DCF!D14</f>
@@ -6467,7 +6553,7 @@
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="123" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C162" s="127">
         <f>DCF!D19</f>
@@ -6492,7 +6578,7 @@
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="123" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="C163" s="127">
         <f>DCF!D20</f>
@@ -6517,7 +6603,7 @@
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="121" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="B164" s="122"/>
       <c r="C164" s="122"/>
@@ -6530,7 +6616,7 @@
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="123" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="C165" s="130">
         <f>$B$27</f>
@@ -6555,7 +6641,7 @@
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="123" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="C166" s="130">
         <f>C165*$B$25</f>
@@ -6580,7 +6666,7 @@
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="123" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="C167" s="130">
         <f>$B$33</f>
@@ -6605,7 +6691,7 @@
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="123" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="C168" s="130">
         <f>C166+C167</f>
@@ -6630,7 +6716,7 @@
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="123" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="C169" s="130">
         <f>MAX(3,0.3*C159)</f>
@@ -6655,7 +6741,7 @@
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="123" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="C170" s="130">
         <f>MIN(C168,C169)</f>
@@ -6680,7 +6766,7 @@
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="123" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="C171" s="130">
         <f>0+C168-C170</f>
@@ -6705,7 +6791,7 @@
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="123" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="C172" s="130">
         <f>C161-$B$40-C170</f>
@@ -6730,7 +6816,7 @@
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="123" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="C173" s="130">
         <f>MAX(0,$B$37*C172)</f>
@@ -6755,7 +6841,7 @@
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="123" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C174" s="130">
         <f>$B$38*MAX(0,C173-$B$39)</f>
@@ -6780,7 +6866,7 @@
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="123" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="C175" s="130">
         <f>MAX(0,C173+C174)</f>
@@ -6805,7 +6891,7 @@
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="131" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="C176" s="132">
         <f>C161-C168-C175</f>
@@ -6830,7 +6916,7 @@
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="123" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="C177" s="130">
         <f>MIN($B$28*$B$27,C165)</f>
@@ -6855,7 +6941,7 @@
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="123" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="C178" s="130">
         <f>$B$30+C176+C160+C162+C163-C177</f>
@@ -6880,7 +6966,7 @@
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="123" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="C179" s="130">
         <f>MAX(0,C178-$B$30)</f>
@@ -6905,7 +6991,7 @@
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="123" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="C180" s="130">
         <f>MIN($B$29*C179,C165-C177)</f>
@@ -6930,7 +7016,7 @@
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="131" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="C181" s="132">
         <f>C165-C177-C180</f>
@@ -6955,7 +7041,7 @@
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="131" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="C182" s="132">
         <f>C178-C180</f>
@@ -6980,7 +7066,7 @@
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="121" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="B183" s="122"/>
       <c r="C183" s="122"/>
@@ -6993,7 +7079,7 @@
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" s="123" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="C184" s="130">
         <f>G159*$B$36</f>
@@ -7002,7 +7088,7 @@
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="123" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="C185" s="130">
         <f>C184-G181+G182</f>
@@ -7011,7 +7097,7 @@
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="123" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="C186" s="130">
         <f>C185*(1-D74)</f>
@@ -7020,7 +7106,7 @@
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="123" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="C187" s="130">
         <f>D66</f>
@@ -7029,19 +7115,19 @@
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="131" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="C188" s="135">
         <f>(C186/C187)^(1/5)-1</f>
         <v>0.22495363264703361</v>
       </c>
       <c r="I188" s="118" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" s="123" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="C189" s="136">
         <f>C186/C187</f>
@@ -7050,7 +7136,7 @@
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" s="119" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="B196" s="120"/>
       <c r="C196" s="120"/>
@@ -7063,23 +7149,23 @@
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" s="121" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="B197" s="121" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="C197" s="121" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="D197" s="121" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="E197" s="122"/>
       <c r="F197" s="122"/>
       <c r="G197" s="122"/>
       <c r="H197" s="122"/>
       <c r="I197" s="118" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
@@ -7126,7 +7212,7 @@
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" s="119" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="B203" s="120"/>
       <c r="C203" s="120"/>
@@ -7139,7 +7225,7 @@
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" s="121" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="B204" s="122"/>
       <c r="C204" s="122"/>
@@ -7152,22 +7238,22 @@
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" s="121" t="s">
+        <v>611</v>
+      </c>
+      <c r="B205" s="121" t="s">
+        <v>612</v>
+      </c>
+      <c r="C205" s="121" t="s">
+        <v>613</v>
+      </c>
+      <c r="D205" s="121" t="s">
+        <v>614</v>
+      </c>
+      <c r="E205" s="121" t="s">
         <v>615</v>
       </c>
-      <c r="B205" s="121" t="s">
+      <c r="F205" s="121" t="s">
         <v>616</v>
-      </c>
-      <c r="C205" s="121" t="s">
-        <v>617</v>
-      </c>
-      <c r="D205" s="121" t="s">
-        <v>618</v>
-      </c>
-      <c r="E205" s="121" t="s">
-        <v>619</v>
-      </c>
-      <c r="F205" s="121" t="s">
-        <v>620</v>
       </c>
       <c r="G205" s="122"/>
       <c r="H205" s="122"/>
@@ -7193,7 +7279,7 @@
         <v>0.27110156747905417</v>
       </c>
       <c r="I206" s="118" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
@@ -7278,7 +7364,7 @@
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="121" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="B212" s="122"/>
       <c r="C212" s="122"/>
@@ -7291,22 +7377,22 @@
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="121" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="B213" s="121" t="s">
+        <v>612</v>
+      </c>
+      <c r="C213" s="121" t="s">
+        <v>613</v>
+      </c>
+      <c r="D213" s="121" t="s">
+        <v>614</v>
+      </c>
+      <c r="E213" s="121" t="s">
+        <v>615</v>
+      </c>
+      <c r="F213" s="121" t="s">
         <v>616</v>
-      </c>
-      <c r="C213" s="121" t="s">
-        <v>617</v>
-      </c>
-      <c r="D213" s="121" t="s">
-        <v>618</v>
-      </c>
-      <c r="E213" s="121" t="s">
-        <v>619</v>
-      </c>
-      <c r="F213" s="121" t="s">
-        <v>620</v>
       </c>
       <c r="G213" s="122"/>
       <c r="H213" s="122"/>
@@ -7314,7 +7400,7 @@
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="123" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="B214" s="137">
         <v>0.1145288791638157</v>
@@ -7332,12 +7418,12 @@
         <v>0.21223737156791561</v>
       </c>
       <c r="I214" s="118" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="123" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="B215" s="137">
         <v>0.1158470645624543</v>
@@ -7357,7 +7443,7 @@
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="123" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="B216" s="137">
         <v>0.11711132812578651</v>
@@ -7377,7 +7463,7 @@
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="123" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="B217" s="137">
         <v>0.1183258062810979</v>
@@ -7397,7 +7483,7 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="123" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="B218" s="137">
         <v>0.1195898410241119</v>
@@ -7417,7 +7503,7 @@
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="119" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="B220" s="120"/>
       <c r="C220" s="120"/>
@@ -7430,16 +7516,16 @@
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="121" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="B221" s="121" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="C221" s="121" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="D221" s="121" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="E221" s="122"/>
       <c r="F221" s="122"/>
@@ -7449,7 +7535,7 @@
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="123" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="B222" s="137">
         <f>C112</f>
@@ -7463,12 +7549,12 @@
         <v>3.2702462249289965E-7</v>
       </c>
       <c r="I222" s="118" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="123" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="B223" s="137">
         <f>C150</f>
@@ -7484,7 +7570,7 @@
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="123" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="B224" s="137">
         <f>C188</f>
@@ -7500,7 +7586,7 @@
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="123" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="B225" s="130">
         <f>G143</f>
@@ -7516,7 +7602,7 @@
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="123" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="B226" s="130">
         <f>G144</f>
@@ -7532,7 +7618,7 @@
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" s="123" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="B227" s="130">
         <f>C149</f>
@@ -7548,7 +7634,7 @@
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" s="119" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="B230" s="120"/>
       <c r="C230" s="120"/>
@@ -7561,52 +7647,52 @@
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" s="144" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" s="118" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" s="118" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" s="118" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" s="118" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" s="118" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" s="118" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" s="118" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" s="118" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" s="119" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="B242" s="120"/>
       <c r="C242" s="120"/>
@@ -7619,57 +7705,57 @@
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" s="118" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" s="118" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" s="118" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" s="118" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" s="118" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" s="118" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" s="118" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" s="118" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" s="118" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" s="118" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" s="118" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
     </row>
   </sheetData>
@@ -7688,44 +7774,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="163" t="s">
-        <v>664</v>
-      </c>
-      <c r="B1" s="156"/>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
-      <c r="E1" s="156"/>
-      <c r="F1" s="156"/>
-      <c r="G1" s="156"/>
+      <c r="A1" s="190" t="s">
+        <v>660</v>
+      </c>
+      <c r="B1" s="183"/>
+      <c r="C1" s="183"/>
+      <c r="D1" s="183"/>
+      <c r="E1" s="183"/>
+      <c r="F1" s="183"/>
+      <c r="G1" s="183"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>667</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>668</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>669</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="84" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="B5" s="85">
         <f>DCF!Q34</f>
@@ -7748,7 +7834,7 @@
         <v>4.9041703491122766</v>
       </c>
       <c r="G5" s="87" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -7757,31 +7843,31 @@
       </c>
       <c r="B6" s="89">
         <f>Trading_comps!E26</f>
-        <v>211</v>
+        <v>171</v>
       </c>
       <c r="C6" s="89">
         <f>Trading_comps!F26</f>
-        <v>361</v>
+        <v>202</v>
       </c>
       <c r="D6" s="89">
         <f>Trading_comps!G26</f>
-        <v>548</v>
+        <v>264</v>
       </c>
       <c r="E6" s="90">
         <f>C6/Inputs!B7</f>
-        <v>26.972504482964734</v>
+        <v>15.092647937836222</v>
       </c>
       <c r="F6" s="90">
         <f>C6/Inputs!B6</f>
-        <v>5.8779471147583697</v>
+        <v>3.2890451999478967</v>
       </c>
       <c r="G6" s="91" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="47" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B7" s="92">
         <f>Transaction_comps!E27</f>
@@ -7804,7 +7890,7 @@
         <v>6.6920672137553732</v>
       </c>
       <c r="G7" s="94" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -7832,7 +7918,7 @@
         <v>3.938713038947506</v>
       </c>
       <c r="G8" s="96" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -7845,19 +7931,19 @@
       <c r="G9" s="97"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="166" t="s">
-        <v>678</v>
-      </c>
-      <c r="B10" s="156"/>
-      <c r="C10" s="156"/>
-      <c r="D10" s="156"/>
-      <c r="E10" s="156"/>
-      <c r="F10" s="156"/>
-      <c r="G10" s="156"/>
+      <c r="A10" s="193" t="s">
+        <v>674</v>
+      </c>
+      <c r="B10" s="183"/>
+      <c r="C10" s="183"/>
+      <c r="D10" s="183"/>
+      <c r="E10" s="183"/>
+      <c r="F10" s="183"/>
+      <c r="G10" s="183"/>
     </row>
     <row r="11" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="C11" s="98">
         <f>DCF!R34</f>
@@ -7866,7 +7952,7 @@
     </row>
     <row r="12" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="C12" s="98">
         <f>Transaction_comps!F27</f>
@@ -7875,28 +7961,56 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="B13" s="72">
         <f>DCF!Q34</f>
         <v>157.92188754137794</v>
       </c>
       <c r="C13" s="61" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="D13" s="72">
         <f>Trading_comps!G26</f>
-        <v>548</v>
+        <v>264</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="145" t="s">
+        <v>679</v>
+      </c>
+      <c r="B14" s="180">
+        <f>170*FY25_base!B69/1000000+FY25_base!B49</f>
+        <v>275.9083</v>
+      </c>
+      <c r="C14" s="180">
+        <f>174*FY25_base!B69/1000000+FY25_base!B49</f>
+        <v>282.05545999999998</v>
+      </c>
+      <c r="D14" s="180">
+        <f>175.2*FY25_base!B69/1000000+FY25_base!B49</f>
+        <v>283.899608</v>
+      </c>
+      <c r="E14" s="173">
+        <f>C14/Inputs!B7</f>
+        <v>21.074078003586369</v>
+      </c>
+      <c r="F14" s="173">
+        <f>C14/Inputs!B6</f>
+        <v>4.59254038035691</v>
+      </c>
+      <c r="G14" s="155" t="s">
+        <v>680</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="99" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="100" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B16" s="101" t="str">
         <f>REPT("░",ROUND(B5/600*48,0))&amp;REPT("█",MAX(1,ROUND((D5-B5)/600*48,0)))&amp;REPT("░",MAX(0,48-ROUND(B5/600*48,0)-MAX(1,ROUND((D5-B5)/600*48,0))))</f>
@@ -7909,20 +8023,20 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="100" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B17" s="101" t="str">
         <f>REPT("░",ROUND(B6/600*48,0))&amp;REPT("█",MAX(1,ROUND((D6-B6)/600*48,0)))&amp;REPT("░",MAX(0,48-ROUND(B6/600*48,0)-MAX(1,ROUND((D6-B6)/600*48,0))))</f>
-        <v>░░░░░░░░░░░░░░░░░███████████████████████████░░░░</v>
+        <v>░░░░░░░░░░░░░░███████░░░░░░░░░░░░░░░░░░░░░░░░░░░</v>
       </c>
       <c r="C17" s="102" t="str">
         <f>"Low €"&amp;TEXT(B6,"0")&amp;"m  |  Base €"&amp;TEXT(C6,"0")&amp;"m  |  High €"&amp;TEXT(D6,"0")&amp;"m"</f>
-        <v>Low €211m  |  Base €361m  |  High €548m</v>
+        <v>Low €171m  |  Base €202m  |  High €264m</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="100" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B18" s="101" t="str">
         <f>REPT("░",ROUND(B7/600*48,0))&amp;REPT("█",MAX(1,ROUND((D7-B7)/600*48,0)))&amp;REPT("░",MAX(0,48-ROUND(B7/600*48,0)-MAX(1,ROUND((D7-B7)/600*48,0))))</f>
@@ -7935,7 +8049,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="100" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B19" s="101" t="str">
         <f>REPT("░",ROUND(B8/600*48,0))&amp;REPT("█",MAX(1,ROUND((D8-B8)/600*48,0)))&amp;REPT("░",MAX(0,48-ROUND(B8/600*48,0)-MAX(1,ROUND((D8-B8)/600*48,0))))</f>
@@ -7948,7 +8062,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B20" s="103" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
     </row>
   </sheetData>
@@ -7972,17 +8086,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="163" t="s">
-        <v>689</v>
-      </c>
-      <c r="B1" s="156"/>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
-      <c r="E1" s="156"/>
+      <c r="A1" s="190" t="s">
+        <v>687</v>
+      </c>
+      <c r="B1" s="183"/>
+      <c r="C1" s="183"/>
+      <c r="D1" s="183"/>
+      <c r="E1" s="183"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8000,12 +8114,12 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="155" t="s">
-        <v>691</v>
-      </c>
-      <c r="B5" s="156"/>
-      <c r="C5" s="156"/>
-      <c r="D5" s="156"/>
+      <c r="A5" s="182" t="s">
+        <v>689</v>
+      </c>
+      <c r="B5" s="183"/>
+      <c r="C5" s="183"/>
+      <c r="D5" s="183"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
@@ -8025,16 +8139,16 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="155" t="s">
-        <v>692</v>
-      </c>
-      <c r="B8" s="156"/>
-      <c r="C8" s="156"/>
-      <c r="D8" s="156"/>
+      <c r="A8" s="182" t="s">
+        <v>690</v>
+      </c>
+      <c r="B8" s="183"/>
+      <c r="C8" s="183"/>
+      <c r="D8" s="183"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B9" s="72">
         <f>FY25_base!B46</f>
@@ -8049,7 +8163,7 @@
         <v>30.981000000000002</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -8069,7 +8183,7 @@
         <v>-5.4020000000000001</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -8089,7 +8203,7 @@
         <v>-10.925000000000001</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -8109,20 +8223,20 @@
         <v>14.654</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="155" t="s">
-        <v>698</v>
-      </c>
-      <c r="B14" s="156"/>
-      <c r="C14" s="156"/>
-      <c r="D14" s="156"/>
+      <c r="A14" s="182" t="s">
+        <v>696</v>
+      </c>
+      <c r="B14" s="183"/>
+      <c r="C14" s="183"/>
+      <c r="D14" s="183"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B15" s="51">
         <f>B6-B12</f>
@@ -8138,16 +8252,16 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="155" t="s">
-        <v>700</v>
-      </c>
-      <c r="B17" s="156"/>
-      <c r="C17" s="156"/>
-      <c r="D17" s="156"/>
+      <c r="A17" s="182" t="s">
+        <v>698</v>
+      </c>
+      <c r="B17" s="183"/>
+      <c r="C17" s="183"/>
+      <c r="D17" s="183"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="B18" s="105">
         <f>FY25_base!B69</f>
@@ -8162,12 +8276,12 @@
         <v>1536790</v>
       </c>
       <c r="E18" s="28" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B19" s="106">
         <f>B18/1000000</f>
@@ -8184,7 +8298,7 @@
     </row>
     <row r="20" spans="1:5" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B20" s="107">
         <f>B15/B19</f>
@@ -8200,16 +8314,16 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="155" t="s">
-        <v>705</v>
-      </c>
-      <c r="B22" s="156"/>
-      <c r="C22" s="156"/>
-      <c r="D22" s="156"/>
+      <c r="A22" s="182" t="s">
+        <v>703</v>
+      </c>
+      <c r="B22" s="183"/>
+      <c r="C22" s="183"/>
+      <c r="D22" s="183"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C23" s="52">
         <f>Transaction_comps!F27</f>
@@ -8218,7 +8332,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="C24" s="51">
         <f>C23-C12</f>
@@ -8227,28 +8341,28 @@
     </row>
     <row r="25" spans="1:5" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="C25" s="107">
         <f>C24/C19</f>
         <v>257.90511390625915</v>
       </c>
       <c r="E25" s="28" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="167" t="s">
-        <v>710</v>
-      </c>
-      <c r="B27" s="156"/>
-      <c r="C27" s="156"/>
-      <c r="D27" s="156"/>
-      <c r="E27" s="156"/>
+      <c r="A27" s="196" t="s">
+        <v>708</v>
+      </c>
+      <c r="B27" s="183"/>
+      <c r="C27" s="183"/>
+      <c r="D27" s="183"/>
+      <c r="E27" s="183"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C28" s="108">
         <f>C6</f>
@@ -8257,7 +8371,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="C29" s="108">
         <f>C12</f>
@@ -8266,7 +8380,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="C30" s="108">
         <f>C15</f>
@@ -8275,7 +8389,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="C31" s="109">
         <f>C19</f>
@@ -8284,7 +8398,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C32" s="110">
         <f>C20</f>
@@ -8308,7 +8422,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -8318,137 +8432,151 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="163" t="s">
-        <v>716</v>
-      </c>
-      <c r="B1" s="156"/>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
+      <c r="A1" s="190" t="s">
+        <v>714</v>
+      </c>
+      <c r="B1" s="183"/>
+      <c r="C1" s="183"/>
+      <c r="D1" s="183"/>
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>717</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>718</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>719</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>720</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="111" t="s">
+        <v>719</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>720</v>
+      </c>
+      <c r="C4" s="112" t="s">
         <v>721</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="D4" s="113" t="s">
         <v>722</v>
-      </c>
-      <c r="C4" s="112" t="s">
-        <v>723</v>
-      </c>
-      <c r="D4" s="113" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="114" t="s">
+        <v>723</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>724</v>
+      </c>
+      <c r="C5" s="115" t="s">
         <v>725</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="D5" s="116" t="s">
         <v>726</v>
-      </c>
-      <c r="C5" s="115" t="s">
-        <v>727</v>
-      </c>
-      <c r="D5" s="116" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="111" t="s">
+        <v>727</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>728</v>
+      </c>
+      <c r="C6" s="112" t="s">
         <v>729</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="D6" s="113" t="s">
         <v>730</v>
-      </c>
-      <c r="C6" s="112" t="s">
-        <v>731</v>
-      </c>
-      <c r="D6" s="113" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="114" t="s">
+        <v>731</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>732</v>
+      </c>
+      <c r="C7" s="115" t="s">
         <v>733</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="D7" s="116" t="s">
         <v>734</v>
-      </c>
-      <c r="C7" s="115" t="s">
-        <v>735</v>
-      </c>
-      <c r="D7" s="116" t="s">
-        <v>736</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="111" t="s">
+        <v>735</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>736</v>
+      </c>
+      <c r="C8" s="112" t="s">
         <v>737</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="D8" s="113" t="s">
         <v>738</v>
-      </c>
-      <c r="C8" s="112" t="s">
-        <v>739</v>
-      </c>
-      <c r="D8" s="113" t="s">
-        <v>740</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="114" t="s">
+        <v>739</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>740</v>
+      </c>
+      <c r="C9" s="115" t="s">
         <v>741</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="D9" s="116" t="s">
         <v>742</v>
-      </c>
-      <c r="C9" s="115" t="s">
-        <v>743</v>
-      </c>
-      <c r="D9" s="116" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="111" t="s">
+        <v>743</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>744</v>
+      </c>
+      <c r="C10" s="112" t="s">
         <v>745</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="D10" s="113" t="s">
         <v>746</v>
-      </c>
-      <c r="C10" s="112" t="s">
-        <v>747</v>
-      </c>
-      <c r="D10" s="113" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="114" t="s">
+        <v>747</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>748</v>
+      </c>
+      <c r="C11" s="115" t="s">
         <v>749</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="D11" s="116" t="s">
         <v>750</v>
       </c>
-      <c r="C11" s="115" t="s">
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="145" t="s">
         <v>751</v>
       </c>
-      <c r="D11" s="116" t="s">
+      <c r="B12" s="181" t="s">
         <v>752</v>
+      </c>
+      <c r="C12" s="181" t="s">
+        <v>753</v>
+      </c>
+      <c r="D12" s="181" t="s">
+        <v>754</v>
       </c>
     </row>
   </sheetData>
@@ -8471,28 +8599,28 @@
     <col min="4" max="4" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="151" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="152" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="B3" s="152" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="C3" s="152" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="D3" s="152" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="B4" s="153">
         <f>Inputs!C6-61.416</f>
@@ -8508,7 +8636,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="B5" s="153">
         <f>Inputs!C7-13.384</f>
@@ -8524,7 +8652,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="B6" s="153">
         <f>LBO_full!B68</f>
@@ -8540,7 +8668,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="B7" s="153">
         <f>LBO_full!C68</f>
@@ -8556,7 +8684,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="B8" s="153">
         <f>LBO_full!D68</f>
@@ -8572,7 +8700,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="B9" s="153">
         <f>LBO_full!B11-0.225</f>
@@ -8588,7 +8716,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="B10" s="153">
         <f>LBO_full!C11-0.225</f>
@@ -8604,7 +8732,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="B11" s="153">
         <f>LBO_full!D11-0.225</f>
@@ -8620,7 +8748,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="B12" s="153">
         <f>LBO_full!D223</f>
@@ -8636,7 +8764,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="B13" s="153">
         <f>LBO_full!D227</f>
@@ -8652,7 +8780,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="B14" s="153">
         <f>Trading_comps!F26-ROUND(AVERAGE(Trading_comps!F22,Trading_comps!F24),0)</f>
@@ -8668,7 +8796,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="B15" s="153">
         <f>Transaction_comps!F27-ROUND(Transaction_comps!F25,0)</f>
@@ -8684,7 +8812,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="B16" s="153">
         <f>Inputs!C56</f>
@@ -8700,7 +8828,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="B17" s="153">
         <f>Football_field!C8-LBO_full!C199</f>
@@ -8716,7 +8844,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="145" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="D18" s="154" t="str">
         <f>IF(COUNTIF(D4:D17,"FAIL")=0,"PASS","FAIL")</f>
@@ -8725,7 +8853,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="147" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
     </row>
   </sheetData>
@@ -8744,13 +8872,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="190" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="156"/>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
-      <c r="E1" s="156"/>
+      <c r="B1" s="183"/>
+      <c r="C1" s="183"/>
+      <c r="D1" s="183"/>
+      <c r="E1" s="183"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
@@ -8775,13 +8903,13 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="155" t="s">
+      <c r="A5" s="182" t="s">
         <v>105</v>
       </c>
-      <c r="B5" s="156"/>
-      <c r="C5" s="156"/>
-      <c r="D5" s="156"/>
-      <c r="E5" s="156"/>
+      <c r="B5" s="183"/>
+      <c r="C5" s="183"/>
+      <c r="D5" s="183"/>
+      <c r="E5" s="183"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
@@ -8889,13 +9017,13 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="155" t="s">
+      <c r="A13" s="182" t="s">
         <v>118</v>
       </c>
-      <c r="B13" s="156"/>
-      <c r="C13" s="156"/>
-      <c r="D13" s="156"/>
-      <c r="E13" s="156"/>
+      <c r="B13" s="183"/>
+      <c r="C13" s="183"/>
+      <c r="D13" s="183"/>
+      <c r="E13" s="183"/>
     </row>
     <row r="14" spans="1:5" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
@@ -8977,13 +9105,13 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="155" t="s">
+      <c r="A20" s="182" t="s">
         <v>127</v>
       </c>
-      <c r="B20" s="156"/>
-      <c r="C20" s="156"/>
-      <c r="D20" s="156"/>
-      <c r="E20" s="156"/>
+      <c r="B20" s="183"/>
+      <c r="C20" s="183"/>
+      <c r="D20" s="183"/>
+      <c r="E20" s="183"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
@@ -9111,13 +9239,13 @@
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="155" t="s">
+      <c r="A29" s="182" t="s">
         <v>138</v>
       </c>
-      <c r="B29" s="156"/>
-      <c r="C29" s="156"/>
-      <c r="D29" s="156"/>
-      <c r="E29" s="156"/>
+      <c r="B29" s="183"/>
+      <c r="C29" s="183"/>
+      <c r="D29" s="183"/>
+      <c r="E29" s="183"/>
     </row>
     <row r="30" spans="1:5" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
@@ -9205,13 +9333,13 @@
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="155" t="s">
+      <c r="A36" s="182" t="s">
         <v>149</v>
       </c>
-      <c r="B36" s="156"/>
-      <c r="C36" s="156"/>
-      <c r="D36" s="156"/>
-      <c r="E36" s="156"/>
+      <c r="B36" s="183"/>
+      <c r="C36" s="183"/>
+      <c r="D36" s="183"/>
+      <c r="E36" s="183"/>
     </row>
     <row r="37" spans="1:5" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
@@ -9265,13 +9393,13 @@
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="155" t="s">
+      <c r="A41" s="182" t="s">
         <v>156</v>
       </c>
-      <c r="B41" s="156"/>
-      <c r="C41" s="156"/>
-      <c r="D41" s="156"/>
-      <c r="E41" s="156"/>
+      <c r="B41" s="183"/>
+      <c r="C41" s="183"/>
+      <c r="D41" s="183"/>
+      <c r="E41" s="183"/>
     </row>
     <row r="42" spans="1:5" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
@@ -9465,18 +9593,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="157" t="s">
+      <c r="A1" s="184" t="s">
         <v>180</v>
       </c>
-      <c r="B1" s="156"/>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
+      <c r="B1" s="183"/>
+      <c r="C1" s="183"/>
+      <c r="D1" s="183"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="155" t="s">
+      <c r="A3" s="182" t="s">
         <v>181</v>
       </c>
-      <c r="B3" s="156"/>
+      <c r="B3" s="183"/>
       <c r="C3" s="3" t="s">
         <v>182</v>
       </c>
@@ -9684,10 +9812,10 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="155" t="s">
+      <c r="A19" s="182" t="s">
         <v>209</v>
       </c>
-      <c r="B19" s="156"/>
+      <c r="B19" s="183"/>
       <c r="C19" s="3" t="s">
         <v>182</v>
       </c>
@@ -9769,10 +9897,10 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="155" t="s">
+      <c r="A26" s="182" t="s">
         <v>219</v>
       </c>
-      <c r="B26" s="156"/>
+      <c r="B26" s="183"/>
       <c r="C26" s="3" t="s">
         <v>220</v>
       </c>
@@ -9857,10 +9985,10 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="155" t="s">
+      <c r="A35" s="182" t="s">
         <v>233</v>
       </c>
-      <c r="B35" s="156"/>
+      <c r="B35" s="183"/>
       <c r="C35" s="3" t="s">
         <v>234</v>
       </c>
@@ -9963,10 +10091,10 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="155" t="s">
+      <c r="A45" s="182" t="s">
         <v>246</v>
       </c>
-      <c r="B45" s="156"/>
+      <c r="B45" s="183"/>
       <c r="C45" s="3" t="s">
         <v>247</v>
       </c>
@@ -10015,10 +10143,10 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="155" t="s">
+      <c r="A51" s="182" t="s">
         <v>254</v>
       </c>
-      <c r="B51" s="156"/>
+      <c r="B51" s="183"/>
       <c r="C51" s="3" t="s">
         <v>247</v>
       </c>
@@ -10080,10 +10208,10 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="155" t="s">
+      <c r="A58" s="182" t="s">
         <v>264</v>
       </c>
-      <c r="B58" s="156"/>
+      <c r="B58" s="183"/>
       <c r="C58" s="3" t="s">
         <v>247</v>
       </c>
@@ -10160,10 +10288,10 @@
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="155" t="s">
+      <c r="A67" s="182" t="s">
         <v>274</v>
       </c>
-      <c r="B67" s="156"/>
+      <c r="B67" s="183"/>
     </row>
     <row r="68" spans="1:4" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="9" t="s">
@@ -10215,27 +10343,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="190" t="s">
         <v>279</v>
       </c>
-      <c r="B1" s="156"/>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
-      <c r="E1" s="156"/>
-      <c r="F1" s="156"/>
-      <c r="G1" s="156"/>
-      <c r="H1" s="156"/>
-      <c r="I1" s="156"/>
-      <c r="J1" s="156"/>
-      <c r="K1" s="156"/>
-      <c r="L1" s="156"/>
-      <c r="M1" s="156"/>
-      <c r="N1" s="156"/>
-      <c r="O1" s="156"/>
-      <c r="P1" s="156"/>
-      <c r="Q1" s="156"/>
-      <c r="R1" s="156"/>
-      <c r="S1" s="156"/>
+      <c r="B1" s="183"/>
+      <c r="C1" s="183"/>
+      <c r="D1" s="183"/>
+      <c r="E1" s="183"/>
+      <c r="F1" s="183"/>
+      <c r="G1" s="183"/>
+      <c r="H1" s="183"/>
+      <c r="I1" s="183"/>
+      <c r="J1" s="183"/>
+      <c r="K1" s="183"/>
+      <c r="L1" s="183"/>
+      <c r="M1" s="183"/>
+      <c r="N1" s="183"/>
+      <c r="O1" s="183"/>
+      <c r="P1" s="183"/>
+      <c r="Q1" s="183"/>
+      <c r="R1" s="183"/>
+      <c r="S1" s="183"/>
     </row>
     <row r="2" spans="1:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="54" t="s">
@@ -10243,36 +10371,36 @@
       </c>
     </row>
     <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="164" t="s">
+      <c r="B3" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="156"/>
-      <c r="D3" s="156"/>
-      <c r="E3" s="164" t="s">
+      <c r="C3" s="183"/>
+      <c r="D3" s="183"/>
+      <c r="E3" s="191" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="156"/>
-      <c r="G3" s="156"/>
-      <c r="H3" s="164" t="s">
+      <c r="F3" s="183"/>
+      <c r="G3" s="183"/>
+      <c r="H3" s="191" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="156"/>
-      <c r="J3" s="156"/>
-      <c r="K3" s="164" t="s">
+      <c r="I3" s="183"/>
+      <c r="J3" s="183"/>
+      <c r="K3" s="191" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="156"/>
-      <c r="M3" s="156"/>
-      <c r="N3" s="164" t="s">
+      <c r="L3" s="183"/>
+      <c r="M3" s="183"/>
+      <c r="N3" s="191" t="s">
         <v>13</v>
       </c>
-      <c r="O3" s="156"/>
-      <c r="P3" s="156"/>
-      <c r="Q3" s="165" t="s">
+      <c r="O3" s="183"/>
+      <c r="P3" s="183"/>
+      <c r="Q3" s="192" t="s">
         <v>281</v>
       </c>
-      <c r="R3" s="156"/>
-      <c r="S3" s="156"/>
+      <c r="R3" s="183"/>
+      <c r="S3" s="183"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B4" s="55" t="s">
@@ -11553,16 +11681,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="157" t="s">
+      <c r="A1" s="184" t="s">
         <v>317</v>
       </c>
-      <c r="B1" s="156"/>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
-      <c r="E1" s="156"/>
-      <c r="F1" s="156"/>
-      <c r="G1" s="156"/>
-      <c r="H1" s="156"/>
+      <c r="B1" s="183"/>
+      <c r="C1" s="183"/>
+      <c r="D1" s="183"/>
+      <c r="E1" s="183"/>
+      <c r="F1" s="183"/>
+      <c r="G1" s="183"/>
+      <c r="H1" s="183"/>
     </row>
     <row r="2" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
@@ -11570,15 +11698,15 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="166" t="s">
+      <c r="A4" s="193" t="s">
         <v>319</v>
       </c>
-      <c r="B4" s="156"/>
-      <c r="C4" s="156"/>
-      <c r="D4" s="156"/>
-      <c r="E4" s="156"/>
-      <c r="F4" s="156"/>
-      <c r="G4" s="156"/>
+      <c r="B4" s="183"/>
+      <c r="C4" s="183"/>
+      <c r="D4" s="183"/>
+      <c r="E4" s="183"/>
+      <c r="F4" s="183"/>
+      <c r="G4" s="183"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
@@ -11731,15 +11859,15 @@
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="166" t="s">
+      <c r="A14" s="193" t="s">
         <v>322</v>
       </c>
-      <c r="B14" s="156"/>
-      <c r="C14" s="156"/>
-      <c r="D14" s="156"/>
-      <c r="E14" s="156"/>
-      <c r="F14" s="156"/>
-      <c r="G14" s="156"/>
+      <c r="B14" s="183"/>
+      <c r="C14" s="183"/>
+      <c r="D14" s="183"/>
+      <c r="E14" s="183"/>
+      <c r="F14" s="183"/>
+      <c r="G14" s="183"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
@@ -11918,13 +12046,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="157" t="s">
+      <c r="A1" s="184" t="s">
         <v>326</v>
       </c>
-      <c r="B1" s="156"/>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
-      <c r="E1" s="156"/>
+      <c r="B1" s="183"/>
+      <c r="C1" s="183"/>
+      <c r="D1" s="183"/>
+      <c r="E1" s="183"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
@@ -11980,13 +12108,13 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="166" t="s">
+      <c r="A8" s="193" t="s">
         <v>332</v>
       </c>
-      <c r="B8" s="156"/>
-      <c r="C8" s="156"/>
-      <c r="D8" s="156"/>
-      <c r="E8" s="156"/>
+      <c r="B8" s="183"/>
+      <c r="C8" s="183"/>
+      <c r="D8" s="183"/>
+      <c r="E8" s="183"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
@@ -12089,13 +12217,13 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="166" t="s">
+      <c r="A15" s="193" t="s">
         <v>338</v>
       </c>
-      <c r="B15" s="156"/>
-      <c r="C15" s="156"/>
-      <c r="D15" s="156"/>
-      <c r="E15" s="156"/>
+      <c r="B15" s="183"/>
+      <c r="C15" s="183"/>
+      <c r="D15" s="183"/>
+      <c r="E15" s="183"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
@@ -12283,13 +12411,13 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="166" t="s">
+      <c r="A27" s="193" t="s">
         <v>354</v>
       </c>
-      <c r="B27" s="156"/>
-      <c r="C27" s="156"/>
-      <c r="D27" s="156"/>
-      <c r="E27" s="156"/>
+      <c r="B27" s="183"/>
+      <c r="C27" s="183"/>
+      <c r="D27" s="183"/>
+      <c r="E27" s="183"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
@@ -12494,386 +12622,388 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="157" t="s">
+      <c r="A1" s="194" t="s">
         <v>366</v>
       </c>
-      <c r="B1" s="156"/>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
-      <c r="E1" s="156"/>
-      <c r="F1" s="156"/>
-      <c r="G1" s="156"/>
-      <c r="H1" s="156"/>
-      <c r="I1" s="156"/>
+      <c r="B1" s="183"/>
+      <c r="C1" s="183"/>
+      <c r="D1" s="183"/>
+      <c r="E1" s="183"/>
+      <c r="F1" s="183"/>
+      <c r="G1" s="183"/>
+      <c r="H1" s="183"/>
+      <c r="I1" s="183"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="155" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="156" t="s">
         <v>368</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="156" t="s">
         <v>369</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="156" t="s">
         <v>370</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="156" t="s">
         <v>371</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="156" t="s">
         <v>372</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="156" t="s">
         <v>373</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="156" t="s">
         <v>374</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="156" t="s">
         <v>375</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="156" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="65" t="s">
+      <c r="A5" s="157" t="s">
         <v>377</v>
       </c>
-      <c r="B5" s="65" t="s">
+      <c r="B5" s="157" t="s">
         <v>378</v>
       </c>
-      <c r="C5" s="65" t="s">
+      <c r="C5" s="158">
+        <v>28.75</v>
+      </c>
+      <c r="D5" s="159">
+        <v>1635</v>
+      </c>
+      <c r="E5" s="160">
+        <v>671.4</v>
+      </c>
+      <c r="F5" s="160">
+        <v>162.80000000000001</v>
+      </c>
+      <c r="G5" s="161">
+        <f>D5/E5</f>
+        <v>2.4352100089365507</v>
+      </c>
+      <c r="H5" s="162">
+        <f>D5/F5</f>
+        <v>10.042997542997542</v>
+      </c>
+      <c r="I5" s="163" t="s">
         <v>379</v>
       </c>
-      <c r="D5" s="66">
-        <v>3636</v>
-      </c>
-      <c r="E5" s="66">
-        <v>700</v>
-      </c>
-      <c r="F5" s="66">
-        <v>140</v>
-      </c>
-      <c r="G5" s="67">
-        <f>D5/E5</f>
-        <v>5.194285714285714</v>
-      </c>
-      <c r="H5" s="67">
-        <f>D5/F5</f>
-        <v>25.971428571428572</v>
-      </c>
-      <c r="I5" s="68" t="s">
+    </row>
+    <row r="6" spans="1:9" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="164" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="29" t="s">
+      <c r="B6" s="164" t="s">
         <v>381</v>
       </c>
-      <c r="B6" s="29" t="s">
+      <c r="C6" s="165">
+        <v>42.72</v>
+      </c>
+      <c r="D6" s="166">
+        <v>3428</v>
+      </c>
+      <c r="E6" s="167">
+        <v>1441.7</v>
+      </c>
+      <c r="F6" s="167">
+        <v>267.89999999999998</v>
+      </c>
+      <c r="G6" s="168">
+        <f>D6/E6</f>
+        <v>2.3777484913643616</v>
+      </c>
+      <c r="H6" s="169">
+        <f>D6/F6</f>
+        <v>12.795819335572975</v>
+      </c>
+      <c r="I6" s="170" t="s">
         <v>382</v>
       </c>
-      <c r="C6" s="29" t="s">
+    </row>
+    <row r="7" spans="1:9" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="157" t="s">
         <v>383</v>
       </c>
-      <c r="D6" s="69">
-        <v>1818</v>
-      </c>
-      <c r="E6" s="69">
-        <v>900</v>
-      </c>
-      <c r="F6" s="69">
-        <v>200</v>
-      </c>
-      <c r="G6" s="70">
-        <f>D6/E6</f>
-        <v>2.02</v>
-      </c>
-      <c r="H6" s="70">
-        <f>D6/F6</f>
-        <v>9.09</v>
-      </c>
-      <c r="I6" s="24" t="s">
+      <c r="B7" s="157" t="s">
         <v>384</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="65" t="s">
+      <c r="C7" s="158">
+        <v>17.48</v>
+      </c>
+      <c r="D7" s="159">
+        <v>1829</v>
+      </c>
+      <c r="E7" s="160">
+        <v>563.70000000000005</v>
+      </c>
+      <c r="F7" s="160">
+        <v>147.5</v>
+      </c>
+      <c r="G7" s="161">
+        <f>D7/E7</f>
+        <v>3.2446336703920524</v>
+      </c>
+      <c r="H7" s="162">
+        <f>D7/F7</f>
+        <v>12.4</v>
+      </c>
+      <c r="I7" s="163" t="s">
         <v>385</v>
       </c>
-      <c r="B7" s="65" t="s">
+    </row>
+    <row r="8" spans="1:9" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="164" t="s">
         <v>386</v>
       </c>
-      <c r="C7" s="65" t="s">
+      <c r="B8" s="164" t="s">
         <v>387</v>
       </c>
-      <c r="D7" s="66">
-        <v>2273</v>
-      </c>
-      <c r="E7" s="66">
-        <v>530</v>
-      </c>
-      <c r="F7" s="66">
-        <v>68</v>
-      </c>
-      <c r="G7" s="67">
-        <f>D7/E7</f>
-        <v>4.2886792452830189</v>
-      </c>
-      <c r="H7" s="67">
-        <f>D7/F7</f>
-        <v>33.426470588235297</v>
-      </c>
-      <c r="I7" s="68" t="s">
+      <c r="C8" s="165">
+        <v>53.02</v>
+      </c>
+      <c r="D8" s="166">
+        <v>2538</v>
+      </c>
+      <c r="E8" s="167">
+        <v>909.5</v>
+      </c>
+      <c r="F8" s="167">
+        <v>147.80000000000001</v>
+      </c>
+      <c r="G8" s="168">
+        <f>D8/E8</f>
+        <v>2.7905442550852118</v>
+      </c>
+      <c r="H8" s="169">
+        <f>D8/F8</f>
+        <v>17.171853856562922</v>
+      </c>
+      <c r="I8" s="170" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="29" t="s">
+    <row r="9" spans="1:9" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="157" t="s">
         <v>389</v>
       </c>
-      <c r="B8" s="29" t="s">
+      <c r="B9" s="157" t="s">
         <v>390</v>
       </c>
-      <c r="C8" s="29" t="s">
-        <v>391</v>
-      </c>
-      <c r="D8" s="69">
-        <v>4091</v>
-      </c>
-      <c r="E8" s="69">
-        <v>760</v>
-      </c>
-      <c r="F8" s="69">
-        <v>122</v>
-      </c>
-      <c r="G8" s="70">
-        <f>D8/E8</f>
-        <v>5.382894736842105</v>
-      </c>
-      <c r="H8" s="70">
-        <f>D8/F8</f>
-        <v>33.532786885245905</v>
-      </c>
-      <c r="I8" s="24" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="71" t="s">
-        <v>393</v>
-      </c>
-      <c r="B9" s="65" t="s">
-        <v>394</v>
-      </c>
-      <c r="C9" s="65" t="s">
-        <v>395</v>
-      </c>
-      <c r="D9" s="66">
+      <c r="C9" s="65"/>
+      <c r="D9" s="159">
         <v>1576</v>
       </c>
-      <c r="E9" s="66">
+      <c r="E9" s="160">
         <v>205.3</v>
       </c>
       <c r="F9" s="66"/>
-      <c r="G9" s="67">
+      <c r="G9" s="161">
         <f>D9/E9</f>
         <v>7.6765708718947874</v>
       </c>
-      <c r="H9" s="67" t="s">
+      <c r="H9" s="67"/>
+      <c r="I9" s="163" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="195" t="s">
+        <v>392</v>
+      </c>
+      <c r="B11" s="183"/>
+      <c r="C11" s="183"/>
+      <c r="D11" s="183"/>
+      <c r="E11" s="183"/>
+      <c r="F11" s="183"/>
+      <c r="G11" s="183"/>
+      <c r="H11" s="183"/>
+      <c r="I11" s="183"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="171" t="s">
+        <v>393</v>
+      </c>
+      <c r="G12" s="172">
+        <f>MEDIAN(G5:G8)</f>
+        <v>2.6128771320108815</v>
+      </c>
+      <c r="H12" s="173">
+        <f>MEDIAN(H5:H8)</f>
+        <v>12.597909667786489</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="171" t="s">
+        <v>394</v>
+      </c>
+      <c r="G13" s="172">
+        <f>MIN(G5:G8)</f>
+        <v>2.3777484913643616</v>
+      </c>
+      <c r="H13" s="173">
+        <f>MIN(H5:H8)</f>
+        <v>10.042997542997542</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="171" t="s">
+        <v>395</v>
+      </c>
+      <c r="G14" s="172">
+        <f>MAX(G5:G8)</f>
+        <v>3.2446336703920524</v>
+      </c>
+      <c r="H14" s="173">
+        <f>MAX(H5:H8)</f>
+        <v>17.171853856562922</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="195" t="s">
         <v>396</v>
       </c>
-      <c r="I9" s="68" t="s">
+      <c r="B16" s="183"/>
+      <c r="C16" s="183"/>
+      <c r="D16" s="183"/>
+      <c r="E16" s="183"/>
+      <c r="F16" s="183"/>
+      <c r="G16" s="183"/>
+      <c r="H16" s="183"/>
+      <c r="I16" s="183"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="171" t="s">
         <v>397</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="166" t="s">
-        <v>398</v>
-      </c>
-      <c r="B11" s="156"/>
-      <c r="C11" s="156"/>
-      <c r="D11" s="156"/>
-      <c r="E11" s="156"/>
-      <c r="F11" s="156"/>
-      <c r="G11" s="156"/>
-      <c r="H11" s="156"/>
-      <c r="I11" s="156"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>399</v>
-      </c>
-      <c r="G12" s="42">
-        <f>MEDIAN(G5:G8)</f>
-        <v>4.7414824797843664</v>
-      </c>
-      <c r="H12" s="42">
-        <f>MEDIAN(H5:H8)</f>
-        <v>29.698949579831933</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>400</v>
-      </c>
-      <c r="G13" s="42">
-        <f>MIN(G5:G8)</f>
-        <v>2.02</v>
-      </c>
-      <c r="H13" s="42">
-        <f>MIN(H5:H8)</f>
-        <v>9.09</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>401</v>
-      </c>
-      <c r="G14" s="42">
-        <f>MAX(G5:G8)</f>
-        <v>5.382894736842105</v>
-      </c>
-      <c r="H14" s="42">
-        <f>MAX(H5:H8)</f>
-        <v>33.532786885245905</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="166" t="s">
-        <v>402</v>
-      </c>
-      <c r="B16" s="156"/>
-      <c r="C16" s="156"/>
-      <c r="D16" s="156"/>
-      <c r="E16" s="156"/>
-      <c r="F16" s="156"/>
-      <c r="G16" s="156"/>
-      <c r="H16" s="156"/>
-      <c r="I16" s="156"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
-        <v>403</v>
-      </c>
-      <c r="E17" s="72">
+      <c r="E17" s="174">
         <f>DCF!C7</f>
         <v>71.856719999999996</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
-        <v>404</v>
-      </c>
-      <c r="F18" s="72">
+      <c r="A18" s="171" t="s">
+        <v>398</v>
+      </c>
+      <c r="F18" s="174">
         <f>DCF!C12</f>
         <v>17.126254079999999</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="175" t="s">
+        <v>399</v>
+      </c>
+      <c r="E20" s="176" t="s">
+        <v>400</v>
+      </c>
+      <c r="F20" s="176" t="s">
+        <v>401</v>
+      </c>
+      <c r="G20" s="176" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="171" t="s">
+        <v>403</v>
+      </c>
+      <c r="E21" s="172">
+        <f>G13</f>
+        <v>2.3777484913643616</v>
+      </c>
+      <c r="F21" s="172">
+        <f>G12</f>
+        <v>2.6128771320108815</v>
+      </c>
+      <c r="G21" s="172">
+        <f>G14</f>
+        <v>3.2446336703920524</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="171" t="s">
+        <v>404</v>
+      </c>
+      <c r="E22" s="177">
+        <f>E21*$E$17</f>
+        <v>170.85720757439134</v>
+      </c>
+      <c r="F22" s="177">
+        <f>F21*$E$17</f>
+        <v>187.75278046930893</v>
+      </c>
+      <c r="G22" s="177">
+        <f>G21*$E$17</f>
+        <v>233.148733155934</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="171" t="s">
         <v>405</v>
       </c>
-      <c r="E20" s="18" t="s">
+      <c r="E23" s="173">
+        <f>H13</f>
+        <v>10.042997542997542</v>
+      </c>
+      <c r="F23" s="173">
+        <f>H12</f>
+        <v>12.597909667786489</v>
+      </c>
+      <c r="G23" s="173">
+        <f>H14</f>
+        <v>17.171853856562922</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="171" t="s">
         <v>406</v>
       </c>
-      <c r="F20" s="18" t="s">
+      <c r="E24" s="177">
+        <f>E23*$F$18</f>
+        <v>171.99892764619162</v>
+      </c>
+      <c r="F24" s="177">
+        <f>F23*$F$18</f>
+        <v>215.7550018473998</v>
+      </c>
+      <c r="G24" s="177">
+        <f>G23*$F$18</f>
+        <v>294.08953217212445</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="175" t="s">
         <v>407</v>
       </c>
-      <c r="G20" s="18" t="s">
+      <c r="E26" s="178">
+        <f>ROUND(AVERAGE(E22,E24),0)</f>
+        <v>171</v>
+      </c>
+      <c r="F26" s="178">
+        <f>ROUND(AVERAGE(F22,F24),0)</f>
+        <v>202</v>
+      </c>
+      <c r="G26" s="178">
+        <f>ROUND(AVERAGE(G22,G24),0)</f>
+        <v>264</v>
+      </c>
+      <c r="I26" s="179" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="155" t="s">
         <v>409</v>
-      </c>
-      <c r="E21" s="41">
-        <v>3</v>
-      </c>
-      <c r="F21" s="41">
-        <v>4.8</v>
-      </c>
-      <c r="G21" s="41">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
-        <v>410</v>
-      </c>
-      <c r="E22" s="51">
-        <f>E17*E21</f>
-        <v>215.57015999999999</v>
-      </c>
-      <c r="F22" s="51">
-        <f>E17*F21</f>
-        <v>344.91225599999996</v>
-      </c>
-      <c r="G22" s="51">
-        <f>E17*G21</f>
-        <v>495.81136800000002</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
-        <v>411</v>
-      </c>
-      <c r="E23" s="41">
-        <v>12</v>
-      </c>
-      <c r="F23" s="41">
-        <v>22</v>
-      </c>
-      <c r="G23" s="41">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
-        <v>412</v>
-      </c>
-      <c r="E24" s="51">
-        <f>F18*E23</f>
-        <v>205.51504896</v>
-      </c>
-      <c r="F24" s="51">
-        <f>F18*F23</f>
-        <v>376.77758975999996</v>
-      </c>
-      <c r="G24" s="51">
-        <f>F18*G23</f>
-        <v>599.41889279999998</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
-        <v>413</v>
-      </c>
-      <c r="E26" s="52">
-        <f>ROUND(AVERAGE(E22,E24),0)</f>
-        <v>211</v>
-      </c>
-      <c r="F26" s="52">
-        <f>ROUND(AVERAGE(F22,F24),0)</f>
-        <v>361</v>
-      </c>
-      <c r="G26" s="52">
-        <f>ROUND(AVERAGE(G22,G24),0)</f>
-        <v>548</v>
-      </c>
-      <c r="I26" s="28" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="14" t="s">
-        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -12901,51 +13031,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="157" t="s">
-        <v>416</v>
-      </c>
-      <c r="B1" s="156"/>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
-      <c r="E1" s="156"/>
-      <c r="F1" s="156"/>
-      <c r="G1" s="156"/>
-      <c r="H1" s="156"/>
-      <c r="I1" s="156"/>
-      <c r="J1" s="156"/>
+      <c r="A1" s="184" t="s">
+        <v>410</v>
+      </c>
+      <c r="B1" s="183"/>
+      <c r="C1" s="183"/>
+      <c r="D1" s="183"/>
+      <c r="E1" s="183"/>
+      <c r="F1" s="183"/>
+      <c r="G1" s="183"/>
+      <c r="H1" s="183"/>
+      <c r="I1" s="183"/>
+      <c r="J1" s="183"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="73" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>371</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>28</v>
@@ -12953,16 +13083,16 @@
     </row>
     <row r="5" spans="1:10" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="71" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="B5" s="74">
         <v>2024</v>
       </c>
       <c r="C5" s="65" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="D5" s="65" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="E5" s="66">
         <v>1576</v>
@@ -12976,24 +13106,24 @@
         <v>7.6765708718947874</v>
       </c>
       <c r="I5" s="67" t="s">
-        <v>396</v>
+        <v>423</v>
       </c>
       <c r="J5" s="68" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="B6" s="75">
         <v>2023</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="E6" s="69">
         <v>7273</v>
@@ -13013,21 +13143,21 @@
         <v>161.62222222222223</v>
       </c>
       <c r="J6" s="24" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="71" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="B7" s="74">
         <v>2022</v>
       </c>
       <c r="C7" s="65" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="D7" s="65" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="E7" s="66">
         <v>1591</v>
@@ -13047,21 +13177,21 @@
         <v>79.55</v>
       </c>
       <c r="J7" s="68" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="B8" s="75">
         <v>2024</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="E8" s="69">
         <v>600</v>
@@ -13081,21 +13211,21 @@
         <v>33.333333333333336</v>
       </c>
       <c r="J8" s="24" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="71" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="B9" s="74">
         <v>2022</v>
       </c>
       <c r="C9" s="65" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="D9" s="65" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="E9" s="66">
         <v>2364</v>
@@ -13115,25 +13245,25 @@
         <v>23.64</v>
       </c>
       <c r="J9" s="68" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="166" t="s">
-        <v>445</v>
-      </c>
-      <c r="B11" s="156"/>
-      <c r="C11" s="156"/>
-      <c r="D11" s="156"/>
-      <c r="E11" s="156"/>
-      <c r="F11" s="156"/>
-      <c r="G11" s="156"/>
-      <c r="H11" s="156"/>
-      <c r="I11" s="156"/>
+      <c r="A11" s="193" t="s">
+        <v>440</v>
+      </c>
+      <c r="B11" s="183"/>
+      <c r="C11" s="183"/>
+      <c r="D11" s="183"/>
+      <c r="E11" s="183"/>
+      <c r="F11" s="183"/>
+      <c r="G11" s="183"/>
+      <c r="H11" s="183"/>
+      <c r="I11" s="183"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>399</v>
+        <v>441</v>
       </c>
       <c r="H12" s="42">
         <f>MEDIAN(H5:H9)</f>
@@ -13144,12 +13274,12 @@
         <v>33.333333333333336</v>
       </c>
       <c r="J12" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="H13" s="42">
         <f>MIN(H5:H9)</f>
@@ -13162,7 +13292,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="H14" s="42">
         <f>MAX(H5:H9)</f>
@@ -13174,27 +13304,27 @@
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="166" t="s">
-        <v>447</v>
-      </c>
-      <c r="B16" s="156"/>
-      <c r="C16" s="156"/>
-      <c r="D16" s="156"/>
-      <c r="E16" s="156"/>
-      <c r="F16" s="156"/>
-      <c r="G16" s="156"/>
-      <c r="H16" s="156"/>
-      <c r="I16" s="156"/>
-      <c r="J16" s="156"/>
+      <c r="A16" s="193" t="s">
+        <v>443</v>
+      </c>
+      <c r="B16" s="183"/>
+      <c r="C16" s="183"/>
+      <c r="D16" s="183"/>
+      <c r="E16" s="183"/>
+      <c r="F16" s="183"/>
+      <c r="G16" s="183"/>
+      <c r="H16" s="183"/>
+      <c r="I16" s="183"/>
+      <c r="J16" s="183"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="76" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="F19" s="72">
         <f>Inputs!B6</f>
@@ -13203,7 +13333,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="F20" s="72">
         <f>DCF!C7</f>
@@ -13212,7 +13342,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="G21" s="72">
         <f>Inputs!B7</f>
@@ -13221,13 +13351,13 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="E23" s="18" t="s">
         <v>59</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="G23" s="18" t="s">
         <v>61</v>
@@ -13235,7 +13365,7 @@
     </row>
     <row r="24" spans="1:10" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E24" s="41">
         <v>4.7</v>
@@ -13247,12 +13377,12 @@
         <v>8.9</v>
       </c>
       <c r="J24" s="28" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="E25" s="51">
         <f>F19*E24</f>
@@ -13269,7 +13399,7 @@
     </row>
     <row r="27" spans="1:10" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="E27" s="52">
         <f>ROUND(E25,0)</f>
@@ -13284,12 +13414,12 @@
         <v>547</v>
       </c>
       <c r="J27" s="28" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="77" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
     </row>
   </sheetData>
@@ -13315,17 +13445,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="157" t="s">
+      <c r="A1" s="184" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="156"/>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
-      <c r="E1" s="156"/>
-      <c r="F1" s="156"/>
-      <c r="G1" s="156"/>
-      <c r="H1" s="156"/>
-      <c r="I1" s="156"/>
+      <c r="B1" s="183"/>
+      <c r="C1" s="183"/>
+      <c r="D1" s="183"/>
+      <c r="E1" s="183"/>
+      <c r="F1" s="183"/>
+      <c r="G1" s="183"/>
+      <c r="H1" s="183"/>
+      <c r="I1" s="183"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
@@ -13333,10 +13463,10 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="155" t="s">
+      <c r="A4" s="182" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="156"/>
+      <c r="B4" s="183"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
@@ -13377,10 +13507,10 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="155" t="s">
+      <c r="A10" s="182" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="156"/>
+      <c r="B10" s="183"/>
       <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
@@ -13513,10 +13643,10 @@
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="155" t="s">
+      <c r="A16" s="182" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="156"/>
+      <c r="B16" s="183"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
@@ -13646,10 +13776,10 @@
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="155" t="s">
+      <c r="A26" s="182" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="156"/>
+      <c r="B26" s="183"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">

--- a/Sidetrade_Valuation_2026_v2.xlsx
+++ b/Sidetrade_Valuation_2026_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abbah\Downloads\Portefolio\Portefolio\Sidetrade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F051A0E-A785-4A38-944C-868FA7EBF77F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{166AB060-922B-46C8-B4D5-13E04260D50A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21840" tabRatio="500" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,10 +48,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="776">
   <si>
-    <t>LBO AFFORDABILITY MODEL — BASE CASE  |  Max Entry EV for IRR targets</t>
-  </si>
-  <si>
-    <t>Simplified LBO: all unlevered FCF applied to debt service. Exit at fixed EBITDA multiple yr 5. IRR = equity return.</t>
+    <t>OBSOLETE — DO NOT USE · LBO AFFORDABILITY MODEL v1 (simplified) — superseded by LBO_full on 15-Jul-2026</t>
+  </si>
+  <si>
+    <t>OBSOLETE (kept for build history only — figures inconsistent with the current model). Simplified LBO: all unlevered FCF applied to debt service, exit at fixed EBITDA multiple yr 5, entry leverage 35% of EV.</t>
   </si>
   <si>
     <t>ASSUMPTIONS  (cross-linked from Inputs)</t>
@@ -192,7 +192,7 @@
     <t>SIDETRADE S.A. — VALUATION ANALYSIS</t>
   </si>
   <si>
-    <t>Order-to-Cash Intelligence Platform  |  Euronext Growth: ALBFR.PA  |  FY2025 base  |  May 2026</t>
+    <t>Order-to-Cash Intelligence Platform  |  Euronext Growth: ALBFR.PA  |  FY2025 base  |  Valuation as of 15-Jul-2026 (v2.1)</t>
   </si>
   <si>
     <t>CENTRAL VALUATION — STAND-ALONE BASIS</t>
@@ -327,13 +327,13 @@
     <t>3. Net debt: strict basis = gross financial debt €31.0m − cash+securities €16.3m = €14.7m. No adjustments for deferred revenue, earn-outs, or operating leases.</t>
   </si>
   <si>
-    <t>4. Trading comps: EV/Sales and EV/EBITDA on FY2026E estimates for BlackLine, BILL, nCino, Workiva. EUR-translated at 1.10 USD/EUR. Esker shown as reference (delisted).</t>
+    <t>4. Trading comps: EV/Sales forward (primary) and EV/non-GAAP operating income (proxy) on refreshed peers BlackLine, BILL, nCino, Workiva — prices as of 15-Jul-2026, May-2026 guidances, EUR/USD 1.1424. Selected range fully formula-driven from the peer table.</t>
   </si>
   <si>
     <t>5. Transaction comps: Esker, Coupa, Billtrust, Pagero, Bottomline. All include control premium (30-50%); not directly comparable to stand-alone DCF/trading EV.</t>
   </si>
   <si>
-    <t>6. LBO: simplified affordability model. All unlevered FCF applied to debt repayment. Exit at 15× EBITDA yr 5. Entry leverage 35%. IRR = equity return (MoM^(1/5)−1).</t>
+    <t>6. LBO: full affordability model (LBO_full tab, engine-solved via lbo_engine.py): entry leverage 4.0x EBITDA FY25, all-in E3M + 479bps ≈ 7.16%, 1% mandatory amortisation + 75% cash sweep, CIR single-count, founder rollover; exit at 15× EBITDA yr 5. The earlier simplified model (35% leverage, full sweep, all-FCF-to-debt) is kept in the LBO_old tab as OBSOLETE history — do not use.</t>
   </si>
   <si>
     <t>7. Margin path: point estimate = linear. Front-loaded and back-loaded paths computed in Margin_path tab. EV spread vs. linear: ±3-5%.</t>
@@ -1419,7 +1419,7 @@
     <t>SIDETRADE — LBO MODEL (FULL)</t>
   </si>
   <si>
-    <t>Build v1.0 · 10-Jun-2026 · per Build Spec v3 · Blue = input · Black = formula · Green = cross-sheet link</t>
+    <t>Build v2.1 · 15-Jul-2026 (CIR single-count fix, comps refresh 15/07, WACC bridge, Checks sheet) · originally v1.0 10-Jun-2026 per Build Spec v3 · Blue = input · Black = formula · Green = cross-sheet link</t>
   </si>
   <si>
     <t>Interest on OPENING debt (documented non-circular variant, Spec §3.4). Engine-solved values flagged in Source column.</t>
@@ -2394,7 +2394,7 @@
     <numFmt numFmtId="174" formatCode="0.00&quot;x&quot;"/>
     <numFmt numFmtId="175" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="46" x14ac:knownFonts="1">
+  <fonts count="48" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2682,6 +2682,18 @@
       <color rgb="FF808080"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="20">
     <fill>
@@ -2812,7 +2824,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="198">
+  <cellXfs count="200">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3130,11 +3142,12 @@
     <xf numFmtId="166" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3142,6 +3155,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3446,31 +3462,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="190" t="s">
+      <c r="A1" s="192" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
+      <c r="E1" s="185"/>
     </row>
     <row r="2" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="189" t="s">
+      <c r="A2" s="191" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="184"/>
-      <c r="C2" s="184"/>
-      <c r="D2" s="184"/>
-      <c r="E2" s="184"/>
+      <c r="B2" s="185"/>
+      <c r="C2" s="185"/>
+      <c r="D2" s="185"/>
+      <c r="E2" s="185"/>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="186" t="s">
+      <c r="A4" s="187" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="184"/>
-      <c r="C4" s="184"/>
-      <c r="D4" s="184"/>
-      <c r="E4" s="184"/>
+      <c r="B4" s="185"/>
+      <c r="C4" s="185"/>
+      <c r="D4" s="185"/>
+      <c r="E4" s="185"/>
     </row>
     <row r="5" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
@@ -3558,13 +3574,13 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="186" t="s">
+      <c r="A11" s="187" t="s">
         <v>55</v>
       </c>
-      <c r="B11" s="184"/>
-      <c r="C11" s="184"/>
-      <c r="D11" s="184"/>
-      <c r="E11" s="184"/>
+      <c r="B11" s="185"/>
+      <c r="C11" s="185"/>
+      <c r="D11" s="185"/>
+      <c r="E11" s="185"/>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
@@ -3579,13 +3595,13 @@
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="186" t="s">
+      <c r="A14" s="187" t="s">
         <v>58</v>
       </c>
-      <c r="B14" s="184"/>
-      <c r="C14" s="184"/>
-      <c r="D14" s="184"/>
-      <c r="E14" s="184"/>
+      <c r="B14" s="185"/>
+      <c r="C14" s="185"/>
+      <c r="D14" s="185"/>
+      <c r="E14" s="185"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B15" s="15" t="s">
@@ -3682,13 +3698,13 @@
       </c>
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="186" t="s">
+      <c r="A21" s="187" t="s">
         <v>71</v>
       </c>
-      <c r="B21" s="184"/>
-      <c r="C21" s="184"/>
-      <c r="D21" s="184"/>
-      <c r="E21" s="184"/>
+      <c r="B21" s="185"/>
+      <c r="C21" s="185"/>
+      <c r="D21" s="185"/>
+      <c r="E21" s="185"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
@@ -3727,13 +3743,13 @@
       </c>
     </row>
     <row r="27" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="186" t="s">
+      <c r="A27" s="187" t="s">
         <v>76</v>
       </c>
-      <c r="B27" s="184"/>
-      <c r="C27" s="184"/>
-      <c r="D27" s="184"/>
-      <c r="E27" s="184"/>
+      <c r="B27" s="185"/>
+      <c r="C27" s="185"/>
+      <c r="D27" s="185"/>
+      <c r="E27" s="185"/>
     </row>
     <row r="28" spans="1:5" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="26" t="s">
@@ -3819,85 +3835,85 @@
       </c>
     </row>
     <row r="35" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="185" t="s">
+      <c r="A35" s="189" t="s">
         <v>89</v>
       </c>
-      <c r="B35" s="184"/>
-      <c r="C35" s="184"/>
-      <c r="D35" s="184"/>
-      <c r="E35" s="184"/>
+      <c r="B35" s="185"/>
+      <c r="C35" s="185"/>
+      <c r="D35" s="185"/>
+      <c r="E35" s="185"/>
     </row>
     <row r="36" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="188" t="s">
+      <c r="A36" s="190" t="s">
         <v>90</v>
       </c>
-      <c r="B36" s="184"/>
-      <c r="C36" s="184"/>
-      <c r="D36" s="184"/>
-      <c r="E36" s="184"/>
+      <c r="B36" s="185"/>
+      <c r="C36" s="185"/>
+      <c r="D36" s="185"/>
+      <c r="E36" s="185"/>
     </row>
     <row r="37" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="187" t="s">
+      <c r="A37" s="188" t="s">
         <v>91</v>
       </c>
-      <c r="B37" s="184"/>
-      <c r="C37" s="184"/>
-      <c r="D37" s="184"/>
-      <c r="E37" s="184"/>
+      <c r="B37" s="185"/>
+      <c r="C37" s="185"/>
+      <c r="D37" s="185"/>
+      <c r="E37" s="185"/>
     </row>
     <row r="38" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="188" t="s">
+      <c r="A38" s="190" t="s">
         <v>92</v>
       </c>
-      <c r="B38" s="184"/>
-      <c r="C38" s="184"/>
-      <c r="D38" s="184"/>
-      <c r="E38" s="184"/>
+      <c r="B38" s="185"/>
+      <c r="C38" s="185"/>
+      <c r="D38" s="185"/>
+      <c r="E38" s="185"/>
     </row>
     <row r="39" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="187" t="s">
+      <c r="A39" s="188" t="s">
         <v>93</v>
       </c>
-      <c r="B39" s="184"/>
-      <c r="C39" s="184"/>
-      <c r="D39" s="184"/>
-      <c r="E39" s="184"/>
+      <c r="B39" s="185"/>
+      <c r="C39" s="185"/>
+      <c r="D39" s="185"/>
+      <c r="E39" s="185"/>
     </row>
     <row r="40" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="188" t="s">
+      <c r="A40" s="190" t="s">
         <v>94</v>
       </c>
-      <c r="B40" s="184"/>
-      <c r="C40" s="184"/>
-      <c r="D40" s="184"/>
-      <c r="E40" s="184"/>
+      <c r="B40" s="185"/>
+      <c r="C40" s="185"/>
+      <c r="D40" s="185"/>
+      <c r="E40" s="185"/>
     </row>
     <row r="41" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="187" t="s">
+      <c r="A41" s="188" t="s">
         <v>95</v>
       </c>
-      <c r="B41" s="184"/>
-      <c r="C41" s="184"/>
-      <c r="D41" s="184"/>
-      <c r="E41" s="184"/>
+      <c r="B41" s="185"/>
+      <c r="C41" s="185"/>
+      <c r="D41" s="185"/>
+      <c r="E41" s="185"/>
     </row>
     <row r="42" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="188" t="s">
+      <c r="A42" s="190" t="s">
         <v>96</v>
       </c>
-      <c r="B42" s="184"/>
-      <c r="C42" s="184"/>
-      <c r="D42" s="184"/>
-      <c r="E42" s="184"/>
+      <c r="B42" s="185"/>
+      <c r="C42" s="185"/>
+      <c r="D42" s="185"/>
+      <c r="E42" s="185"/>
     </row>
     <row r="43" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="187" t="s">
+      <c r="A43" s="188" t="s">
         <v>97</v>
       </c>
-      <c r="B43" s="184"/>
-      <c r="C43" s="184"/>
-      <c r="D43" s="184"/>
-      <c r="E43" s="184"/>
+      <c r="B43" s="185"/>
+      <c r="C43" s="185"/>
+      <c r="D43" s="185"/>
+      <c r="E43" s="185"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -7781,15 +7797,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="191" t="s">
+      <c r="A1" s="193" t="s">
         <v>660</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
+      <c r="E1" s="185"/>
+      <c r="F1" s="185"/>
+      <c r="G1" s="185"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
@@ -7938,15 +7954,15 @@
       <c r="G9" s="97"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="194" t="s">
+      <c r="A10" s="196" t="s">
         <v>674</v>
       </c>
-      <c r="B10" s="184"/>
-      <c r="C10" s="184"/>
-      <c r="D10" s="184"/>
-      <c r="E10" s="184"/>
-      <c r="F10" s="184"/>
-      <c r="G10" s="184"/>
+      <c r="B10" s="185"/>
+      <c r="C10" s="185"/>
+      <c r="D10" s="185"/>
+      <c r="E10" s="185"/>
+      <c r="F10" s="185"/>
+      <c r="G10" s="185"/>
     </row>
     <row r="11" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
@@ -8093,13 +8109,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="191" t="s">
+      <c r="A1" s="193" t="s">
         <v>687</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
+      <c r="E1" s="185"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
@@ -8121,12 +8137,12 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="183" t="s">
+      <c r="A5" s="184" t="s">
         <v>689</v>
       </c>
-      <c r="B5" s="184"/>
-      <c r="C5" s="184"/>
-      <c r="D5" s="184"/>
+      <c r="B5" s="185"/>
+      <c r="C5" s="185"/>
+      <c r="D5" s="185"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
@@ -8146,12 +8162,12 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="183" t="s">
+      <c r="A8" s="184" t="s">
         <v>690</v>
       </c>
-      <c r="B8" s="184"/>
-      <c r="C8" s="184"/>
-      <c r="D8" s="184"/>
+      <c r="B8" s="185"/>
+      <c r="C8" s="185"/>
+      <c r="D8" s="185"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
@@ -8234,12 +8250,12 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="183" t="s">
+      <c r="A14" s="184" t="s">
         <v>696</v>
       </c>
-      <c r="B14" s="184"/>
-      <c r="C14" s="184"/>
-      <c r="D14" s="184"/>
+      <c r="B14" s="185"/>
+      <c r="C14" s="185"/>
+      <c r="D14" s="185"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
@@ -8259,12 +8275,12 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="183" t="s">
+      <c r="A17" s="184" t="s">
         <v>698</v>
       </c>
-      <c r="B17" s="184"/>
-      <c r="C17" s="184"/>
-      <c r="D17" s="184"/>
+      <c r="B17" s="185"/>
+      <c r="C17" s="185"/>
+      <c r="D17" s="185"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
@@ -8321,12 +8337,12 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="183" t="s">
+      <c r="A22" s="184" t="s">
         <v>703</v>
       </c>
-      <c r="B22" s="184"/>
-      <c r="C22" s="184"/>
-      <c r="D22" s="184"/>
+      <c r="B22" s="185"/>
+      <c r="C22" s="185"/>
+      <c r="D22" s="185"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
@@ -8359,13 +8375,13 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="197" t="s">
+      <c r="A27" s="199" t="s">
         <v>708</v>
       </c>
-      <c r="B27" s="184"/>
-      <c r="C27" s="184"/>
-      <c r="D27" s="184"/>
-      <c r="E27" s="184"/>
+      <c r="B27" s="185"/>
+      <c r="C27" s="185"/>
+      <c r="D27" s="185"/>
+      <c r="E27" s="185"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
@@ -8439,12 +8455,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="191" t="s">
+      <c r="A1" s="193" t="s">
         <v>714</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -8879,13 +8895,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="191" t="s">
+      <c r="A1" s="193" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
+      <c r="E1" s="185"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
@@ -8910,13 +8926,13 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="183" t="s">
+      <c r="A5" s="184" t="s">
         <v>105</v>
       </c>
-      <c r="B5" s="184"/>
-      <c r="C5" s="184"/>
-      <c r="D5" s="184"/>
-      <c r="E5" s="184"/>
+      <c r="B5" s="185"/>
+      <c r="C5" s="185"/>
+      <c r="D5" s="185"/>
+      <c r="E5" s="185"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
@@ -9024,13 +9040,13 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="183" t="s">
+      <c r="A13" s="184" t="s">
         <v>118</v>
       </c>
-      <c r="B13" s="184"/>
-      <c r="C13" s="184"/>
-      <c r="D13" s="184"/>
-      <c r="E13" s="184"/>
+      <c r="B13" s="185"/>
+      <c r="C13" s="185"/>
+      <c r="D13" s="185"/>
+      <c r="E13" s="185"/>
     </row>
     <row r="14" spans="1:5" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
@@ -9112,13 +9128,13 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="183" t="s">
+      <c r="A20" s="184" t="s">
         <v>127</v>
       </c>
-      <c r="B20" s="184"/>
-      <c r="C20" s="184"/>
-      <c r="D20" s="184"/>
-      <c r="E20" s="184"/>
+      <c r="B20" s="185"/>
+      <c r="C20" s="185"/>
+      <c r="D20" s="185"/>
+      <c r="E20" s="185"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
@@ -9246,13 +9262,13 @@
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="183" t="s">
+      <c r="A29" s="184" t="s">
         <v>138</v>
       </c>
-      <c r="B29" s="184"/>
-      <c r="C29" s="184"/>
-      <c r="D29" s="184"/>
-      <c r="E29" s="184"/>
+      <c r="B29" s="185"/>
+      <c r="C29" s="185"/>
+      <c r="D29" s="185"/>
+      <c r="E29" s="185"/>
     </row>
     <row r="30" spans="1:5" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
@@ -9340,13 +9356,13 @@
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="183" t="s">
+      <c r="A36" s="184" t="s">
         <v>149</v>
       </c>
-      <c r="B36" s="184"/>
-      <c r="C36" s="184"/>
-      <c r="D36" s="184"/>
-      <c r="E36" s="184"/>
+      <c r="B36" s="185"/>
+      <c r="C36" s="185"/>
+      <c r="D36" s="185"/>
+      <c r="E36" s="185"/>
     </row>
     <row r="37" spans="1:5" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
@@ -9400,13 +9416,13 @@
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="183" t="s">
+      <c r="A41" s="184" t="s">
         <v>156</v>
       </c>
-      <c r="B41" s="184"/>
-      <c r="C41" s="184"/>
-      <c r="D41" s="184"/>
-      <c r="E41" s="184"/>
+      <c r="B41" s="185"/>
+      <c r="C41" s="185"/>
+      <c r="D41" s="185"/>
+      <c r="E41" s="185"/>
     </row>
     <row r="42" spans="1:5" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
@@ -9600,18 +9616,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="185" t="s">
+      <c r="A1" s="189" t="s">
         <v>180</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="183" t="s">
+      <c r="A3" s="184" t="s">
         <v>181</v>
       </c>
-      <c r="B3" s="184"/>
+      <c r="B3" s="185"/>
       <c r="C3" s="3" t="s">
         <v>182</v>
       </c>
@@ -9819,10 +9835,10 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="183" t="s">
+      <c r="A19" s="184" t="s">
         <v>209</v>
       </c>
-      <c r="B19" s="184"/>
+      <c r="B19" s="185"/>
       <c r="C19" s="3" t="s">
         <v>182</v>
       </c>
@@ -9904,10 +9920,10 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="183" t="s">
+      <c r="A26" s="184" t="s">
         <v>219</v>
       </c>
-      <c r="B26" s="184"/>
+      <c r="B26" s="185"/>
       <c r="C26" s="3" t="s">
         <v>220</v>
       </c>
@@ -9992,10 +10008,10 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="183" t="s">
+      <c r="A35" s="184" t="s">
         <v>233</v>
       </c>
-      <c r="B35" s="184"/>
+      <c r="B35" s="185"/>
       <c r="C35" s="3" t="s">
         <v>234</v>
       </c>
@@ -10098,10 +10114,10 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="183" t="s">
+      <c r="A45" s="184" t="s">
         <v>246</v>
       </c>
-      <c r="B45" s="184"/>
+      <c r="B45" s="185"/>
       <c r="C45" s="3" t="s">
         <v>247</v>
       </c>
@@ -10150,10 +10166,10 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="183" t="s">
+      <c r="A51" s="184" t="s">
         <v>254</v>
       </c>
-      <c r="B51" s="184"/>
+      <c r="B51" s="185"/>
       <c r="C51" s="3" t="s">
         <v>247</v>
       </c>
@@ -10215,10 +10231,10 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="183" t="s">
+      <c r="A58" s="184" t="s">
         <v>264</v>
       </c>
-      <c r="B58" s="184"/>
+      <c r="B58" s="185"/>
       <c r="C58" s="3" t="s">
         <v>247</v>
       </c>
@@ -10295,10 +10311,10 @@
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="183" t="s">
+      <c r="A67" s="184" t="s">
         <v>274</v>
       </c>
-      <c r="B67" s="184"/>
+      <c r="B67" s="185"/>
     </row>
     <row r="68" spans="1:4" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="9" t="s">
@@ -10350,27 +10366,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="191" t="s">
+      <c r="A1" s="193" t="s">
         <v>279</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
-      <c r="H1" s="184"/>
-      <c r="I1" s="184"/>
-      <c r="J1" s="184"/>
-      <c r="K1" s="184"/>
-      <c r="L1" s="184"/>
-      <c r="M1" s="184"/>
-      <c r="N1" s="184"/>
-      <c r="O1" s="184"/>
-      <c r="P1" s="184"/>
-      <c r="Q1" s="184"/>
-      <c r="R1" s="184"/>
-      <c r="S1" s="184"/>
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
+      <c r="E1" s="185"/>
+      <c r="F1" s="185"/>
+      <c r="G1" s="185"/>
+      <c r="H1" s="185"/>
+      <c r="I1" s="185"/>
+      <c r="J1" s="185"/>
+      <c r="K1" s="185"/>
+      <c r="L1" s="185"/>
+      <c r="M1" s="185"/>
+      <c r="N1" s="185"/>
+      <c r="O1" s="185"/>
+      <c r="P1" s="185"/>
+      <c r="Q1" s="185"/>
+      <c r="R1" s="185"/>
+      <c r="S1" s="185"/>
     </row>
     <row r="2" spans="1:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="54" t="s">
@@ -10378,36 +10394,36 @@
       </c>
     </row>
     <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="192" t="s">
+      <c r="B3" s="194" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="184"/>
-      <c r="D3" s="184"/>
-      <c r="E3" s="192" t="s">
+      <c r="C3" s="185"/>
+      <c r="D3" s="185"/>
+      <c r="E3" s="194" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="184"/>
-      <c r="G3" s="184"/>
-      <c r="H3" s="192" t="s">
+      <c r="F3" s="185"/>
+      <c r="G3" s="185"/>
+      <c r="H3" s="194" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="184"/>
-      <c r="J3" s="184"/>
-      <c r="K3" s="192" t="s">
+      <c r="I3" s="185"/>
+      <c r="J3" s="185"/>
+      <c r="K3" s="194" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="184"/>
-      <c r="M3" s="184"/>
-      <c r="N3" s="192" t="s">
+      <c r="L3" s="185"/>
+      <c r="M3" s="185"/>
+      <c r="N3" s="194" t="s">
         <v>13</v>
       </c>
-      <c r="O3" s="184"/>
-      <c r="P3" s="184"/>
-      <c r="Q3" s="193" t="s">
+      <c r="O3" s="185"/>
+      <c r="P3" s="185"/>
+      <c r="Q3" s="195" t="s">
         <v>281</v>
       </c>
-      <c r="R3" s="184"/>
-      <c r="S3" s="184"/>
+      <c r="R3" s="185"/>
+      <c r="S3" s="185"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B4" s="55" t="s">
@@ -11688,16 +11704,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="185" t="s">
+      <c r="A1" s="189" t="s">
         <v>317</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
-      <c r="H1" s="184"/>
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
+      <c r="E1" s="185"/>
+      <c r="F1" s="185"/>
+      <c r="G1" s="185"/>
+      <c r="H1" s="185"/>
     </row>
     <row r="2" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
@@ -11705,15 +11721,15 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="194" t="s">
+      <c r="A4" s="196" t="s">
         <v>319</v>
       </c>
-      <c r="B4" s="184"/>
-      <c r="C4" s="184"/>
-      <c r="D4" s="184"/>
-      <c r="E4" s="184"/>
-      <c r="F4" s="184"/>
-      <c r="G4" s="184"/>
+      <c r="B4" s="185"/>
+      <c r="C4" s="185"/>
+      <c r="D4" s="185"/>
+      <c r="E4" s="185"/>
+      <c r="F4" s="185"/>
+      <c r="G4" s="185"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
@@ -11866,15 +11882,15 @@
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="194" t="s">
+      <c r="A14" s="196" t="s">
         <v>322</v>
       </c>
-      <c r="B14" s="184"/>
-      <c r="C14" s="184"/>
-      <c r="D14" s="184"/>
-      <c r="E14" s="184"/>
-      <c r="F14" s="184"/>
-      <c r="G14" s="184"/>
+      <c r="B14" s="185"/>
+      <c r="C14" s="185"/>
+      <c r="D14" s="185"/>
+      <c r="E14" s="185"/>
+      <c r="F14" s="185"/>
+      <c r="G14" s="185"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
@@ -12053,13 +12069,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="185" t="s">
+      <c r="A1" s="189" t="s">
         <v>326</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
+      <c r="E1" s="185"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
@@ -12115,13 +12131,13 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="194" t="s">
+      <c r="A8" s="196" t="s">
         <v>332</v>
       </c>
-      <c r="B8" s="184"/>
-      <c r="C8" s="184"/>
-      <c r="D8" s="184"/>
-      <c r="E8" s="184"/>
+      <c r="B8" s="185"/>
+      <c r="C8" s="185"/>
+      <c r="D8" s="185"/>
+      <c r="E8" s="185"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
@@ -12224,13 +12240,13 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="194" t="s">
+      <c r="A15" s="196" t="s">
         <v>338</v>
       </c>
-      <c r="B15" s="184"/>
-      <c r="C15" s="184"/>
-      <c r="D15" s="184"/>
-      <c r="E15" s="184"/>
+      <c r="B15" s="185"/>
+      <c r="C15" s="185"/>
+      <c r="D15" s="185"/>
+      <c r="E15" s="185"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
@@ -12418,13 +12434,13 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="194" t="s">
+      <c r="A27" s="196" t="s">
         <v>354</v>
       </c>
-      <c r="B27" s="184"/>
-      <c r="C27" s="184"/>
-      <c r="D27" s="184"/>
-      <c r="E27" s="184"/>
+      <c r="B27" s="185"/>
+      <c r="C27" s="185"/>
+      <c r="D27" s="185"/>
+      <c r="E27" s="185"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
@@ -12629,17 +12645,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="195" t="s">
+      <c r="A1" s="197" t="s">
         <v>366</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
-      <c r="H1" s="184"/>
-      <c r="I1" s="184"/>
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
+      <c r="E1" s="185"/>
+      <c r="F1" s="185"/>
+      <c r="G1" s="185"/>
+      <c r="H1" s="185"/>
+      <c r="I1" s="185"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="155" t="s">
@@ -12824,17 +12840,17 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="196" t="s">
+      <c r="A11" s="198" t="s">
         <v>392</v>
       </c>
-      <c r="B11" s="184"/>
-      <c r="C11" s="184"/>
-      <c r="D11" s="184"/>
-      <c r="E11" s="184"/>
-      <c r="F11" s="184"/>
-      <c r="G11" s="184"/>
-      <c r="H11" s="184"/>
-      <c r="I11" s="184"/>
+      <c r="B11" s="185"/>
+      <c r="C11" s="185"/>
+      <c r="D11" s="185"/>
+      <c r="E11" s="185"/>
+      <c r="F11" s="185"/>
+      <c r="G11" s="185"/>
+      <c r="H11" s="185"/>
+      <c r="I11" s="185"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="171" t="s">
@@ -12876,17 +12892,17 @@
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="196" t="s">
+      <c r="A16" s="198" t="s">
         <v>396</v>
       </c>
-      <c r="B16" s="184"/>
-      <c r="C16" s="184"/>
-      <c r="D16" s="184"/>
-      <c r="E16" s="184"/>
-      <c r="F16" s="184"/>
-      <c r="G16" s="184"/>
-      <c r="H16" s="184"/>
-      <c r="I16" s="184"/>
+      <c r="B16" s="185"/>
+      <c r="C16" s="185"/>
+      <c r="D16" s="185"/>
+      <c r="E16" s="185"/>
+      <c r="F16" s="185"/>
+      <c r="G16" s="185"/>
+      <c r="H16" s="185"/>
+      <c r="I16" s="185"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="171" t="s">
@@ -13038,18 +13054,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="185" t="s">
+      <c r="A1" s="189" t="s">
         <v>410</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
-      <c r="H1" s="184"/>
-      <c r="I1" s="184"/>
-      <c r="J1" s="184"/>
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
+      <c r="E1" s="185"/>
+      <c r="F1" s="185"/>
+      <c r="G1" s="185"/>
+      <c r="H1" s="185"/>
+      <c r="I1" s="185"/>
+      <c r="J1" s="185"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="73" t="s">
@@ -13256,17 +13272,17 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="194" t="s">
+      <c r="A11" s="196" t="s">
         <v>440</v>
       </c>
-      <c r="B11" s="184"/>
-      <c r="C11" s="184"/>
-      <c r="D11" s="184"/>
-      <c r="E11" s="184"/>
-      <c r="F11" s="184"/>
-      <c r="G11" s="184"/>
-      <c r="H11" s="184"/>
-      <c r="I11" s="184"/>
+      <c r="B11" s="185"/>
+      <c r="C11" s="185"/>
+      <c r="D11" s="185"/>
+      <c r="E11" s="185"/>
+      <c r="F11" s="185"/>
+      <c r="G11" s="185"/>
+      <c r="H11" s="185"/>
+      <c r="I11" s="185"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
@@ -13311,18 +13327,18 @@
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="194" t="s">
+      <c r="A16" s="196" t="s">
         <v>443</v>
       </c>
-      <c r="B16" s="184"/>
-      <c r="C16" s="184"/>
-      <c r="D16" s="184"/>
-      <c r="E16" s="184"/>
-      <c r="F16" s="184"/>
-      <c r="G16" s="184"/>
-      <c r="H16" s="184"/>
-      <c r="I16" s="184"/>
-      <c r="J16" s="184"/>
+      <c r="B16" s="185"/>
+      <c r="C16" s="185"/>
+      <c r="D16" s="185"/>
+      <c r="E16" s="185"/>
+      <c r="F16" s="185"/>
+      <c r="G16" s="185"/>
+      <c r="H16" s="185"/>
+      <c r="I16" s="185"/>
+      <c r="J16" s="185"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="76" t="s">
@@ -13442,6 +13458,9 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FFC00000"/>
+  </sheetPr>
   <dimension ref="A1:I35"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -13452,28 +13471,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="185" t="s">
+      <c r="A1" s="186" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
-      <c r="H1" s="184"/>
-      <c r="I1" s="184"/>
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
+      <c r="E1" s="185"/>
+      <c r="F1" s="185"/>
+      <c r="G1" s="185"/>
+      <c r="H1" s="185"/>
+      <c r="I1" s="185"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="183" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="183" t="s">
+      <c r="A4" s="184" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="184"/>
+      <c r="B4" s="185"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
@@ -13514,10 +13533,10 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="183" t="s">
+      <c r="A10" s="184" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="184"/>
+      <c r="B10" s="185"/>
       <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
@@ -13650,10 +13669,10 @@
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="183" t="s">
+      <c r="A16" s="184" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="184"/>
+      <c r="B16" s="185"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
@@ -13783,10 +13802,10 @@
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="183" t="s">
+      <c r="A26" s="184" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="184"/>
+      <c r="B26" s="185"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">

--- a/Sidetrade_Valuation_2026_v2.xlsx
+++ b/Sidetrade_Valuation_2026_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abbah\Downloads\Portefolio\Portefolio\Sidetrade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{166AB060-922B-46C8-B4D5-13E04260D50A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75E4E93E-324A-4B25-AC5D-2207C280626E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21840" tabRatio="500" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
